--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-08-31 10:21 UTC</t>
+          <t>Généré le 2026-10-11 13:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
-        <v>47000</v>
+        <v>14000</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>8</v>
@@ -1993,13 +1993,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>197000</v>
+        <v>20000</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
         <v>12</v>
@@ -2042,13 +2042,13 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>250000</v>
+        <v>28000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -2090,13 +2090,13 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>349000</v>
+        <v>38000</v>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="F5" t="n">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>18</v>
@@ -2138,13 +2138,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>500000</v>
+        <v>41000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>15</v>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="H2" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
@@ -3250,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>15</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>0</v>
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>0</v>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
@@ -4817,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
@@ -4964,10 +4964,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>7</v>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5458,10 +5458,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>20</v>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -5596,13 +5596,13 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -5886,10 +5886,10 @@
         <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
@@ -5955,10 +5955,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>0</v>
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>15</v>
@@ -6243,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>0</v>
@@ -6387,13 +6387,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>5</v>
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>0</v>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>15</v>
@@ -6891,10 +6891,10 @@
         <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7028,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0</v>
@@ -7173,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>2</v>
@@ -7242,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -7310,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K66" s="5" t="n">
         <v>0</v>
@@ -7379,10 +7379,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7584,10 +7584,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
         <v>0</v>
@@ -7722,13 +7722,13 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K72" s="5" t="n">
         <v>0</v>
@@ -7988,34 +7988,34 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>5</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>40</v>
@@ -8063,34 +8063,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
@@ -8138,13 +8138,13 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -8162,10 +8162,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>30</v>
@@ -8199,27 +8199,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gobelin_chaman</t>
+          <t>squelette</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gobelin Chaman</t>
+          <t>Squelette</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5" s="9">
         <f>ROUND((E5*(1+(H5/100)*MAX(0,I5-100)/100)*(1+G5/100))*((D5+F5*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J5/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8255,1444 +8255,1444 @@
       </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
+          <t>os_poli ×1-2 (22%)
+poussiere_d_ossements ×1-2 (18%)
+dague_rouillee ×1-1 (5%)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>squelette.png</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Un pantin d'os réanimé. Le premier pas dans le royaume des morts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_chaman</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Chaman</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" s="9">
+        <f>ROUND((E6*(1+(H6/100)*MAX(0,I6-100)/100)*(1+G6/100))*((D6+F6*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J6/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="9">
+        <f>IFERROR(VLOOKUP(O6,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
           <t>gourde_de_chaman ×1-1 (20%)
 fetiche_d_os ×1-1 (5%)
 baton_a_crane ×1-1 (2%)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>gobelin_chaman.png</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>Une créature intelligente.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>zombie</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Zombie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>528</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>112</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" s="9">
+        <f>ROUND((E7*(1+(H7/100)*MAX(0,I7-100)/100)*(1+G7/100))*((D7+F7*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J7/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="9">
+        <f>IFERROR(VLOOKUP(O7,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>chair_putride ×1-2 (22%)
+lambeau_de_vetement ×1-2 (18%)
+dent_gatee ×1-1 (12%)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>zombie.png</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Une carcasse putride et lente, mais coriace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>gobelin_ballon</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Gobelin Ballon</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>480</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J6" s="5" t="n">
+      <c r="D8" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="N6" s="5" t="n">
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="N8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="O6" s="9">
-        <f>ROUND((E6*(1+(H6/100)*MAX(0,I6-100)/100)*(1+G6/100))*((D6+F6*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J6/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O8" s="9">
+        <f>ROUND((E8*(1+(H8/100)*MAX(0,I8-100)/100)*(1+G8/100))*((D8+F8*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J8/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P6" s="9">
-        <f>IFERROR(VLOOKUP(O6,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P8" s="9">
+        <f>IFERROR(VLOOKUP(O8,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>toile_de_dirigeable ×1-2 (22%)
 grappin_rouille ×1-1 (10%)
 petite_bombe ×1-2 (6%)</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>gobelin_ballon.png</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S8" s="5" t="inlineStr">
         <is>
           <t>Un groupe de créatures inventives.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>gobelin_geant</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gobelin Géant</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>150</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>110</v>
-      </c>
-      <c r="M7" t="n">
-        <v>75</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="D9" t="n">
+        <v>610</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>144</v>
+      </c>
+      <c r="M9" t="n">
+        <v>69</v>
+      </c>
+      <c r="N9" t="n">
         <v>20</v>
       </c>
-      <c r="O7" s="9">
-        <f>ROUND((E7*(1+(H7/100)*MAX(0,I7-100)/100)*(1+G7/100))*((D7+F7*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J7/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O9" s="9">
+        <f>ROUND((E9*(1+(H9/100)*MAX(0,I9-100)/100)*(1+G9/100))*((D9+F9*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J9/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P7" s="9">
-        <f>IFERROR(VLOOKUP(O7,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P9" s="9">
+        <f>IFERROR(VLOOKUP(O9,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>os_massif ×1-2 (22%)
 ceinturon_epais ×1-1 (5%)
 gourdin_de_tronc ×1-1 (2%)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>gobelin_geant.png</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Une créature imposante.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>momie</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Momie</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>418</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="9">
+        <f>ROUND((E10*(1+(H10/100)*MAX(0,I10-100)/100)*(1+G10/100))*((D10+F10*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J10/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="9">
+        <f>IFERROR(VLOOKUP(O10,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>bandelette_maudite ×1-2 (22%)
+resine_d_embaumement ×1-1 (10%)
+griffe_noircie ×1-1 (5%)</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>momie.png</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>Un corps embaumé aux bandelettes maudites, quasi increvable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>gobelin_runique</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Gobelin Runique</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>573</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="D11" t="n">
+        <v>361</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>238</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="N8" s="5" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>169</v>
+      </c>
+      <c r="M11" t="n">
+        <v>81</v>
+      </c>
+      <c r="N11" t="n">
         <v>20</v>
       </c>
-      <c r="O8" s="9">
-        <f>ROUND((E8*(1+(H8/100)*MAX(0,I8-100)/100)*(1+G8/100))*((D8+F8*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J8/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O11" s="9">
+        <f>ROUND((E11*(1+(H11/100)*MAX(0,I11-100)/100)*(1+G11/100))*((D11+F11*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J11/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P8" s="9">
-        <f>IFERROR(VLOOKUP(O8,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P11" s="9">
+        <f>IFERROR(VLOOKUP(O11,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>encre_rituelle ×1-2 (20%)
 pierre_runique ×1-1 (10%)
 collier_de_perles ×1-1 (4%)</t>
         </is>
       </c>
-      <c r="R8" s="5" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>gobelin_runique.png</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Une créature mystérieuse.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>fantome</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Fantôme</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="9">
+        <f>ROUND((E12*(1+(H12/100)*MAX(0,I12-100)/100)*(1+G12/100))*((D12+F12*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J12/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="9">
+        <f>IFERROR(VLOOKUP(O12,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>voile_ectoplasmique ×1-1 (4%)
+chaine_spectrale ×1-1 (4%)
+boulet_hante ×1-1 (2%)</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>fantome.png</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>Une âme errante insaisissable qui glisse entre les coups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gobelin_assassin</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gobelin Assassin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gobelin</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>297</v>
+      </c>
+      <c r="E13" t="n">
+        <v>54</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>150</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>194</v>
+      </c>
+      <c r="M13" t="n">
+        <v>93</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" s="9">
+        <f>ROUND((E13*(1+(H13/100)*MAX(0,I13-100)/100)*(1+G13/100))*((D13+F13*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J13/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="9">
+        <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>morceau_de_tissu ×1-2 (20%)
+dagues_jumelles ×1-1 (5%)
+cape_silencieuse ×1-1 (1%)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>gobelin_assassin.png</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Une créature discrète.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>gobelin_superieur</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Gobelin Supérieur</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>gobelin</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>876</v>
-      </c>
-      <c r="E9" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D14" s="5" t="n">
+        <v>539</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>300</v>
-      </c>
-      <c r="M9" t="n">
-        <v>144</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="N14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="O9" s="9">
-        <f>ROUND((E9*(1+(H9/100)*MAX(0,I9-100)/100)*(1+G9/100))*((D9+F9*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J9/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O14" s="9">
+        <f>ROUND((E14*(1+(H14/100)*MAX(0,I14-100)/100)*(1+G14/100))*((D14+F14*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J14/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P9" s="9">
-        <f>IFERROR(VLOOKUP(O9,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P14" s="9">
+        <f>IFERROR(VLOOKUP(O14,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>plaque_a_pointes ×1-1 (5%)
 casque_a_cornes ×1-1 (4%)
 masse_cloutee ×1-1 (1%)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>gobelin_superieur.png</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>Une créature supérieure.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_assassin</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Gobelin Assassin</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>gobelin</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="E10" s="5" t="n">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gargouille</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gargouille</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>858</v>
+      </c>
+      <c r="E15" t="n">
+        <v>43</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>238</v>
+      </c>
+      <c r="M15" t="n">
+        <v>114</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="9">
+        <f>ROUND((E15*(1+(H15/100)*MAX(0,I15-100)/100)*(1+G15/100))*((D15+F15*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J15/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="9">
+        <f>IFERROR(VLOOKUP(O15,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>eclat_de_pierre ×1-2 (22%)
+aile_de_pierre ×1-1 (4%)
+coeur_de_granit ×1-1 (3%)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>gargouille.png</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Une statue de pierre animée qui frappe comme un bélier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>diablotin</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Diablotin</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>demoniaque</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>383</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>225</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="9">
-        <f>ROUND((E10*(1+(H10/100)*MAX(0,I10-100)/100)*(1+G10/100))*((D10+F10*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J10/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O16" s="9">
+        <f>ROUND((E16*(1+(H16/100)*MAX(0,I16-100)/100)*(1+G16/100))*((D16+F16*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J16/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P10" s="9">
-        <f>IFERROR(VLOOKUP(O10,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P16" s="9">
+        <f>IFERROR(VLOOKUP(O16,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×1-2 (20%)
-dagues_jumelles ×1-1 (5%)
-cape_silencieuse ×1-1 (1%)</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_assassin.png</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>Une créature discrète.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diablotin</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Diablotin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>demoniaque</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>602</v>
-      </c>
-      <c r="E11" t="n">
-        <v>56</v>
-      </c>
-      <c r="F11" t="n">
-        <v>33</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" t="n">
-        <v>150</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>350</v>
-      </c>
-      <c r="M11" t="n">
-        <v>168</v>
-      </c>
-      <c r="N11" t="n">
-        <v>40</v>
-      </c>
-      <c r="O11" s="9">
-        <f>ROUND((E11*(1+(H11/100)*MAX(0,I11-100)/100)*(1+G11/100))*((D11+F11*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J11/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="9">
-        <f>IFERROR(VLOOKUP(O11,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>corne_naissante ×1-2 (22%)
 braise_infernale ×1-1 (10%)
 trident_ebreche ×1-1 (5%)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>diablotin.png</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>Petit démon espiègle et véloce, tout juste éclos du Berceau.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>banshee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Banshee</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>510</v>
+      </c>
+      <c r="E17" t="n">
+        <v>123</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>281</v>
+      </c>
+      <c r="M17" t="n">
+        <v>135</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="9">
+        <f>ROUND((E17*(1+(H17/100)*MAX(0,I17-100)/100)*(1+G17/100))*((D17+F17*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J17/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="9">
+        <f>IFERROR(VLOOKUP(O17,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>echo_de_cri ×1-1 (18%)
+larme_spectrale ×1-1 (5%)
+couronne_d_epines ×1-1 (2%)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>banshee.png</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Un spectre hurlant dont le cri glaçant transperce l'âme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>demon_cornu</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Démon cornu</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="G12" s="5" t="n">
+      <c r="D18" s="5" t="n">
+        <v>726</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>192</v>
-      </c>
-      <c r="N12" s="5" t="n">
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="N18" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="O12" s="9">
-        <f>ROUND((E12*(1+(H12/100)*MAX(0,I12-100)/100)*(1+G12/100))*((D12+F12*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J12/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O18" s="9">
+        <f>ROUND((E18*(1+(H18/100)*MAX(0,I18-100)/100)*(1+G18/100))*((D18+F18*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J18/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P12" s="9">
-        <f>IFERROR(VLOOKUP(O12,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P18" s="9">
+        <f>IFERROR(VLOOKUP(O18,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>corne_de_demon ×1-2 (20%)
 ceinturon_cloute ×1-1 (5%)
 lame_infernale ×1-1 (2%)</t>
         </is>
       </c>
-      <c r="R12" s="5" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>demon_cornu.png</t>
         </is>
       </c>
-      <c r="S12" s="5" t="inlineStr">
+      <c r="S18" s="5" t="inlineStr">
         <is>
           <t>Fantassin cornu des légions infernales, brutal et sans pitié.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>liche_maudite</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Liche maudite</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mort-vivant</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>598</v>
+      </c>
+      <c r="E19" t="n">
+        <v>145</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>338</v>
+      </c>
+      <c r="M19" t="n">
+        <v>162</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" s="9">
+        <f>ROUND((E19*(1+(H19/100)*MAX(0,I19-100)/100)*(1+G19/100))*((D19+F19*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J19/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P19" s="9">
+        <f>IFERROR(VLOOKUP(O19,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>grimoire_en_lambeaux ×1-1 (5%)
+orbe_maudit ×1-1 (2%)
+couronne_ternie ×1-1 (1%)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>liche_maudite.png</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>ogre_demoniaque</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Ogre démoniaque</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1007</v>
-      </c>
-      <c r="E13" t="n">
-        <v>115</v>
-      </c>
-      <c r="F13" t="n">
-        <v>26</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="D20" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>450</v>
-      </c>
-      <c r="M13" t="n">
-        <v>216</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="O13" s="9">
-        <f>ROUND((E13*(1+(H13/100)*MAX(0,I13-100)/100)*(1+G13/100))*((D13+F13*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J13/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O20" s="9">
+        <f>ROUND((E20*(1+(H20/100)*MAX(0,I20-100)/100)*(1+G20/100))*((D20+F20*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J20/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P13" s="9">
-        <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P20" s="9">
+        <f>IFERROR(VLOOKUP(O20,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>croc_d_ogre ×1-2 (20%)
 plaque_rouillee ×1-1 (5%)
 espadon_dentele ×1-1 (1%)</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>ogre_demoniaque.png</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>Masse de muscles corrompue qui écrase tout sur son passage.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cerbere</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cerbère</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>1386</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="G14" s="5" t="n">
+      <c r="D21" t="n">
+        <v>924</v>
+      </c>
+      <c r="E21" t="n">
+        <v>123</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G21" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="n">
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>100</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="N14" s="5" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>438</v>
+      </c>
+      <c r="M21" t="n">
+        <v>210</v>
+      </c>
+      <c r="N21" t="n">
         <v>15</v>
       </c>
-      <c r="O14" s="9">
-        <f>ROUND((E14*(1+(H14/100)*MAX(0,I14-100)/100)*(1+G14/100))*((D14+F14*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J14/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O21" s="9">
+        <f>ROUND((E21*(1+(H21/100)*MAX(0,I21-100)/100)*(1+G21/100))*((D21+F21*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J21/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P14" s="9">
-        <f>IFERROR(VLOOKUP(O14,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P21" s="9">
+        <f>IFERROR(VLOOKUP(O21,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>croc_triple ×1-2 (12%)
 collier_a_pointes ×1-1 (5%)
 chaine_de_l_abime ×1-1 (3%)</t>
         </is>
       </c>
-      <c r="R14" s="5" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>cerbere.png</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Molosse à trois têtes gardant les portes de l'abîme.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>succube</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Succube</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1211</v>
-      </c>
-      <c r="E15" t="n">
-        <v>137</v>
-      </c>
-      <c r="F15" t="n">
-        <v>31</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="D22" s="5" t="n">
+        <v>810</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>550</v>
-      </c>
-      <c r="M15" t="n">
-        <v>264</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="N22" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="O15" s="9">
-        <f>ROUND((E15*(1+(H15/100)*MAX(0,I15-100)/100)*(1+G15/100))*((D15+F15*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J15/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O22" s="9">
+        <f>ROUND((E22*(1+(H22/100)*MAX(0,I22-100)/100)*(1+G22/100))*((D22+F22*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J22/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P15" s="9">
-        <f>IFERROR(VLOOKUP(O15,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P22" s="9">
+        <f>IFERROR(VLOOKUP(O22,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>philtre_de_charme ×1-1 (10%)
 aile_de_cuir ×1-1 (5%)
 corset_de_soie_noire ×1-1 (2%)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>succube.png</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>Démone envoûtante qui draine la vie de ses proies.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>ange_dechu</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Ange déchu</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>1641</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="G16" s="5" t="n">
+      <c r="D23" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E23" t="n">
+        <v>150</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45</v>
+      </c>
+      <c r="G23" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>100</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>288</v>
-      </c>
-      <c r="N16" s="5" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>544</v>
+      </c>
+      <c r="M23" t="n">
+        <v>261</v>
+      </c>
+      <c r="N23" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="9">
-        <f>ROUND((E16*(1+(H16/100)*MAX(0,I16-100)/100)*(1+G16/100))*((D16+F16*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J16/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O23" s="9">
+        <f>ROUND((E23*(1+(H23/100)*MAX(0,I23-100)/100)*(1+G23/100))*((D23+F23*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J23/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P16" s="9">
-        <f>IFERROR(VLOOKUP(O16,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P23" s="9">
+        <f>IFERROR(VLOOKUP(O23,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>plume_noircie ×1-2 (15%)
 flamme_sacree ×1-1 (5%)
 couronne_dechue ×1-1 (1%)</t>
         </is>
       </c>
-      <c r="R16" s="5" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>ange_dechu.png</t>
         </is>
       </c>
-      <c r="S16" s="5" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Ancien séraphin banni ; sa lumière s'est muée en fureur.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>archidemon</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Archidémon</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>demoniaque</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>2749</v>
-      </c>
-      <c r="E17" t="n">
-        <v>66</v>
-      </c>
-      <c r="F17" t="n">
-        <v>117</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="D24" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>675</v>
-      </c>
-      <c r="M17" t="n">
-        <v>324</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>606</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="N24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O17" s="9">
-        <f>ROUND((E17*(1+(H17/100)*MAX(0,I17-100)/100)*(1+G17/100))*((D17+F17*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J17/100))/'⚙️ Calibrage'!$B$10,0)</f>
+      <c r="O24" s="9">
+        <f>ROUND((E24*(1+(H24/100)*MAX(0,I24-100)/100)*(1+G24/100))*((D24+F24*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J24/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P17" s="9">
-        <f>IFERROR(VLOOKUP(O17,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+      <c r="P24" s="9">
+        <f>IFERROR(VLOOKUP(O24,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>corne_d_archidemon ×1-1 (12%)
 sceau_de_corruption ×1-1 (2%)
 lame_des_enfers ×1-1 (1%)</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>archidemon.png</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>Seigneur des enfers, apogée de la corruption du Berceau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>squelette</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Squelette</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>714</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>237</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="O18" s="9">
-        <f>ROUND((E18*(1+(H18/100)*MAX(0,I18-100)/100)*(1+G18/100))*((D18+F18*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J18/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P18" s="9">
-        <f>IFERROR(VLOOKUP(O18,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>os_poli ×1-2 (22%)
-poussiere_d_ossements ×1-2 (18%)
-dague_rouillee ×1-1 (5%)</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>squelette.png</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>Un pantin d'os réanimé. Le premier pas dans le royaume des morts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>zombie</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Zombie</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1209</v>
-      </c>
-      <c r="E19" t="n">
-        <v>30</v>
-      </c>
-      <c r="F19" t="n">
-        <v>51</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>100</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>273</v>
-      </c>
-      <c r="M19" t="n">
-        <v>131</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20</v>
-      </c>
-      <c r="O19" s="9">
-        <f>ROUND((E19*(1+(H19/100)*MAX(0,I19-100)/100)*(1+G19/100))*((D19+F19*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J19/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="9">
-        <f>IFERROR(VLOOKUP(O19,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>chair_putride ×1-2 (22%)
-lambeau_de_vetement ×1-2 (18%)
-dent_gatee ×1-1 (12%)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>zombie.png</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Une carcasse putride et lente, mais coriace.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>fantome</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Fantôme</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>668</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>393</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="O20" s="9">
-        <f>ROUND((E20*(1+(H20/100)*MAX(0,I20-100)/100)*(1+G20/100))*((D20+F20*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J20/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="9">
-        <f>IFERROR(VLOOKUP(O20,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>voile_ectoplasmique ×1-1 (4%)
-chaine_spectrale ×1-1 (4%)
-boulet_hante ×1-1 (2%)</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>fantome.png</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>Une âme errante insaisissable qui glisse entre les coups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>momie</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Momie</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1691</v>
-      </c>
-      <c r="E21" t="n">
-        <v>42</v>
-      </c>
-      <c r="F21" t="n">
-        <v>72</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>100</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>399</v>
-      </c>
-      <c r="M21" t="n">
-        <v>191</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" s="9">
-        <f>ROUND((E21*(1+(H21/100)*MAX(0,I21-100)/100)*(1+G21/100))*((D21+F21*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J21/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="9">
-        <f>IFERROR(VLOOKUP(O21,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>bandelette_maudite ×1-2 (22%)
-resine_d_embaumement ×1-1 (10%)
-griffe_noircie ×1-1 (5%)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>momie.png</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Un corps embaumé aux bandelettes maudites, quasi increvable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>gargouille</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Gargouille</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>456</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" s="9">
-        <f>ROUND((E22*(1+(H22/100)*MAX(0,I22-100)/100)*(1+G22/100))*((D22+F22*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J22/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="9">
-        <f>IFERROR(VLOOKUP(O22,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre ×1-2 (22%)
-aile_de_pierre ×1-1 (4%)
-coeur_de_granit ×1-1 (3%)</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>gargouille.png</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>Une statue de pierre animée qui frappe comme un bélier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>liche_maudite</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Liche maudite</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1193</v>
-      </c>
-      <c r="E23" t="n">
-        <v>135</v>
-      </c>
-      <c r="F23" t="n">
-        <v>30</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>100</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>541</v>
-      </c>
-      <c r="M23" t="n">
-        <v>260</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" s="9">
-        <f>ROUND((E23*(1+(H23/100)*MAX(0,I23-100)/100)*(1+G23/100))*((D23+F23*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J23/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P23" s="9">
-        <f>IFERROR(VLOOKUP(O23,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>grimoire_en_lambeaux ×1-1 (5%)
-orbe_maudit ×1-1 (2%)
-couronne_ternie ×1-1 (1%)</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>liche_maudite.png</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>banshee</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Banshee</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>mort-vivant</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>733</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" s="9">
-        <f>ROUND((E24*(1+(H24/100)*MAX(0,I24-100)/100)*(1+G24/100))*((D24+F24*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J24/100))/'⚙️ Calibrage'!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="P24" s="9">
-        <f>IFERROR(VLOOKUP(O24,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
-        <v/>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>echo_de_cri ×1-1 (18%)
-larme_spectrale ×1-1 (5%)
-couronne_d_epines ×1-1 (2%)</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>banshee.png</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>Un spectre hurlant dont le cri glaçant transperce l'âme.</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -14,12 +14,11 @@
     <sheet name="📦 Ressources" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="🛠️ Recettes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="🏪 Shop" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="🧬 Classes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="🌳 Skill Tree" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="🏷️ Titres" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="🌸 Panoplies" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="🐉 World Bosses" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="⚙️ Calibrage" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="🌳 Skill Tree" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="🏷️ Titres" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="🌸 Panoplies" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="🐉 World Bosses" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="⚙️ Calibrage" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$73</definedName>
@@ -28,11 +27,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🧬 Classes'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🌳 Skill Tree'!$A$1:$I$149</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🏷️ Titres'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -518,7 +516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-11 13:40 UTC</t>
+          <t>Généré le 2026-10-11 18:19 UTC</t>
         </is>
       </c>
     </row>
@@ -597,129 +595,117 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>🧬 Classes</t>
+          <t>🌳 Skill Tree</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Classes joueur + bonus + déblocage.</t>
+          <t>Tous les nœuds de l'arbre.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>🌳 Skill Tree</t>
+          <t>🏷️ Titres</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tous les nœuds de l'arbre.</t>
+          <t>Titres, conditions et effets.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>🏷️ Titres</t>
+          <t>🌸 Panoplies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Titres, conditions et effets.</t>
+          <t>Familles de set + paliers de bonus.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>🌸 Panoplies</t>
+          <t>🐉 World Bosses</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Familles de set + paliers de bonus.</t>
+          <t>Bosses + modifiers.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>🐉 World Bosses</t>
+          <t>⚙️ Calibrage</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bosses + modifiers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>⚙️ Calibrage</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>Constantes du score de puissance. NE PAS supprimer.</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>🛠️ Comment équilibrer (round-trip)</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>🛠️ Comment équilibrer (round-trip)</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
+          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
+          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
+          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
+          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
-        <is>
-          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
         <is>
           <t>Power d'un équipement = puissance MARGINALE qu'il ajoute à un perso de base (power(base+item) − power(base)).</t>
         </is>
@@ -731,1044 +717,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Icône</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Exclusif</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Cible / Valeur</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Effets</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>slime_slayer</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Slime Slayer</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>kills_family</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>slime / 100</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>damage_bonus_vs_family → target=slime, value=10
-damage_reduction_from_family → target=slime, value=10</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Tueur de slimes confirmé. +10% dégâts infligés et -10% dégâts subis face aux slimes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gobelin_slayer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gobelin Slayer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>👹</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>kills_family</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>gobelin / 100</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>damage_bonus_vs_family → target=gobelin, value=10
-damage_reduction_from_family → target=gobelin, value=10</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Bourreau des gobelins. +10% dégâts infligés et -10% dégâts subis face aux gobelins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>champion_1v1</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Champion en 1vs1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>👑</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>duel_top1</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>champion_all_stats → value=1</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Détenteur du sommet du ladder 1v1. +1% sur toutes vos stats (multiplicatif sur PV/atk/def, additif sur crit/esquive, +1 flat sur vitesse/régen). Perdu dès qu'un autre joueur prend la première place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>farmer_fou</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Le Farmer Fou</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🌾</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>kills_record</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>gold_xp_bonus_pct → value=1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>bourreau</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Le Bourreau</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>🩸</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>kills_total</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=5</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Tueur impitoyable de 500 monstres au total. +5% sur les dégâts critiques (additif sur crit_damage).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>intouchable</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>L'Intouchable</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🌪️</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>dodges_total</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>dodge_flat → value=1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Esquiveur aguerri (100 esquives encaissées en combat de groupe). +1% d'esquive permanent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>taverne_addict</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Taverne Addict</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>🍺</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>daily_streak</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>daily_bonus_item → target=potion_soin, value=1</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin I à chaque /daily (en plus de l'or).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>slime_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Slime</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>slime / 50</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>gobelin / 50</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gobelin_combattant_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Combattant</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>gobelin_combattant / 50</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_chaman_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Chaman</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_chaman / 50</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>gobelin_geant_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Géant</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>gobelin_geant / 50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_runique_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Runique</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_runique / 50</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>gobelin_ballon_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Ballon</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>gobelin_ballon / 50</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_assassin_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Assassin</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_assassin / 50</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>gobelin_superieur_chasseur_legendaire</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Chasseur Légendaire — Gobelin Supérieur</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>🏹</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>kills_mob</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>gobelin_superieur / 50</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>mvp_world_boss</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>MVP des World Boss</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>🏆</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>world_boss_mvp</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>champion_all_stats → value=2</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tueur_slime_titan</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Tueur du Titan Visqueux</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>⚔️</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>world_boss_kill</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>slime_titan / 1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>tueur_gobelin_warlord</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Tueur du Seigneur de Guerre Gobelin</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>⚔️</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>world_boss_kill</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>gobelin_warlord / 1</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>tueur_stone_colossus</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tueur du Colosse de Pierre</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>⚔️</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>world_boss_kill</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stone_colossus / 1</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>tueur_shadow_wraith</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Tueur du Spectre des Ténèbres</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>⚔️</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>world_boss_kill</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>shadow_wraith / 1</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>tueur_ancient_dragon</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Tueur du Dragon Ancestral</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>⚔️</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>world_boss_kill</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ancient_dragon / 1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>ma_survie_avant_tout</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Ma survie avant tout</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>dodge_flat → value=1
-speed_flat → value=1
-defense_flat → value=10
-hp_max_flat → value=200</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>A ignoré une « petite fille » qui s'est révélée être un monstre déguisé — l'instinct de survie récompensé. Esquive +1%, Vitesse +1, Défense +10, PV max +200.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H24"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1841,7 +789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2184,7 +1132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12476,21 +11424,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -12506,196 +11451,42 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Atk</t>
+          <t>Niveau max</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>Coûts/niveau</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>Effets</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crit %</t>
+          <t>Prérequis</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Crit dmg</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Esquive</t>
+          <t>Icône</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Vitesse</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Regen</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Déblocage</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Guerrier</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>{"type": "has_item", "item_code": "gobelin_tooth", "quantity": 5}</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Une classe robuste spécialisée dans le combat rapproché.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rogue</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Voleur</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>{"type": "has_item", "item_code": "slime_gel", "quantity": 5}</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Une classe rapide et offensive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Gardien</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>{"type": "has_item", "item_code": "gobelin_tooth", "quantity": 10}
-{"type": "has_item", "item_code": "slime_gel", "quantity": 3}</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Une classe défensive et résistante.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12706,18 +11497,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -12733,35 +11523,30 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niveau max</t>
+          <t>Icône</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Coûts/niveau</t>
+          <t>Exclusif</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Cible / Valeur</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Effets</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Prérequis</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
       <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Icône</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -12770,6665 +11555,976 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>aventurier</t>
+          <t>slime_slayer</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Aventurier</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>1</v>
+          <t>Slime Slayer</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>racine</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>0, 0</t>
+          <t>slime / 100</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=slime, value=10
+damage_reduction_from_family → target=slime, value=10</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Le commencement de votre voyage. Les trois voies partent d'ici.</t>
+          <t>Tueur de slimes confirmé. +10% dégâts infligés et -10% dégâts subis face aux slimes.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>voie_atq</t>
+          <t>gobelin_slayer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Voie de l'Attaque</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+          <t>Gobelin Slayer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>aventurier</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0, -150</t>
+          <t>gobelin / 100</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=gobelin, value=10
+damage_reduction_from_family → target=gobelin, value=10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Entrée de la voie de l'attaque.</t>
+          <t>Bourreau des gobelins. +10% dégâts infligés et -10% dégâts subis face aux gobelins.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>atq_1</t>
+          <t>champion_1v1</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Force 1</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>3</v>
+          <t>Champion en 1vs1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [5,10,15]</t>
+          <t>duel_top1</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>voie_atq</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>-147, -172</t>
+          <t>champion_all_stats → value=1</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>+5 Attaque par niveau · max +15 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Détenteur du sommet du ladder 1v1. +1% sur toutes vos stats (multiplicatif sur PV/atk/def, additif sur crit/esquive, +1 flat sur vitesse/régen). Perdu dès qu'un autre joueur prend la première place.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>atq_2</t>
+          <t>farmer_fou</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Force 1</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
+          <t>Le Farmer Fou</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🌾</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>atk_flat → [5,10,15]</t>
+          <t>kills_record</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>atq_1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-290, -214</t>
+          <t>gold_xp_bonus_pct → value=1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>+5 Attaque par niveau · max +15 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>atq_3</t>
+          <t>bourreau</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Force 1</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>3</v>
+          <t>Le Bourreau</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [5,10,15]</t>
+          <t>kills_total</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>atq_2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>-425, -278</t>
+          <t>crit_damage_flat → value=5</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>+5 Attaque par niveau · max +15 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Tueur impitoyable de 500 monstres au total. +5% sur les dégâts critiques (additif sur crit_damage).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>atq_4</t>
+          <t>intouchable</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Force 1</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
+          <t>L'Intouchable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🌪️</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>atk_flat → [5,10,15]</t>
+          <t>dodges_total</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>atq_3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-549, -361</t>
+          <t>dodge_flat → value=1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>+5 Attaque par niveau · max +15 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Esquiveur aguerri (100 esquives encaissées en combat de groupe). +1% d'esquive permanent.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>atq_5</t>
+          <t>taverne_addict</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Force 1</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>3</v>
+          <t>Taverne Addict</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>🍺</t>
+        </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [5,10,15]</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>atq_4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>-658, -461</t>
+          <t>daily_bonus_item → target=potion_soin, value=1</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>+5 Attaque par niveau · max +15 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin I à chaque /daily (en plus de l'or).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>atq_6</t>
+          <t>slime_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frappe affûtée</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>Chasseur Légendaire — Slime</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>atk_percent → [1]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>atq_5</t>
+          <t>slime / 50</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-752, -577</t>
+          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>💥</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% Attaque (1 amélioration, 3 pts).</t>
+          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>atq_7</t>
+          <t>gobelin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Force 2</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [6,12,18]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>atq_6</t>
+          <t>gobelin / 50</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>-826, -706</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>+6 Attaque par niveau · max +18 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>atq_8</t>
+          <t>gobelin_combattant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Force 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Combattant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>atk_flat → [6,12,18]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>atq_7</t>
+          <t>gobelin_combattant / 50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-879, -846</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>+6 Attaque par niveau · max +18 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>atq_9</t>
+          <t>gobelin_chaman_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Force 2</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Chaman</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [6,12,18]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>atq_8</t>
+          <t>gobelin_chaman / 50</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>-909, -991</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>+6 Attaque par niveau · max +18 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>atq_10</t>
+          <t>gobelin_geant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Force 2</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Géant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>atk_flat → [6,12,18]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>atq_9</t>
+          <t>gobelin_geant / 50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-915, -1140</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>+6 Attaque par niveau · max +18 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>atq_11</t>
+          <t>gobelin_runique_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Force 2</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Runique</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [6,12,18]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>atq_10</t>
+          <t>gobelin_runique / 50</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>-898, -1288</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>+6 Attaque par niveau · max +18 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>atq_12</t>
+          <t>gobelin_ballon_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Œil vif</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
+          <t>Chasseur Légendaire — Gobelin Ballon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>crit_chance_flat → [1]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>atq_11</t>
+          <t>gobelin_ballon / 50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-856, -1431</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🎯</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% de chance de critique (1 amélioration, 3 pts).</t>
+          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>atq_13</t>
+          <t>gobelin_assassin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Force 3</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Assassin</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [7,14,21]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>atq_12</t>
+          <t>gobelin_assassin / 50</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>-791, -1565</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>+7 Attaque par niveau · max +21 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>atq_14</t>
+          <t>gobelin_superieur_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Force 3</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
+          <t>Chasseur Légendaire — Gobelin Supérieur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>atk_flat → [7,14,21]</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>atq_13</t>
+          <t>gobelin_superieur / 50</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-704, -1686</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>+7 Attaque par niveau · max +21 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>atq_15</t>
+          <t>mvp_world_boss</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Force 3</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>3</v>
+          <t>MVP des World Boss</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [7,14,21]</t>
+          <t>world_boss_mvp</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>atq_14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>-598, -1790</t>
+          <t>champion_all_stats → value=2</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>+7 Attaque par niveau · max +21 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>atq_16</t>
+          <t>tueur_slime_titan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Force 3</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
+          <t>Tueur du Titan Visqueux</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>atk_flat → [7,14,21]</t>
+          <t>world_boss_kill</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>atq_15</t>
+          <t>slime_titan / 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-475, -1874</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+7 Attaque par niveau · max +21 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>atq_17</t>
+          <t>tueur_gobelin_warlord</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Force 3</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>3</v>
+          <t>Tueur du Seigneur de Guerre Gobelin</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [7,14,21]</t>
+          <t>world_boss_kill</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>atq_16</t>
+          <t>gobelin_warlord / 1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>-339, -1935</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>+7 Attaque par niveau · max +21 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>atq_18</t>
+          <t>tueur_stone_colossus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Célérité</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
+          <t>Tueur du Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>world_boss_kill</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>atq_17</t>
+          <t>stone_colossus / 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-195, -1971</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>💨</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Vitesse (1 amélioration, 3 pts).</t>
+          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>atq_19</t>
+          <t>tueur_shadow_wraith</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Force 4</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>3</v>
+          <t>Tueur du Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [8,16,24]</t>
+          <t>world_boss_kill</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>atq_18</t>
+          <t>shadow_wraith / 1</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>-46, -1979</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>+8 Attaque par niveau · max +24 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>atq_20</t>
+          <t>tueur_ancient_dragon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Force 4</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3</v>
+          <t>Tueur du Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>atk_flat → [8,16,24]</t>
+          <t>world_boss_kill</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>atq_19</t>
+          <t>ancient_dragon / 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>102, -1960</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>+8 Attaque par niveau · max +24 Attaque (3 niveaux, 1 pt/niveau).</t>
+          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>atq_21</t>
+          <t>ma_survie_avant_tout</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Force 4</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>3</v>
+          <t>Ma survie avant tout</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1,1,1</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>atk_flat → [8,16,24]</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>atq_20</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>243, -1913</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>dodge_flat → value=1
+speed_flat → value=1
+defense_flat → value=10
+hp_max_flat → value=200</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>+8 Attaque par niveau · max +24 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>atq_22</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Force 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>atk_flat → [8,16,24]</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>atq_21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>373, -1840</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>+8 Attaque par niveau · max +24 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>atq_23</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Force 4</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [8,16,24]</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>atq_22</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>485, -1743</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>+8 Attaque par niveau · max +24 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>atq_24</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Coup dévastateur</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → [5]</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>atq_23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>576, -1625</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +5% de dégâts critiques (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>atq_25</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Force 5</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>atq_24</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>641, -1492</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>+9 Attaque par niveau · max +27 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>atq_26</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Force 5</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>atk_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>atq_25</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>677, -1347</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>+9 Attaque par niveau · max +27 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>atq_27</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Force 5</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>atq_26</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>681, -1198</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>+9 Attaque par niveau · max +27 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>atq_28</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Force 5</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>atk_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>atq_27</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>653, -1052</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>+9 Attaque par niveau · max +27 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>atq_29</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Force 5</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>atq_28</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>592, -917</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>+9 Attaque par niveau · max +27 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>atq_30</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Frappe affûtée</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>atk_percent → [1]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>atq_29</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>502, -798</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>💥</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% Attaque (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>atq_31</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Force 6</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>atq_30</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>387, -704</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>+10 Attaque par niveau · max +30 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>atq_32</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Force 6</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>atk_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>atq_31</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>252, -641</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>+10 Attaque par niveau · max +30 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>atq_33</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Force 6</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>atq_32</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>106, -614</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>+10 Attaque par niveau · max +30 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>atq_34</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Force 6</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>atk_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>atq_33</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-42, -625</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>+10 Attaque par niveau · max +30 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>atq_35</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Force 6</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>atq_34</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>-182, -675</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>+10 Attaque par niveau · max +30 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>atq_36</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Œil vif</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>crit_chance_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>atq_35</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-302, -762</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>🎯</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% de chance de critique (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>atq_37</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Force 7</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>atq_36</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>-393, -880</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>+11 Attaque par niveau · max +33 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>atq_38</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Force 7</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>atk_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>atq_37</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-443, -1019</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>+11 Attaque par niveau · max +33 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>atq_39</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Force 7</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>atq_38</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>-448, -1168</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>+11 Attaque par niveau · max +33 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>atq_40</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Force 7</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>atk_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>atq_39</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-402, -1309</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>+11 Attaque par niveau · max +33 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>atq_41</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Force 7</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>atq_40</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>-311, -1425</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>+11 Attaque par niveau · max +33 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>atq_42</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Célérité</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>speed_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>atq_41</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-182, -1499</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>💨</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Vitesse (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>atq_43</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Force 8</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>atq_42</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>-35, -1515</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>+12 Attaque par niveau · max +36 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>atq_44</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Force 8</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>atk_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>atq_43</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>104, -1464</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>+12 Attaque par niveau · max +36 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>atq_45</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Force 8</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>atq_44</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>200, -1353</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>+12 Attaque par niveau · max +36 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>atq_46</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Force 8</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>atk_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>atq_45</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>220, -1208</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>+12 Attaque par niveau · max +36 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>atq_47</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Force 8</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>atk_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>atq_46</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>140, -1087</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>💪</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>+12 Attaque par niveau · max +36 Attaque (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>atq_48</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Coup dévastateur</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → [5]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>atq_47</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0, -1085</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +5% de dégâts critiques (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>voie_def</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Voie de la Défense</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>aventurier</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>130, 75</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Entrée de la voie de la défense.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>def_1</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Armure 1</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>def_flat → [5,10,15]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>voie_def</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>222, -42</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>+5 Défense par niveau · max +15 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>def_2</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 1</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [100,200,300]</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>def_1</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>331, -144</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>+100 PV max par niveau · max +300 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>def_3</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Armure 1</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>3</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>def_flat → [5,10,15]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>def_2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>453, -229</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>+5 Défense par niveau · max +15 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>def_4</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 1</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [100,200,300]</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>def_3</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>586, -295</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>+100 PV max par niveau · max +300 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>def_5</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Armure 1</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>3</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>def_flat → [5,10,15]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>def_4</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>728, -340</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>+5 Défense par niveau · max +15 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>def_6</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Peau de pierre</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>def_percent → [1]</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>def_5</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>876, -362</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>🪨</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% Défense (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>def_7</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Vitalité 2</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [120,240,360]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>def_6</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1025, -362</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>+120 PV max par niveau · max +360 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>def_8</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Armure 2</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [6,12,18]</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>def_7</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>1172, -338</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>+6 Défense par niveau · max +18 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>def_9</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Vitalité 2</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [120,240,360]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>def_8</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>1313, -292</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>+120 PV max par niveau · max +360 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>def_10</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Armure 2</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [6,12,18]</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>def_9</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>1445, -223</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>+6 Défense par niveau · max +18 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>def_11</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Vitalité 2</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [120,240,360]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>def_10</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1564, -134</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>+120 PV max par niveau · max +360 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>def_12</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Endurance</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_percent → [1]</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>def_11</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>1667, -26</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>💗</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% PV max (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>def_13</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Armure 3</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>3</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>def_flat → [7,14,21]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>def_12</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1750, 97</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>+7 Défense par niveau · max +21 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>def_14</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 3</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [140,280,420]</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>def_13</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>1812, 233</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>+140 PV max par niveau · max +420 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>def_15</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Armure 3</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>def_flat → [7,14,21]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>def_14</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>1849, 377</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>+7 Défense par niveau · max +21 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>def_16</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 3</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [140,280,420]</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>def_15</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>1860, 526</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>+140 PV max par niveau · max +420 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>def_17</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Armure 3</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>def_flat → [7,14,21]</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>def_16</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1845, 674</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>+7 Défense par niveau · max +21 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>def_18</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Esquive</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>dodge_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>def_17</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>1804, 817</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>🌀</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% d'esquive (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>def_19</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Vitalité 4</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [160,320,480]</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>def_18</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>1737, 950</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>+160 PV max par niveau · max +480 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>def_20</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Armure 4</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [8,16,24]</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>def_19</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>1647, 1068</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>+8 Défense par niveau · max +24 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>def_21</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Vitalité 4</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [160,320,480]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>def_20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>1536, 1167</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>+160 PV max par niveau · max +480 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>def_22</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Armure 4</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [8,16,24]</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>def_21</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>1407, 1243</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>+8 Défense par niveau · max +24 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>def_23</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Vitalité 4</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [160,320,480]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>def_22</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>1267, 1292</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>+160 PV max par niveau · max +480 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>def_24</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Régénération</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>hp_regeneration_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>def_23</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>1119, 1312</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>💚</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Régénération de PV (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>def_25</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Armure 5</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>3</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>def_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>def_24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>971, 1301</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>+9 Défense par niveau · max +27 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>def_26</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 5</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [180,360,540]</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>def_25</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>828, 1260</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>+180 PV max par niveau · max +540 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>def_27</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Armure 5</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>def_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>def_26</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>697, 1189</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>+9 Défense par niveau · max +27 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>def_28</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 5</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [180,360,540]</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>def_27</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>585, 1091</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>+180 PV max par niveau · max +540 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>def_29</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Armure 5</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>3</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>def_flat → [9,18,27]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>def_28</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>498, 971</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>+9 Défense par niveau · max +27 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>def_30</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Peau de pierre</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>def_percent → [1]</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>def_29</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>440, 834</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>🪨</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% Défense (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>def_31</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Vitalité 6</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>3</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [200,400,600]</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>def_30</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>416, 687</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>+200 PV max par niveau · max +600 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>def_32</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>Armure 6</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>def_31</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>429, 539</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>+10 Défense par niveau · max +30 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>def_33</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Vitalité 6</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [200,400,600]</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>def_32</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>478, 399</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>+200 PV max par niveau · max +600 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>def_34</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>Armure 6</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [10,20,30]</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>def_33</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>562, 276</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>+10 Défense par niveau · max +30 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>def_35</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Vitalité 6</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [200,400,600]</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>def_34</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>675, 180</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>+200 PV max par niveau · max +600 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>def_36</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>Endurance</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_percent → [1]</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>def_35</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>811, 119</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>💗</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% PV max (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>def_37</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Armure 7</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>def_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>def_36</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>958, 100</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>+11 Défense par niveau · max +33 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>def_38</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 7</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [220,440,660]</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>def_37</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>1104, 126</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>+220 PV max par niveau · max +660 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>def_39</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Armure 7</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>3</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>def_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>def_38</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>1235, 196</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>+11 Défense par niveau · max +33 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>def_40</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Vitalité 7</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [220,440,660]</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>def_39</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>1335, 306</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>+220 PV max par niveau · max +660 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>def_41</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Armure 7</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>def_flat → [11,22,33]</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>def_40</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>1390, 444</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>+11 Défense par niveau · max +33 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>def_42</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>Esquive</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>dodge_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>def_41</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>1389, 592</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>🌀</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1% d'esquive (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>def_43</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Vitalité 8</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [240,480,720]</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>def_42</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>1329, 727</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>+240 PV max par niveau · max +720 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>def_44</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>Armure 8</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>def_43</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>1216, 822</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>+12 Défense par niveau · max +36 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>def_45</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Vitalité 8</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>3</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [240,480,720]</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>def_44</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>1072, 850</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>+240 PV max par niveau · max +720 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>def_46</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>Armure 8</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>def_flat → [12,24,36]</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>def_45</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>937, 794</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>+12 Défense par niveau · max +36 Défense (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>def_47</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Vitalité 8</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>3</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>hp_max_flat → [240,480,720]</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>def_46</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>871, 665</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>❤️</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>+240 PV max par niveau · max +720 PV max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>def_48</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>Régénération</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>hp_regeneration_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>def_47</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>940, 542</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t>💚</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Régénération de PV (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>voie_uti</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Voie Utilitaire</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>aventurier</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-130, 75</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>🎒</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Entrée de la voie utilitaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>uti_1</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 1</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>voie_uti</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>-75, 213</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>uti_2</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Chance 1</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>3</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>uti_1</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-41, 358</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>uti_3</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 1</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [20,40,60]</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>uti_2</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>-28, 507</t>
-        </is>
-      </c>
-      <c r="H104" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>+20 Mana max par niveau · max +60 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>uti_4</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Bourse 1</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>3</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>uti_3</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-38, 655</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>uti_5</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 1</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>uti_4</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>-70, 801</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>uti_6</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Fortune</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [2]</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>uti_5</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-124, 939</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% d'or gagné (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>uti_7</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>Chance 2</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>uti_6</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>-199, 1068</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>uti_8</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 2</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>3</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [25,50,75]</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>uti_7</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-293, 1184</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>+25 Mana max par niveau · max +75 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>uti_9</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 2</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>uti_8</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>-404, 1283</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>uti_10</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Sagesse 2</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>3</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>uti_9</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-530, 1363</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>uti_11</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>Chance 2</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>uti_10</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>-666, 1421</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>uti_12</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Érudition</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>1</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [2]</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>uti_11</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-811, 1457</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% d'XP gagnée (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>uti_13</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 3</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [30,60,90]</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>uti_12</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>-960, 1467</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>+30 Mana max par niveau · max +90 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>uti_14</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Bourse 3</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>3</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>uti_13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-1108, 1453</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>uti_15</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 3</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>uti_14</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>-1251, 1413</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>uti_16</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Chance 3</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>3</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>uti_15</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-1385, 1348</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>uti_17</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 3</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [30,60,90]</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>uti_16</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>-1506, 1261</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>+30 Mana max par niveau · max +90 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>uti_18</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Pillage</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [2]</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>uti_17</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-1609, 1154</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% de chance de butin (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>uti_19</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 4</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>uti_18</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>-1691, 1029</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>uti_20</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Sagesse 4</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>3</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>uti_19</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-1748, 892</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>uti_21</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>Chance 4</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>uti_20</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>-1778, 746</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>uti_22</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 4</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>3</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [35,70,105]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>uti_21</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-1780, 597</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>+35 Mana max par niveau · max +105 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>uti_23</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 4</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>uti_22</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>-1752, 451</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>uti_24</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Flux de mana</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>mana_regeneration_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>uti_23</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-1696, 314</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>🌊</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Régénération de mana (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>uti_25</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 5</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>uti_24</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>-1612, 190</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>uti_26</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Chance 5</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>3</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>uti_25</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-1505, 87</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>uti_27</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 5</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [40,80,120]</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>uti_26</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>-1378, 9</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>+40 Mana max par niveau · max +120 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>uti_28</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Bourse 5</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>3</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>uti_27</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-1238, -39</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>uti_29</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 5</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>uti_28</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>-1090, -55</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>uti_30</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Fortune</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [2]</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>uti_29</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-942, -36</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% d'or gagné (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>uti_31</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>Chance 6</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>uti_30</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>-803, 17</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>uti_32</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 6</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>3</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [45,90,135]</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>uti_31</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-681, 102</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>+45 Mana max par niveau · max +135 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>uti_33</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 6</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>uti_32</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>-585, 215</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>uti_34</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Sagesse 6</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>3</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>uti_33</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-520, 349</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>uti_35</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>Chance 6</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>uti_34</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>-494, 495</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>uti_36</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Érudition</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [2]</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>uti_35</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-509, 643</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% d'XP gagnée (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>uti_37</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 7</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [50,100,150]</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>uti_36</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>-566, 780</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>+50 Mana max par niveau · max +150 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>uti_38</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Bourse 7</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>3</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>uti_37</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-661, 893</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>uti_39</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>Sagesse 7</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>uti_38</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>-787, 971</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>uti_40</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Chance 7</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>3</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>uti_39</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-932, 1003</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>uti_41</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 7</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [50,100,150]</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>uti_40</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>-1079, 982</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>+50 Mana max par niveau · max +150 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>uti_42</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Pillage</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [2]</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>uti_41</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-1207, 907</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +2% de chance de butin (1 amélioration, 3 pts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>uti_43</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 8</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>uti_42</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>-1294, 788</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>uti_44</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Sagesse 8</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>3</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>xp_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>uti_43</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-1320, 643</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>✨</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>+1% d'XP gagnée par niveau · max +3% d'XP gagnée (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>uti_45</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>Chance 8</t>
-        </is>
-      </c>
-      <c r="C146" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>drop_rate_multiplier → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>uti_44</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>-1272, 503</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>🎁</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>+1% de chance de butin par niveau · max +3% de chance de butin (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>uti_46</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Réserve d'énergie 8</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>3</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>mana_max_flat → [55,110,165]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>uti_45</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-1156, 414</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>+55 Mana max par niveau · max +165 Mana max (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>uti_47</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>Bourse 8</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
-        <is>
-          <t>1,1,1</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>gold_drop_percent → [1,2,3]</t>
-        </is>
-      </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>uti_46</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>-1011, 422</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
-        <is>
-          <t>+1% d'or gagné par niveau · max +3% d'or gagné (3 niveaux, 1 pt/niveau).</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>uti_48</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Flux de mana</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>mana_regeneration_flat → [1]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>uti_47</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-940, 542</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>🌊</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Nœud spécial : +1 Régénération de mana (1 amélioration, 3 pts).</t>
+          <t>A ignoré une « petite fille » qui s'est révélée être un monstre déguisé — l'instinct de survie récompensé. Esquive +1%, Vitesse +1, Défense +10, PV max +200.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I149"/>
+  <autoFilter ref="A1:H24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-11 18:19 UTC</t>
+          <t>Généré le 2026-10-11 18:28 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -21,13 +21,13 @@
     <sheet name="⚙️ Calibrage" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$U$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
@@ -38,9 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -112,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,14 +119,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -516,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-11 18:28 UTC</t>
+          <t>Généré le 2026-10-13 21:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1148,24 +1145,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>⚙️ Calibrage du score de puissance — NE PAS supprimer (formules liées)</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Score ≥</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Rang</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Base ATK</t>
         </is>
@@ -1183,7 +1180,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Base DEF</t>
         </is>
@@ -1201,7 +1198,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Base PV</t>
         </is>
@@ -1219,7 +1216,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Base Crit %</t>
         </is>
@@ -1237,7 +1234,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Base Crit dmg (100 = neutre)</t>
         </is>
@@ -1255,7 +1252,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Base Esquive %</t>
         </is>
@@ -1273,7 +1270,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Base Vitesse</t>
         </is>
@@ -1291,7 +1288,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>K_DEF (1 DEF = N PV effectifs)</t>
         </is>
@@ -1309,7 +1306,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>SCALE (diviseur)</t>
         </is>
@@ -1327,7 +1324,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Power base (auto)</t>
         </is>
@@ -1536,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1546,7 +1543,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -1554,11 +1551,12 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1599,65 +1597,70 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Atk</t>
+          <t>Niv. requis</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>Atk %</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>Def %</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>PV %</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Crit %</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Crit dmg</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Esquive</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Vitesse</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Regen</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Mana max</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Regen mana</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Prix achat</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1696,10 +1699,10 @@
         </is>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>0</v>
@@ -1714,23 +1717,27 @@
         <v>0</v>
       </c>
       <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H2)*(1+(('⚙️ Calibrage'!$B$5+K2)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L2)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N2)/100))*((('⚙️ Calibrage'!$B$4+J2)+('⚙️ Calibrage'!$B$3+I2)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M2)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="5" t="n"/>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>(D6)
 craft : boi ,drop du chaman
@@ -1772,16 +1779,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1790,22 +1797,27 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H3)*(1+(('⚙️ Calibrage'!$B$5+K3)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L3)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N3)/100))*((('⚙️ Calibrage'!$B$4+J3)+('⚙️ Calibrage'!$B$3+I3)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M3)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>80</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>(D1)</t>
         </is>
@@ -1844,16 +1856,16 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
@@ -1867,18 +1879,22 @@
       <c r="O4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H4)*(1+(('⚙️ Calibrage'!$B$5+K4)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L4)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N4)/100))*((('⚙️ Calibrage'!$B$4+J4)+('⚙️ Calibrage'!$B$3+I4)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M4)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="5" t="n"/>
-      <c r="S4" s="5" t="n">
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>(D2)</t>
         </is>
@@ -1917,16 +1933,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1935,22 +1951,27 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>-4</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H5)*(1+(('⚙️ Calibrage'!$B$5+K5)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L5)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N5)/100))*((('⚙️ Calibrage'!$B$4+J5)+('⚙️ Calibrage'!$B$3+I5)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M5)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1985,10 +2006,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
@@ -2008,18 +2029,22 @@
       <c r="O6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H6)*(1+(('⚙️ Calibrage'!$B$5+K6)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L6)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N6)/100))*((('⚙️ Calibrage'!$B$4+J6)+('⚙️ Calibrage'!$B$3+I6)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M6)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2054,40 +2079,45 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>45</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H7)*(1+(('⚙️ Calibrage'!$B$5+K7)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L7)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N7)/100))*((('⚙️ Calibrage'!$B$4+J7)+('⚙️ Calibrage'!$B$3+I7)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M7)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P7" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>1856</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Il bat encore. On l'entend quand le combat se tait.</t>
         </is>
@@ -2126,20 +2156,20 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" s="5" t="n">
         <v>0</v>
       </c>
@@ -2149,18 +2179,22 @@
       <c r="O8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H8)*(1+(('⚙️ Calibrage'!$B$5+K8)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L8)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N8)/100))*((('⚙️ Calibrage'!$B$4+J8)+('⚙️ Calibrage'!$B$3+I8)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M8)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2195,40 +2229,45 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H9)*(1+(('⚙️ Calibrage'!$B$5+K9)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L9)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N9)/100))*((('⚙️ Calibrage'!$B$4+J9)+('⚙️ Calibrage'!$B$3+I9)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M9)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P9" t="n">
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>80</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>(D3)</t>
         </is>
@@ -2267,10 +2306,10 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -2279,29 +2318,33 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H10)*(1+(('⚙️ Calibrage'!$B$5+K10)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L10)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N10)/100))*((('⚙️ Calibrage'!$B$4+J10)+('⚙️ Calibrage'!$B$3+I10)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M10)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>Une paire de dagues gobelines bien affutées.</t>
         </is>
@@ -2340,40 +2383,45 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>20</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H11)*(1+(('⚙️ Calibrage'!$B$5+K11)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L11)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N11)/100))*((('⚙️ Calibrage'!$B$4+J11)+('⚙️ Calibrage'!$B$3+I11)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M11)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P11" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2408,41 +2456,45 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H12)*(1+(('⚙️ Calibrage'!$B$5+K12)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L12)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N12)/100))*((('⚙️ Calibrage'!$B$4+J12)+('⚙️ Calibrage'!$B$3+I12)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M12)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>(D3)
 craft :fer ,boi ,griffe de goblin 
@@ -2483,10 +2535,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2501,22 +2553,27 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>-2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H13)*(1+(('⚙️ Calibrage'!$B$5+K13)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L13)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N13)/100))*((('⚙️ Calibrage'!$B$4+J13)+('⚙️ Calibrage'!$B$3+I13)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M13)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P13" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2551,20 +2608,20 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="5" t="n">
         <v>0</v>
       </c>
@@ -2574,18 +2631,22 @@
       <c r="O14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H14)*(1+(('⚙️ Calibrage'!$B$5+K14)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L14)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N14)/100))*((('⚙️ Calibrage'!$B$4+J14)+('⚙️ Calibrage'!$B$3+I14)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M14)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2620,40 +2681,45 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>6</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>25</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H15)*(1+(('⚙️ Calibrage'!$B$5+K15)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L15)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N15)/100))*((('⚙️ Calibrage'!$B$4+J15)+('⚙️ Calibrage'!$B$3+I15)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M15)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P15" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>1501</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2688,41 +2754,45 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H16)*(1+(('⚙️ Calibrage'!$B$5+K16)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L16)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N16)/100))*((('⚙️ Calibrage'!$B$4+J16)+('⚙️ Calibrage'!$B$3+I16)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M16)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>551</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>L'acier ébréché d'un chef gobelin qui n'a jamais reculé.</t>
         </is>
@@ -2761,10 +2831,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2773,28 +2843,33 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>12</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H17)*(1+(('⚙️ Calibrage'!$B$5+K17)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L17)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N17)/100))*((('⚙️ Calibrage'!$B$4+J17)+('⚙️ Calibrage'!$B$3+I17)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M17)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P17" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2829,10 +2904,10 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -2841,29 +2916,33 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
         <v>-3</v>
       </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H18)*(1+(('⚙️ Calibrage'!$B$5+K18)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L18)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N18)/100))*((('⚙️ Calibrage'!$B$4+J18)+('⚙️ Calibrage'!$B$3+I18)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M18)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>344</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2898,10 +2977,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2916,22 +2995,27 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H19)*(1+(('⚙️ Calibrage'!$B$5+K19)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L19)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N19)/100))*((('⚙️ Calibrage'!$B$4+J19)+('⚙️ Calibrage'!$B$3+I19)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M19)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P19" t="n">
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2966,10 +3050,10 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
@@ -2981,26 +3065,30 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H20)*(1+(('⚙️ Calibrage'!$B$5+K20)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L20)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N20)/100))*((('⚙️ Calibrage'!$B$4+J20)+('⚙️ Calibrage'!$B$3+I20)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M20)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
         <is>
           <t>(D8)
 (snipeur) ta première ataque inflige +5dégat
@@ -3042,13 +3130,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -3063,19 +3151,24 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>5</v>
       </c>
-      <c r="P21" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H21)*(1+(('⚙️ Calibrage'!$B$5+K21)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L21)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N21)/100))*((('⚙️ Calibrage'!$B$4+J21)+('⚙️ Calibrage'!$B$3+I21)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M21)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>(D2),(D4)
 quand un énémie l'ataque il perd 2pv
@@ -3117,10 +3210,10 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>0</v>
@@ -3140,18 +3233,22 @@
       <c r="O22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H22)*(1+(('⚙️ Calibrage'!$B$5+K22)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L22)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N22)/100))*((('⚙️ Calibrage'!$B$4+J22)+('⚙️ Calibrage'!$B$3+I22)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M22)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="T22" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3186,10 +3283,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3207,19 +3304,24 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H23)*(1+(('⚙️ Calibrage'!$B$5+K23)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L23)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N23)/100))*((('⚙️ Calibrage'!$B$4+J23)+('⚙️ Calibrage'!$B$3+I23)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M23)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>(D4)
 craft: fer ,bois ,gelé de slime ,griff de goblin
@@ -3260,22 +3362,22 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>10</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
@@ -3283,18 +3385,22 @@
       <c r="O24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H24)*(1+(('⚙️ Calibrage'!$B$5+K24)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L24)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N24)/100))*((('⚙️ Calibrage'!$B$4+J24)+('⚙️ Calibrage'!$B$3+I24)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M24)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3329,13 +3435,13 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3347,22 +3453,27 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>-2</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H25)*(1+(('⚙️ Calibrage'!$B$5+K25)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L25)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N25)/100))*((('⚙️ Calibrage'!$B$4+J25)+('⚙️ Calibrage'!$B$3+I25)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M25)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P25" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>(D5)
 craft :fer, grif de goblin, dent de goblin
@@ -3403,10 +3514,10 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
@@ -3421,23 +3532,27 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H26)*(1+(('⚙️ Calibrage'!$B$5+K26)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L26)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N26)/100))*((('⚙️ Calibrage'!$B$4+J26)+('⚙️ Calibrage'!$B$3+I26)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M26)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
         <is>
           <t>(D4)
 craft fer ,gelé de slime ,griffe de goblin
@@ -3478,40 +3593,45 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>10</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H27)*(1+(('⚙️ Calibrage'!$B$5+K27)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L27)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N27)/100))*((('⚙️ Calibrage'!$B$4+J27)+('⚙️ Calibrage'!$B$3+I27)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M27)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P27" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>(D1)
 craft bois ,fer, gelé de slime
@@ -3552,10 +3672,10 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
@@ -3570,23 +3690,27 @@
         <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H28)*(1+(('⚙️ Calibrage'!$B$5+K28)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L28)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N28)/100))*((('⚙️ Calibrage'!$B$4+J28)+('⚙️ Calibrage'!$B$3+I28)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M28)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n">
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="T28" s="5" t="inlineStr">
+      <c r="U28" s="5" t="inlineStr">
         <is>
           <t>(D4)</t>
         </is>
@@ -3625,7 +3749,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -3648,17 +3772,22 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H29)*(1+(('⚙️ Calibrage'!$B$5+K29)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L29)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N29)/100))*((('⚙️ Calibrage'!$B$4+J29)+('⚙️ Calibrage'!$B$3+I29)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M29)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P29" t="n">
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
+        <v>30</v>
+      </c>
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="S29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3693,7 +3822,7 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>0</v>
@@ -3705,29 +3834,33 @@
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H30)*(1+(('⚙️ Calibrage'!$B$5+K30)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L30)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N30)/100))*((('⚙️ Calibrage'!$B$4+J30)+('⚙️ Calibrage'!$B$3+I30)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M30)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q30" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="inlineStr"/>
+      <c r="S30" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3762,16 +3895,16 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3785,17 +3918,22 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H31)*(1+(('⚙️ Calibrage'!$B$5+K31)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L31)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N31)/100))*((('⚙️ Calibrage'!$B$4+J31)+('⚙️ Calibrage'!$B$3+I31)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M31)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P31" t="n">
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
         <v>80</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>(D2)</t>
         </is>
@@ -3834,13 +3972,13 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0</v>
@@ -3857,18 +3995,22 @@
       <c r="O32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P32" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H32)*(1+(('⚙️ Calibrage'!$B$5+K32)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L32)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N32)/100))*((('⚙️ Calibrage'!$B$4+J32)+('⚙️ Calibrage'!$B$3+I32)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M32)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
         <is>
           <t>(D4)(D5)
 craft: grife de goblin ,fer
@@ -3909,40 +4051,45 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>5</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H33)*(1+(('⚙️ Calibrage'!$B$5+K33)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L33)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N33)/100))*((('⚙️ Calibrage'!$B$4+J33)+('⚙️ Calibrage'!$B$3+I33)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M33)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P33" t="n">
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3977,7 +4124,7 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>0</v>
@@ -3986,32 +4133,36 @@
         <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="M34" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P34" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H34)*(1+(('⚙️ Calibrage'!$B$5+K34)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L34)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N34)/100))*((('⚙️ Calibrage'!$B$4+J34)+('⚙️ Calibrage'!$B$3+I34)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M34)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4046,40 +4197,45 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>15</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H35)*(1+(('⚙️ Calibrage'!$B$5+K35)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L35)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N35)/100))*((('⚙️ Calibrage'!$B$4+J35)+('⚙️ Calibrage'!$B$3+I35)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M35)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P35" t="n">
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>1061</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4114,41 +4270,45 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P36" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H36)*(1+(('⚙️ Calibrage'!$B$5+K36)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L36)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N36)/100))*((('⚙️ Calibrage'!$B$4+J36)+('⚙️ Calibrage'!$B$3+I36)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M36)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="5" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4183,16 +4343,16 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4204,19 +4364,24 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>5</v>
       </c>
-      <c r="P37" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H37)*(1+(('⚙️ Calibrage'!$B$5+K37)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L37)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N37)/100))*((('⚙️ Calibrage'!$B$4+J37)+('⚙️ Calibrage'!$B$3+I37)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M37)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>(D2)
 craft : fer, fourure ,gelé de slime
@@ -4257,10 +4422,10 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -4275,23 +4440,27 @@
         <v>0</v>
       </c>
       <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H38)*(1+(('⚙️ Calibrage'!$B$5+K38)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L38)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N38)/100))*((('⚙️ Calibrage'!$B$4+J38)+('⚙️ Calibrage'!$B$3+I38)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M38)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R38" s="5" t="n"/>
-      <c r="S38" s="5" t="n">
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="T38" s="5" t="inlineStr">
+      <c r="U38" s="5" t="inlineStr">
         <is>
           <t>(D1)</t>
         </is>
@@ -4330,40 +4499,45 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>5</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>-1</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H39)*(1+(('⚙️ Calibrage'!$B$5+K39)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L39)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N39)/100))*((('⚙️ Calibrage'!$B$4+J39)+('⚙️ Calibrage'!$B$3+I39)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M39)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P39" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>80</v>
       </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>(D4) (D6)
 +20 de mana aussi</t>
@@ -4403,20 +4577,20 @@
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="L40" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="5" t="n">
         <v>0</v>
       </c>
@@ -4426,18 +4600,22 @@
       <c r="O40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P40" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H40)*(1+(('⚙️ Calibrage'!$B$5+K40)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L40)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N40)/100))*((('⚙️ Calibrage'!$B$4+J40)+('⚙️ Calibrage'!$B$3+I40)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M40)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="5" t="n"/>
-      <c r="S40" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="T40" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4472,40 +4650,45 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>-20</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="P41" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H41)*(1+(('⚙️ Calibrage'!$B$5+K41)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L41)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N41)/100))*((('⚙️ Calibrage'!$B$4+J41)+('⚙️ Calibrage'!$B$3+I41)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M41)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P41" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="n">
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>80</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>(D4</t>
         </is>
@@ -4544,41 +4727,45 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M42" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P42" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H42)*(1+(('⚙️ Calibrage'!$B$5+K42)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L42)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N42)/100))*((('⚙️ Calibrage'!$B$4+J42)+('⚙️ Calibrage'!$B$3+I42)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M42)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="7" t="inlineStr">
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="7" t="inlineStr">
         <is>
           <t>(D6)
 craft :tissu + drop du chaman goblin
@@ -4620,40 +4807,45 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>10</v>
       </c>
       <c r="M43" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" t="n">
         <v>5</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="P43" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H43)*(1+(('⚙️ Calibrage'!$B$5+K43)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L43)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N43)/100))*((('⚙️ Calibrage'!$B$4+J43)+('⚙️ Calibrage'!$B$3+I43)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M43)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P43" t="n">
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="n">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="T43" t="n">
         <v>1200</v>
       </c>
-      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4688,41 +4880,45 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>15</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H44)*(1+(('⚙️ Calibrage'!$B$5+K44)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L44)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N44)/100))*((('⚙️ Calibrage'!$B$4+J44)+('⚙️ Calibrage'!$B$3+I44)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M44)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R44" s="5" t="n"/>
-      <c r="S44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="7" t="inlineStr">
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="7" t="inlineStr">
         <is>
           <t>(D3)
 craft ,tissu ,gelé de slime ,fourure
@@ -4763,7 +4959,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4772,31 +4968,36 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>5</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
         <v>8</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>4</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H45)*(1+(('⚙️ Calibrage'!$B$5+K45)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L45)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N45)/100))*((('⚙️ Calibrage'!$B$4+J45)+('⚙️ Calibrage'!$B$3+I45)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M45)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P45" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4831,16 +5032,16 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
@@ -4849,23 +5050,27 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
         <v>-2</v>
       </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H46)*(1+(('⚙️ Calibrage'!$B$5+K46)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L46)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N46)/100))*((('⚙️ Calibrage'!$B$4+J46)+('⚙️ Calibrage'!$B$3+I46)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M46)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P46" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R46" s="5" t="n"/>
-      <c r="S46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4900,16 +5105,16 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4923,17 +5128,22 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="P47" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H47)*(1+(('⚙️ Calibrage'!$B$5+K47)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L47)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N47)/100))*((('⚙️ Calibrage'!$B$4+J47)+('⚙️ Calibrage'!$B$3+I47)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M47)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P47" t="n">
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4968,16 +5178,16 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
@@ -4986,23 +5196,27 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
         <v>-2</v>
       </c>
-      <c r="O48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H48)*(1+(('⚙️ Calibrage'!$B$5+K48)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L48)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N48)/100))*((('⚙️ Calibrage'!$B$4+J48)+('⚙️ Calibrage'!$B$3+I48)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M48)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="5" t="inlineStr">
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
         <is>
           <t>Une plaque de granit vivant, taillée dans le Colosse lui-même.</t>
         </is>
@@ -5041,16 +5255,16 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5059,22 +5273,27 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>-1</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H49)*(1+(('⚙️ Calibrage'!$B$5+K49)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L49)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N49)/100))*((('⚙️ Calibrage'!$B$4+J49)+('⚙️ Calibrage'!$B$3+I49)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M49)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P49" t="n">
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>(D4)(D5)  
 craft : tissu ,fourure et dent de goblin
@@ -5115,7 +5334,7 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>0</v>
@@ -5124,32 +5343,36 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L50" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="O50" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H50)*(1+(('⚙️ Calibrage'!$B$5+K50)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L50)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N50)/100))*((('⚙️ Calibrage'!$B$4+J50)+('⚙️ Calibrage'!$B$3+I50)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M50)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R50" s="5" t="n"/>
-      <c r="S50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="5" t="inlineStr">
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
         <is>
           <t>(D1) (D3)</t>
         </is>
@@ -5188,16 +5411,16 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5209,19 +5432,24 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
         <v>5</v>
       </c>
-      <c r="P51" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H51)*(1+(('⚙️ Calibrage'!$B$5+K51)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L51)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N51)/100))*((('⚙️ Calibrage'!$B$4+J51)+('⚙️ Calibrage'!$B$3+I51)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M51)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>(D2)
 craft: fer beaucoup ,gelé de slime beaucoup
@@ -5262,41 +5490,45 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
         <v>-20</v>
       </c>
-      <c r="M52" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H52)*(1+(('⚙️ Calibrage'!$B$5+K52)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L52)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N52)/100))*((('⚙️ Calibrage'!$B$4+J52)+('⚙️ Calibrage'!$B$3+I52)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M52)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P52" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R52" s="5" t="n"/>
-      <c r="S52" s="5" t="n">
+      <c r="R52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="T52" s="5" t="inlineStr">
+      <c r="U52" s="5" t="inlineStr">
         <is>
           <t>(D2)</t>
         </is>
@@ -5335,16 +5567,16 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -5356,19 +5588,24 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
         <v>10</v>
       </c>
-      <c r="P53" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H53)*(1+(('⚙️ Calibrage'!$B$5+K53)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L53)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N53)/100))*((('⚙️ Calibrage'!$B$4+J53)+('⚙️ Calibrage'!$B$3+I53)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M53)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="n">
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="T53" t="n">
         <v>1600</v>
       </c>
-      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -5403,16 +5640,16 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
@@ -5421,23 +5658,27 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H54)*(1+(('⚙️ Calibrage'!$B$5+K54)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L54)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N54)/100))*((('⚙️ Calibrage'!$B$4+J54)+('⚙️ Calibrage'!$B$3+I54)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M54)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P54" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="5" t="n">
+      <c r="R54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="T54" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5472,7 +5713,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -5481,31 +5722,36 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" t="n">
         <v>5</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>10</v>
       </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
       <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
         <v>-1</v>
       </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H55)*(1+(('⚙️ Calibrage'!$B$5+K55)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L55)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N55)/100))*((('⚙️ Calibrage'!$B$4+J55)+('⚙️ Calibrage'!$B$3+I55)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M55)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P55" t="n">
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="n">
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="n">
         <v>120</v>
       </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>(D3)(D6)
 +30 mana</t>
@@ -5545,41 +5791,45 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="M56" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P56" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H56)*(1+(('⚙️ Calibrage'!$B$5+K56)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L56)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N56)/100))*((('⚙️ Calibrage'!$B$4+J56)+('⚙️ Calibrage'!$B$3+I56)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M56)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P56" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R56" s="5" t="n"/>
-      <c r="S56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="7" t="inlineStr">
+      <c r="R56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="7" t="inlineStr">
         <is>
           <t>(D6)(D5)
 craft :fourure ,tissu et (un drop du goblin chaman 
@@ -5621,13 +5871,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -5639,22 +5889,27 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>-1</v>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H57)*(1+(('⚙️ Calibrage'!$B$5+K57)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L57)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N57)/100))*((('⚙️ Calibrage'!$B$4+J57)+('⚙️ Calibrage'!$B$3+I57)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M57)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P57" t="n">
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="n">
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
         <v>120</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>(D4)</t>
         </is>
@@ -5693,41 +5948,45 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L58" s="5" t="n">
+      <c r="M58" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="M58" s="5" t="n">
+      <c r="N58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N58" s="5" t="n">
+      <c r="O58" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H58)*(1+(('⚙️ Calibrage'!$B$5+K58)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L58)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N58)/100))*((('⚙️ Calibrage'!$B$4+J58)+('⚙️ Calibrage'!$B$3+I58)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M58)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P58" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q58" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="7" t="inlineStr">
+      <c r="R58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="7" t="inlineStr">
         <is>
           <t>(D3)(D8)
 craft: tissu ,fourures ,griff de goblin
@@ -5768,7 +6027,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -5783,25 +6042,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
         <v>4</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>5</v>
       </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H59)*(1+(('⚙️ Calibrage'!$B$5+K59)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L59)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N59)/100))*((('⚙️ Calibrage'!$B$4+J59)+('⚙️ Calibrage'!$B$3+I59)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M59)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -5836,16 +6100,16 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
@@ -5854,23 +6118,27 @@
         <v>0</v>
       </c>
       <c r="N60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="5" t="n">
         <v>-1</v>
       </c>
-      <c r="O60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H60)*(1+(('⚙️ Calibrage'!$B$5+K60)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L60)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N60)/100))*((('⚙️ Calibrage'!$B$4+J60)+('⚙️ Calibrage'!$B$3+I60)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M60)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P60" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q60" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R60" s="5" t="n"/>
-      <c r="S60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5905,13 +6173,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5923,22 +6191,27 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H61)*(1+(('⚙️ Calibrage'!$B$5+K61)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L61)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N61)/100))*((('⚙️ Calibrage'!$B$4+J61)+('⚙️ Calibrage'!$B$3+I61)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M61)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P61" t="n">
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5973,41 +6246,45 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="M62" s="5" t="n">
+      <c r="N62" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="N62" s="5" t="n">
+      <c r="O62" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="O62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H62)*(1+(('⚙️ Calibrage'!$B$5+K62)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L62)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N62)/100))*((('⚙️ Calibrage'!$B$4+J62)+('⚙️ Calibrage'!$B$3+I62)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M62)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P62" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="R62" s="5" t="n"/>
-      <c r="S62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="5" t="inlineStr">
+      <c r="S62" s="6" t="n">
+        <v>1642</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="5" t="inlineStr">
         <is>
           <t>Elle ne projette aucune ombre. Ceux qui la portent non plus.</t>
         </is>
@@ -6046,7 +6323,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -6055,31 +6332,36 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
         <v>5</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>10</v>
       </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>4</v>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H63)*(1+(('⚙️ Calibrage'!$B$5+K63)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L63)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N63)/100))*((('⚙️ Calibrage'!$B$4+J63)+('⚙️ Calibrage'!$B$3+I63)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M63)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P63" t="n">
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="inlineStr">
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
         <is>
           <t>Annule la première attaque subie.</t>
         </is>
@@ -6118,19 +6400,19 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="5" t="n">
         <v>0</v>
@@ -6141,18 +6423,22 @@
       <c r="O64" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P64" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H64)*(1+(('⚙️ Calibrage'!$B$5+K64)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L64)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N64)/100))*((('⚙️ Calibrage'!$B$4+J64)+('⚙️ Calibrage'!$B$3+I64)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M64)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P64" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q64" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R64" s="5" t="n"/>
-      <c r="S64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="5" t="inlineStr"/>
+      <c r="R64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6187,16 +6473,16 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -6210,17 +6496,22 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="P65" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H65)*(1+(('⚙️ Calibrage'!$B$5+K65)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L65)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N65)/100))*((('⚙️ Calibrage'!$B$4+J65)+('⚙️ Calibrage'!$B$3+I65)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M65)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P65" t="n">
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6255,16 +6546,16 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0</v>
@@ -6278,18 +6569,22 @@
       <c r="O66" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P66" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H66)*(1+(('⚙️ Calibrage'!$B$5+K66)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L66)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N66)/100))*((('⚙️ Calibrage'!$B$4+J66)+('⚙️ Calibrage'!$B$3+I66)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M66)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P66" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q66" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R66" s="5" t="n"/>
-      <c r="S66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6324,40 +6619,45 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
         <v>2</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H67)*(1+(('⚙️ Calibrage'!$B$5+K67)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L67)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N67)/100))*((('⚙️ Calibrage'!$B$4+J67)+('⚙️ Calibrage'!$B$3+I67)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M67)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P67" t="n">
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6392,7 +6692,7 @@
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I68" s="5" t="n">
         <v>0</v>
@@ -6415,18 +6715,22 @@
       <c r="O68" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P68" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H68)*(1+(('⚙️ Calibrage'!$B$5+K68)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L68)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N68)/100))*((('⚙️ Calibrage'!$B$4+J68)+('⚙️ Calibrage'!$B$3+I68)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M68)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P68" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q68" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="R68" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="R68" s="5" t="n"/>
-      <c r="S68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5" t="inlineStr"/>
+      <c r="S68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6461,13 +6765,13 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6484,17 +6788,22 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="P69" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H69)*(1+(('⚙️ Calibrage'!$B$5+K69)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L69)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N69)/100))*((('⚙️ Calibrage'!$B$4+J69)+('⚙️ Calibrage'!$B$3+I69)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M69)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P69" t="n">
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6529,16 +6838,16 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>0</v>
@@ -6550,20 +6859,24 @@
         <v>0</v>
       </c>
       <c r="O70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="P70" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H70)*(1+(('⚙️ Calibrage'!$B$5+K70)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L70)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N70)/100))*((('⚙️ Calibrage'!$B$4+J70)+('⚙️ Calibrage'!$B$3+I70)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M70)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
-      </c>
       <c r="Q70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="5" t="n"/>
-      <c r="S70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="5" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="R70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5" t="inlineStr">
         <is>
           <t>Un noyau de gelée qui bat encore, arraché au Titan Visqueux.</t>
         </is>
@@ -6602,7 +6915,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -6611,11 +6924,11 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
         <v>3</v>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
@@ -6625,17 +6938,22 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="P71" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H71)*(1+(('⚙️ Calibrage'!$B$5+K71)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L71)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N71)/100))*((('⚙️ Calibrage'!$B$4+J71)+('⚙️ Calibrage'!$B$3+I71)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M71)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P71" t="n">
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6670,41 +6988,45 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="M72" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P72" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H72)*(1+(('⚙️ Calibrage'!$B$5+K72)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L72)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N72)/100))*((('⚙️ Calibrage'!$B$4+J72)+('⚙️ Calibrage'!$B$3+I72)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M72)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P72" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q72" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R72" s="5" t="n"/>
-      <c r="S72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="5" t="inlineStr"/>
+      <c r="R72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="6" t="n">
+        <v>1175</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6739,7 +7061,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -6754,29 +7076,34 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
         <v>6</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="6">
-        <f>ROUND((('⚙️ Calibrage'!$B$2+H73)*(1+(('⚙️ Calibrage'!$B$5+K73)/100)*MAX(0,('⚙️ Calibrage'!$B$6+L73)-100)/100)*(1+('⚙️ Calibrage'!$B$8+N73)/100))*((('⚙️ Calibrage'!$B$4+J73)+('⚙️ Calibrage'!$B$3+I73)*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-('⚙️ Calibrage'!$B$7+M73)/100))/'⚙️ Calibrage'!$B$10-'⚙️ Calibrage'!$B$11,1)</f>
-        <v/>
+      <c r="P73" t="n">
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T73"/>
-  <conditionalFormatting sqref="P2:P73">
+  <autoFilter ref="A1:U73"/>
+  <conditionalFormatting sqref="S2:S73">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6968,11 +7295,11 @@
       <c r="N2" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <f>ROUND((E2*(1+(H2/100)*MAX(0,I2-100)/100)*(1+G2/100))*((D2+F2*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J2/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="6">
         <f>IFERROR(VLOOKUP(O2,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7043,11 +7370,11 @@
       <c r="N3" t="n">
         <v>40</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="6">
         <f>ROUND((E3*(1+(H3/100)*MAX(0,I3-100)/100)*(1+G3/100))*((D3+F3*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J3/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="6">
         <f>IFERROR(VLOOKUP(O3,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7118,11 +7445,11 @@
       <c r="N4" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="6">
         <f>ROUND((E4*(1+(H4/100)*MAX(0,I4-100)/100)*(1+G4/100))*((D4+F4*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J4/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="6">
         <f>IFERROR(VLOOKUP(O4,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7193,11 +7520,11 @@
       <c r="N5" t="n">
         <v>25</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="6">
         <f>ROUND((E5*(1+(H5/100)*MAX(0,I5-100)/100)*(1+G5/100))*((D5+F5*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J5/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="6">
         <f>IFERROR(VLOOKUP(O5,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7268,11 +7595,11 @@
       <c r="N6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="6">
         <f>ROUND((E6*(1+(H6/100)*MAX(0,I6-100)/100)*(1+G6/100))*((D6+F6*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J6/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="6">
         <f>IFERROR(VLOOKUP(O6,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7343,11 +7670,11 @@
       <c r="N7" t="n">
         <v>20</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="6">
         <f>ROUND((E7*(1+(H7/100)*MAX(0,I7-100)/100)*(1+G7/100))*((D7+F7*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J7/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="6">
         <f>IFERROR(VLOOKUP(O7,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7418,11 +7745,11 @@
       <c r="N8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="6">
         <f>ROUND((E8*(1+(H8/100)*MAX(0,I8-100)/100)*(1+G8/100))*((D8+F8*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J8/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="6">
         <f>IFERROR(VLOOKUP(O8,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7493,11 +7820,11 @@
       <c r="N9" t="n">
         <v>20</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="6">
         <f>ROUND((E9*(1+(H9/100)*MAX(0,I9-100)/100)*(1+G9/100))*((D9+F9*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J9/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="6">
         <f>IFERROR(VLOOKUP(O9,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7568,11 +7895,11 @@
       <c r="N10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="6">
         <f>ROUND((E10*(1+(H10/100)*MAX(0,I10-100)/100)*(1+G10/100))*((D10+F10*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J10/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="6">
         <f>IFERROR(VLOOKUP(O10,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7643,11 +7970,11 @@
       <c r="N11" t="n">
         <v>20</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="6">
         <f>ROUND((E11*(1+(H11/100)*MAX(0,I11-100)/100)*(1+G11/100))*((D11+F11*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J11/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="6">
         <f>IFERROR(VLOOKUP(O11,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7718,11 +8045,11 @@
       <c r="N12" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="6">
         <f>ROUND((E12*(1+(H12/100)*MAX(0,I12-100)/100)*(1+G12/100))*((D12+F12*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J12/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="6">
         <f>IFERROR(VLOOKUP(O12,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7793,11 +8120,11 @@
       <c r="N13" t="n">
         <v>10</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="6">
         <f>ROUND((E13*(1+(H13/100)*MAX(0,I13-100)/100)*(1+G13/100))*((D13+F13*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J13/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="6">
         <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7868,11 +8195,11 @@
       <c r="N14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="6">
         <f>ROUND((E14*(1+(H14/100)*MAX(0,I14-100)/100)*(1+G14/100))*((D14+F14*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J14/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="6">
         <f>IFERROR(VLOOKUP(O14,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -7943,11 +8270,11 @@
       <c r="N15" t="n">
         <v>7</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="6">
         <f>ROUND((E15*(1+(H15/100)*MAX(0,I15-100)/100)*(1+G15/100))*((D15+F15*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J15/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="6">
         <f>IFERROR(VLOOKUP(O15,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8018,11 +8345,11 @@
       <c r="N16" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="6">
         <f>ROUND((E16*(1+(H16/100)*MAX(0,I16-100)/100)*(1+G16/100))*((D16+F16*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J16/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="6">
         <f>IFERROR(VLOOKUP(O16,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8093,11 +8420,11 @@
       <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="6">
         <f>ROUND((E17*(1+(H17/100)*MAX(0,I17-100)/100)*(1+G17/100))*((D17+F17*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J17/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="6">
         <f>IFERROR(VLOOKUP(O17,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8168,11 +8495,11 @@
       <c r="N18" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="6">
         <f>ROUND((E18*(1+(H18/100)*MAX(0,I18-100)/100)*(1+G18/100))*((D18+F18*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J18/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="6">
         <f>IFERROR(VLOOKUP(O18,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8243,11 +8570,11 @@
       <c r="N19" t="n">
         <v>4</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="6">
         <f>ROUND((E19*(1+(H19/100)*MAX(0,I19-100)/100)*(1+G19/100))*((D19+F19*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J19/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="6">
         <f>IFERROR(VLOOKUP(O19,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8318,11 +8645,11 @@
       <c r="N20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="6">
         <f>ROUND((E20*(1+(H20/100)*MAX(0,I20-100)/100)*(1+G20/100))*((D20+F20*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J20/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="6">
         <f>IFERROR(VLOOKUP(O20,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8393,11 +8720,11 @@
       <c r="N21" t="n">
         <v>15</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="6">
         <f>ROUND((E21*(1+(H21/100)*MAX(0,I21-100)/100)*(1+G21/100))*((D21+F21*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J21/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="6">
         <f>IFERROR(VLOOKUP(O21,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8468,11 +8795,11 @@
       <c r="N22" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="6">
         <f>ROUND((E22*(1+(H22/100)*MAX(0,I22-100)/100)*(1+G22/100))*((D22+F22*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J22/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="6">
         <f>IFERROR(VLOOKUP(O22,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8543,11 +8870,11 @@
       <c r="N23" t="n">
         <v>8</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="6">
         <f>ROUND((E23*(1+(H23/100)*MAX(0,I23-100)/100)*(1+G23/100))*((D23+F23*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J23/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="6">
         <f>IFERROR(VLOOKUP(O23,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -8618,11 +8945,11 @@
       <c r="N24" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="6">
         <f>ROUND((E24*(1+(H24/100)*MAX(0,I24-100)/100)*(1+G24/100))*((D24+F24*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J24/100))/'⚙️ Calibrage'!$B$10,0)</f>
         <v/>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="6">
         <f>IFERROR(VLOOKUP(O24,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
@@ -11424,18 +11751,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -11451,42 +11782,2386 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Forme</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Niveau max</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Coûts/niveau</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Effets</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Prérequis</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Règle</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Icône</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>racine_combat</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Aventurier</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>départ</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>-80, 450</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Le commencement. Les trois voies de combat partent d'ici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>voie_attaque</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Voie de l'Attaque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aventurier</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-80, 260</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Début de voie — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>voie_defense</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Voie de la Défense</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Aventurier</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>85, 545</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Début de voie — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>voie_support</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Voie du Support</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aventurier</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-245, 545</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Début de voie — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>classe_combattant</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Combattant</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Attaque, Défense, Défense, Attaque</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>249, 260</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>🦾</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Classe obtenue en reliant deux voies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>classe_paladin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Paladin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Support, Défense, Support, Défense</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-80, 830</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>🏰</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Classe obtenue en reliant deux voies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>classe_vampire</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Vampire</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Attaque, Support, Attaque, Support</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>-409, 260</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Classe obtenue en reliant deux voies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>racine_explorateur</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Explorateur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>départ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1820, 500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>La voie de l'explorateur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>axe_or</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Axe de l'Or</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,3,5]</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Explorateur</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>1954, 634</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Début d'axe — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>axe_drop</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Axe du Butin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [1,3,5]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Axe de l'Or, Axe de l'Expérience</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1820, 785</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🍀</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Début d'axe — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>axe_xp</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Axe de l'Expérience</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,3,5]</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Explorateur</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>1686, 634</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Début d'axe — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>axe_confort</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Axe du Confort</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>unlock_feature → [Notification privé lorsque le cooldown d'une commande est prêt,Notification privé lorsque le cooldown d'une commande est prêt,Notification privé lorsque le cooldown d'une commande est prêt]
+unlock_feature → [1 participation journalière supplémentaire pour défier la tour solo,1 participation journalière supplémentaire pour défier la tour solo,1 participation journalière supplémentaire pour défier la tour solo]
+unlock_feature → [Notifié lorsqu'un événement aparait,Notifié lorsqu'un événement aparait,Notifié lorsqu'un événement aparait]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Axe du Butin</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1820, 975</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Début d'axe — à étoffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>passif_1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Voie du Support</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>-409, 640</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>passif_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-574, 735</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>passif_4</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>-416, 786</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>passif_5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-539, 573</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>passif_6</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Support, Support</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>-650, 450</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>passif_7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Support, Support</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-366, 943</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>passif_8</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>-222, 697</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>passif_9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-365, 450</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>❤️</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>stat_1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Voie de la Défense</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>249, 640</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>actif_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Voie de l'Attaque</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-80, 70</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>actif_2</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>-222, 203</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>actif_3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>63, 203</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>actif_5</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>-80, -120</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>actif_6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-203, -9</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>actif_7</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Attaque, Attaque</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>-365, -44</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>actif_8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>43, -9</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>actif_9</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Attaque, Attaque</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>205, -44</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>actif_10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-416, 114</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>actif_11</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>256, 114</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>stat_3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>63, 697</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>stat_4</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>205, 450</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>stat_5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>414, 735</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>stat_7</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>379, 573</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>stat_8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Défense, Défense</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>490, 450</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>stat_9</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>256, 786</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>stat_10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>43, 909</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>stat_2</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>379, 327</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>stat_6</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Défense, Défense</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>205, 944</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>passif_2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>-204, 909</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>🔷</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>passif_10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Départ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-539, 327</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>🔷</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:M43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11844,7 +14519,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin I à chaque /daily (en plus de l'or).</t>
+          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin à chaque /daily (en plus de l'or).</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-13 21:00 UTC</t>
+          <t>Généré le 2026-10-20 18:20 UTC</t>
         </is>
       </c>
     </row>
@@ -11751,18 +11751,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Voie de l'Attaque</t>
+          <t>Voie du Guerrier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Voies</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [5]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -11948,11 +11948,7 @@
           <t>⚔️</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Début de voie — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -11962,7 +11958,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Voie de la Défense</t>
+          <t>Voie du Protecteur</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -11972,7 +11968,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Voies</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
@@ -11986,7 +11982,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [5]</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -12005,11 +12001,7 @@
           <t>🛡️</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Début de voie — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12029,7 +12021,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Voies</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -12043,7 +12035,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [5]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12062,11 +12054,7 @@
           <t>❤️</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Début de voie — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -12086,7 +12074,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Classe</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
@@ -12098,14 +12086,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [combattant]
+hp_max_percent → [5]
+atk_percent → [5]</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Attaque, Défense, Défense, Attaque</t>
+          <t>Attaque, Deg. Crit., Défense, Régénération</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -12120,12 +12110,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>🦾</t>
+          <t>👊</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Classe obtenue en reliant deux voies.</t>
+          <t>Classe Combattant : +5 % de PV max et +5 % d'attaque.</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12137,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Classe</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -12159,14 +12149,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>grant_class → [paladin]
+heal_received_percent → [50]
+def_percent → [5]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Support, Défense, Support, Défense</t>
+          <t>PV, Défense, Régénération, Rég. Mana</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -12186,7 +12178,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Classe obtenue en reliant deux voies.</t>
+          <t>Classe Paladin : soins reçus +50 % et +5 % de défense.</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12200,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Classe</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
@@ -12220,14 +12212,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [vampire]
+lifesteal_percent → [5]</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Attaque, Support, Attaque, Support</t>
+          <t>Attaque, Deg. Crit., PV, Rég. Mana</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -12242,12 +12235,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>🩸</t>
+          <t>🧛</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Classe obtenue en reliant deux voies.</t>
+          <t>Classe Vampire : se soigne de 5 % des dégâts infligés.</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12291,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1820, 500</t>
+          <t>1090, -230</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -12320,7 +12313,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Axe de l'Or</t>
+          <t>Bonus Or</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -12330,7 +12323,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
@@ -12344,7 +12337,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>gold_drop_percent → [1,3,5]</t>
+          <t>gold_drop_percent → [1,4,10]</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -12355,7 +12348,7 @@
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>1954, 634</t>
+          <t>1224, -96</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -12363,11 +12356,7 @@
           <t>💰</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Début d'axe — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12377,7 +12366,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Axe du Butin</t>
+          <t>Chance Drop</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12387,7 +12376,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -12401,12 +12390,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>drop_rate_multiplier → [1,3,5]</t>
+          <t>drop_rate_multiplier → [10,40,100]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Axe de l'Or, Axe de l'Expérience</t>
+          <t>Bonus Or, Bonus XP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -12416,7 +12405,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1820, 785</t>
+          <t>1090, 55</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -12424,11 +12413,7 @@
           <t>🍀</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Début d'axe — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -12438,7 +12423,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Axe de l'Expérience</t>
+          <t>Bonus XP</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -12448,7 +12433,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -12462,7 +12447,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>xp_drop_percent → [1,3,5]</t>
+          <t>xp_drop_percent → [1,4,10]</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -12473,7 +12458,7 @@
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>1686, 634</t>
+          <t>956, -96</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -12481,11 +12466,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Début d'axe — à étoffer.</t>
-        </is>
-      </c>
+      <c r="M12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12495,7 +12476,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axe du Confort</t>
+          <t>Confort</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12505,34 +12486,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>unlock_feature → [Notification privé lorsque le cooldown d'une commande est prêt,Notification privé lorsque le cooldown d'une commande est prêt,Notification privé lorsque le cooldown d'une commande est prêt]
-unlock_feature → [1 participation journalière supplémentaire pour défier la tour solo,1 participation journalière supplémentaire pour défier la tour solo,1 participation journalière supplémentaire pour défier la tour solo]
-unlock_feature → [Notifié lorsqu'un événement aparait,Notifié lorsqu'un événement aparait,Notifié lorsqu'un événement aparait]</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>unlock_feature → [notify_cooldowns]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Axe du Butin</t>
+          <t>Chance Drop</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1820, 975</t>
+          <t>1090, 245</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -12542,7 +12521,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Début d'axe — à étoffer.</t>
+          <t>Reçois un message privé quand un de tes temps de recharge est terminé.</t>
         </is>
       </c>
     </row>
@@ -12554,17 +12533,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
@@ -12578,7 +12557,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [1]</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -12602,22 +12581,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>passif_3</t>
+          <t>passif_4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -12631,23 +12610,23 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-574, 735</t>
+          <t>-416, 786</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>💧</t>
+          <t>💨</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -12655,22 +12634,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>passif_4</t>
+          <t>passif_5</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
@@ -12684,18 +12663,18 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>-416, 786</t>
+          <t>-539, 573</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -12708,22 +12687,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>passif_5</t>
+          <t>passif_6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -12737,23 +12716,23 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [1]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-539, 573</t>
+          <t>-650, 450</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>💨</t>
+          <t>❤️</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -12761,22 +12740,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>passif_6</t>
+          <t>passif_7</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
@@ -12790,22 +12769,18 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [1]</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Support, Support</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>toutes</t>
-        </is>
-      </c>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>-650, 450</t>
+          <t>-366, 943</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -12818,22 +12793,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>passif_7</t>
+          <t>passif_8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -12847,22 +12822,18 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [1]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Support, Support</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>toutes</t>
-        </is>
-      </c>
+          <t>Voie du Support</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-366, 943</t>
+          <t>-222, 697</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -12875,22 +12846,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>passif_8</t>
+          <t>passif_9</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
@@ -12904,18 +12875,18 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_max_percent → [1]</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Voie du Support</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>-222, 697</t>
+          <t>-365, 450</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -12928,22 +12899,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>passif_9</t>
+          <t>stat_1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -12957,23 +12928,23 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [1]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Voie du Protecteur</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-365, 450</t>
+          <t>249, 640</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>❤️</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -12981,22 +12952,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>stat_1</t>
+          <t>actif_1</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Attaque</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -13010,23 +12981,23 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Voie de la Défense</t>
+          <t>Voie du Guerrier</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>249, 640</t>
+          <t>-80, 70</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr"/>
@@ -13034,7 +13005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>actif_1</t>
+          <t>actif_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13049,7 +13020,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -13063,18 +13034,18 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Voie de l'Attaque</t>
+          <t>Voie du Guerrier</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-80, 70</t>
+          <t>-222, 203</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -13087,7 +13058,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>actif_2</t>
+          <t>actif_3</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13102,7 +13073,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
@@ -13116,18 +13087,18 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Voie du Guerrier</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>-222, 203</t>
+          <t>63, 203</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -13140,22 +13111,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>actif_3</t>
+          <t>actif_6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -13169,7 +13140,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -13180,12 +13151,12 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>63, 203</t>
+          <t>-203, -9</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>💨</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -13193,7 +13164,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>actif_5</t>
+          <t>actif_7</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -13208,7 +13179,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
@@ -13222,23 +13193,23 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>-80, -120</t>
+          <t>-365, -44</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>🎯</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr"/>
@@ -13246,22 +13217,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>actif_6</t>
+          <t>actif_8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -13275,7 +13246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13286,7 +13257,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-203, -9</t>
+          <t>43, -9</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -13299,7 +13270,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>actif_7</t>
+          <t>actif_9</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -13314,7 +13285,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
@@ -13328,22 +13299,18 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>atk_percent → [1]</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Attaque, Attaque</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>toutes</t>
-        </is>
-      </c>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>-365, -44</t>
+          <t>205, -44</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -13356,22 +13323,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>actif_8</t>
+          <t>actif_10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -13385,7 +13352,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>crit_damage_flat → [5]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -13396,12 +13363,12 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>43, -9</t>
+          <t>-416, 114</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>💨</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -13409,22 +13376,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>actif_9</t>
+          <t>actif_11</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>Attaque</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Attaque</t>
-        </is>
-      </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -13438,27 +13405,23 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>crit_damage_flat → [5]</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Attaque, Attaque</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>toutes</t>
-        </is>
-      </c>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>205, -44</t>
+          <t>256, 114</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>💥</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr"/>
@@ -13466,22 +13429,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>actif_10</t>
+          <t>stat_3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -13495,23 +13458,23 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [1]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Voie du Protecteur</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-416, 114</t>
+          <t>63, 697</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>💥</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -13519,22 +13482,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>actif_11</t>
+          <t>stat_4</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Défense</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
@@ -13548,23 +13511,23 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [1]</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Attaque</t>
+          <t>Voie du Protecteur</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>256, 114</t>
+          <t>205, 450</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>💥</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr"/>
@@ -13572,22 +13535,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stat_3</t>
+          <t>stat_7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -13601,7 +13564,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -13612,12 +13575,12 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>63, 697</t>
+          <t>379, 573</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>💨</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -13625,7 +13588,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>stat_4</t>
+          <t>stat_8</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -13640,7 +13603,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
@@ -13654,18 +13617,18 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [1]</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>205, 450</t>
+          <t>490, 450</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -13678,22 +13641,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stat_5</t>
+          <t>stat_9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -13707,7 +13670,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>speed_flat → [1]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -13718,12 +13681,12 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>414, 735</t>
+          <t>256, 786</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🌀</t>
+          <t>💨</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -13731,22 +13694,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>stat_7</t>
+          <t>stat_10</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
@@ -13760,7 +13723,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_regeneration_flat → [5]</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -13771,12 +13734,12 @@
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>379, 573</t>
+          <t>43, 909</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>💨</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr"/>
@@ -13784,22 +13747,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stat_8</t>
+          <t>stat_2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Défense</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Défense</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -13813,27 +13776,23 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hp_regeneration_flat → [5]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Défense, Défense</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>toutes</t>
-        </is>
-      </c>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>490, 450</t>
+          <t>379, 327</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -13841,7 +13800,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>stat_9</t>
+          <t>stat_6</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -13856,7 +13815,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
@@ -13870,23 +13829,23 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>def_percent → [1]</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>256, 786</t>
+          <t>205, 944</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>💨</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr"/>
@@ -13894,22 +13853,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stat_10</t>
+          <t>passif_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Rég. Mana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -13923,23 +13882,23 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mana_regeneration_flat → [1]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>43, 909</t>
+          <t>-204, 909</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -13947,22 +13906,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>stat_2</t>
+          <t>passif_10</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Rég. Mana</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
@@ -13976,23 +13935,23 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mana_regeneration_flat → [1]</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>379, 327</t>
+          <t>-539, 327</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🔷</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr"/>
@@ -14000,22 +13959,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stat_6</t>
+          <t>passif_14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>AOE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Défense</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -14029,12 +13988,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>splash_damage_percent → [25]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Défense, Défense</t>
+          <t>Rég. Mana, Deg. Crit.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -14044,35 +14003,39 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>205, 944</t>
+          <t>-574, 165</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>🔮</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Les attaques infligent aussi des dégats aux ennemis adjacents la cible, 25% de dégats de l'attaque.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>passif_2</t>
+          <t>type_1_6</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Classe</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
@@ -14084,48 +14047,57 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [mage]
+mage_affinity_bonus → [1]</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr"/>
+          <t>Deg. Crit., Rég. Mana</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>-204, 909</t>
+          <t>-820, 22</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>🔷</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr"/>
+          <t>🧙</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Classe Mage : dégâts ×1,5 si son affinité dans l'élément de l'attaque atteint 25, ×2 à 50, ×5 à 100.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>passif_10</t>
+          <t>type_1_8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Chance Crit.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Départ</t>
+          <t>Stats Avancées</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -14139,29 +14111,2307 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>crit_chance_flat → [1]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>AOE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-539, 327</t>
+          <t>-550, -20</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>type_1_10</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>mana_max_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>AOE</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>-722, 278</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>type_1_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rég. Mana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mana_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-906, 229</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>🔷</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>type_1_2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>-685, -155</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>passif_11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Résistant</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>damage_taken_reduction_percent → [10]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Rég. Mana, Régénération</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>-80, 1020</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>🫧</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Réduit de 10% les dégats reçus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>type_1_3</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Egide</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [egide]
+team_shield_percent → [10]</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Rég. Mana, Régénération</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>-80, 1305</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>🗿</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Au début du combat donne un bouclier de 10% de ses points de vie max à lui et tous ses alliés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>type_1_4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>mana_max_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Résistant</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>-252, 1092</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>type_1_5</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Résistant</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>92, 1092</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>type_1_7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>141, 1276</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>type_1_9</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Rég. Mana</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>mana_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>-301, 1276</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>🔷</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>passif_12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tenace</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sentinelle</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>last_stand → [1]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Deg. Crit., Régénération</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>414, 165</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>💀</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Lors d'un combat, la première attaque devant le tuer le laisse à 1 pv à la place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>type_1_11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Titan</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [titan]
+damage_dealt_percent → [5]
+damage_taken_reduction_percent → [5]</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Deg. Crit., Régénération</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>660, 23</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>🦾</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Inflige 5% de dégats supplémentaires et réduit de 5% les dégats reçus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>type_1_12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sentinelle</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>crit_chance_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tenace</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>390, -20</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>type_1_13</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Sentinelle</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Tenace</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>562, 278</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>type_1_14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sentinelle</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>746, 229</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>type_1_15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Sentinelle</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>525, -155</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>passif_13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>mana_max_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-935, 450</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>passif_15</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>mana_max_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>-507, 1190</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>passif_16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Soigneur</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>grant_class → [soigneur]
+healer_spell → [1]
+heal_power_multiplier → [2]
+speed_per_ally → [1]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Rég. Mana, Rég. Mana</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-820, 878</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>💚</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Classe Soigneur : remplace son attaque par un sort de soin (cible choisie selon sa tactique, /tactique), soins donnés doublés, +1 de vitesse par allié présent au combat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>passif_17</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Rég. Mana</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>mana_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>-906, 671</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>🔷</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>passif_18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Rég. Mana</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>mana_regeneration_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-685, 1055</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>🔷</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>passif_3</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>348, 1190</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>passif_19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>dodge_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>775, 450</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>passif_20</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Rempart</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [rempart]
+redirect_ally_damage_percent → [50]</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Régénération, Régénération</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>660, 878</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>🧱</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Redirige 50% des dégats que devrait recevoir ses alliés sur lui à la place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>passif_21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>525, 1055</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>passif_22</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Régénération</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>hp_regeneration_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>746, 671</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>passif_23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>crit_chance_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>348, -290</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>passif_24</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>141, -376</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>passif_25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Assassin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>grant_class → [assassin]
+crit_chance_multiplier → [2]
+crit_damage_multiplier → [3]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Deg. Crit., Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-80, -405</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>🥷</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Double ses chances de critique et triple ses dégats critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>passif_26</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Deg. Crit.</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → [5]</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>-301, -376</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>passif_27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chance Crit.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Stats Avancées</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>crit_chance_flat → [1]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-507, -290</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>passif_28</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Vaillant</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Défense</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>taunt_chance_percent → [50]</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Vitesse, Vitesse</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>414, 735</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Durant le combat à 50% de chance d'appliquer provocation sur l'ennemi, la prochaine attaque de l'ennemi devra cibler en priorité le lanceur de provocation, si plusieurs joueurs on lancé provocation, seul le dernier lanceur sera ciblé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>passif_29</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>heal_buff_percent → [10]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Vitesse, Vitesse</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-574, 735</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>💊</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Les soins accordent également un bonus pour le combat de 10% d'attaque et 10% de défense sur la cible du soin et sur soit même, non cumulable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>actif_4</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Léthal</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Attaque</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>armor_penetration_percent → [10]</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Vitesse, Vitesse</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>-80, -120</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>🗡️</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Ignore 10% de la défense ennemie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>axe_or_1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bonus Or</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,4,10]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1224, 379</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>axe_drop_1</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Chance Drop</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [10,40,100]</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Bonus Or, Bonus XP</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>1090, 530</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>🍀</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>axe_xp_1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bonus XP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,4,10]</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>956, 379</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>axe_confort_1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>unlock_feature → [tower_bonus_ticket]</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Chance Drop</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>1090, 720</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>+1 ticket par jour pour la tour solo (non cumulable : 1 maximum par jour).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>axe_or_2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bonus Or</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>gold_drop_percent → [1,4,10]</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1224, 854</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>axe_drop_2</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Chance Drop</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr"/>
+      <c r="F82" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_multiplier → [10,40,100]</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Bonus Or, Bonus XP</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>toutes</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>1090, 1005</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>🍀</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>axe_xp_2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bonus XP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>xp_drop_percent → [1,4,10]</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>956, 854</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>axe_confort_2</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Confort</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Utilité</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr"/>
+      <c r="F84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>unlock_feature → [notify_events]</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Chance Drop</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>1090, 1195</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>Reçois un message privé quand un événement apparaît.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M43"/>
+  <autoFilter ref="A1:M84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-20 18:20 UTC</t>
+          <t>Généré le 2026-10-20 23:51 UTC</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>64</v>
@@ -912,8 +912,8 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 5
-auto_heal_per_turn = 50</t>
+          <t>damage_immunity_threshold = 7
+auto_heal_per_turn = 14</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E3" t="n">
         <v>114</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>28000</v>
+        <v>22000</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>164</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 50
+          <t>damage_immunity_threshold = 30
 reflect_pct = 15</t>
         </is>
       </c>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="E5" t="n">
         <v>214</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>41000</v>
+        <v>15000</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>264</v>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 100
+          <t>damage_immunity_threshold = 46
 enrage_below_pct = 25
 enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 2000
+auto_heal_per_turn = 20
 reflect_pct = 20
-adds = {'attack': 250, 'summon_turn_interval': 5, 'max_active': 2}
+adds = {'attack': 158, 'summon_turn_interval': 5, 'max_active': 2}
 phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
         </is>
       </c>
@@ -7263,13 +7263,13 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>5</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>40</v>
@@ -7338,13 +7338,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -7413,13 +7413,13 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -7638,13 +7638,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>317</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>610</v>
+        <v>366</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -8238,13 +8238,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>858</v>
+        <v>515</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>5</v>
@@ -8913,13 +8913,13 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1832</v>
+        <v>1099</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>5</v>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-20 23:51 UTC</t>
+          <t>Généré le 2026-10-21 10:16 UTC</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16734,17 +16734,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>taverne_addict</t>
+          <t>habitue_taverne</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Taverne Addict</t>
+          <t>Habitué de la taverne</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>🍺</t>
+          <t>🍻</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -16759,34 +16759,34 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>daily_bonus_item → target=potion_soin, value=1</t>
+          <t>gold_xp_bonus_pct → value=1</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Daily streak de 30 jours. Reçoit en bonus une potion de soin à chaque /daily (en plus de l'or).</t>
+          <t>Série /daily de 7 jours. +1 % sur l'or et l'XP gagnés en combat.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>slime_chasseur_legendaire</t>
+          <t>taverne_addict</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Slime</t>
+          <t>Taverne Addict</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>🍺</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16796,39 +16796,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>kills_mob</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>slime / 50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
+          <t>Série /daily de 30 jours. +3 % de dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chasseur_legendaire</t>
+          <t>pilier_taverne</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin</t>
+          <t>Pilier de la taverne</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>🏛️</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -16838,34 +16838,34 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>kills_mob</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>gobelin / 50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
+          <t>gold_xp_bonus_pct → value=2</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
+          <t>Série /daily de 100 jours. +2 % sur l'or et l'XP gagnés en combat.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gobelin_combattant_chasseur_legendaire</t>
+          <t>slime_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Combattant</t>
+          <t>Chasseur Légendaire — Slime</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16885,29 +16885,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>gobelin_combattant / 50</t>
+          <t>slime / 50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
+          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman_chasseur_legendaire</t>
+          <t>gobelin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Chaman</t>
+          <t>Chasseur Légendaire — Gobelin</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -16927,29 +16927,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman / 50</t>
+          <t>gobelin / 50</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gobelin_geant_chasseur_legendaire</t>
+          <t>gobelin_combattant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Géant</t>
+          <t>Chasseur Légendaire — Gobelin Combattant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -16969,29 +16969,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>gobelin_geant / 50</t>
+          <t>gobelin_combattant / 50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_runique_chasseur_legendaire</t>
+          <t>gobelin_chaman_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Runique</t>
+          <t>Chasseur Légendaire — Gobelin Chaman</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -17011,29 +17011,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_runique / 50</t>
+          <t>gobelin_chaman / 50</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gobelin_ballon_chasseur_legendaire</t>
+          <t>gobelin_geant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Ballon</t>
+          <t>Chasseur Légendaire — Gobelin Géant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17053,29 +17053,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>gobelin_ballon / 50</t>
+          <t>gobelin_geant / 50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>gobelin_assassin_chasseur_legendaire</t>
+          <t>gobelin_runique_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Assassin</t>
+          <t>Chasseur Légendaire — Gobelin Runique</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -17095,29 +17095,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>gobelin_assassin / 50</t>
+          <t>gobelin_runique / 50</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gobelin_superieur_chasseur_legendaire</t>
+          <t>gobelin_ballon_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Supérieur</t>
+          <t>Chasseur Légendaire — Gobelin Ballon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -17137,76 +17137,76 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>gobelin_superieur / 50</t>
+          <t>gobelin_ballon / 50</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>mvp_world_boss</t>
+          <t>gobelin_assassin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MVP des World Boss</t>
+          <t>Chasseur Légendaire — Gobelin Assassin</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>🏆</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>world_boss_mvp</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>gobelin_assassin / 50</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>champion_all_stats → value=2</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
+          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tueur_slime_titan</t>
+          <t>gobelin_superieur_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tueur du Titan Visqueux</t>
+          <t>Chasseur Légendaire — Gobelin Supérieur</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17216,76 +17216,76 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>slime_titan / 1</t>
+          <t>gobelin_superieur / 50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
+          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>tueur_gobelin_warlord</t>
+          <t>mvp_world_boss</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Seigneur de Guerre Gobelin</t>
+          <t>MVP des World Boss</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🏆</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>world_boss_mvp</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>gobelin_warlord / 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>champion_all_stats → value=2</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
+          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tueur_stone_colossus</t>
+          <t>tueur_slime_titan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tueur du Colosse de Pierre</t>
+          <t>Tueur du Titan Visqueux</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stone_colossus / 1</t>
+          <t>slime_titan / 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -17315,19 +17315,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>tueur_shadow_wraith</t>
+          <t>tueur_gobelin_warlord</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Spectre des Ténèbres</t>
+          <t>Tueur du Seigneur de Guerre Gobelin</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>shadow_wraith / 1</t>
+          <t>gobelin_warlord / 1</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -17357,19 +17357,19 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tueur_ancient_dragon</t>
+          <t>tueur_stone_colossus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tueur du Dragon Ancestral</t>
+          <t>Tueur du Colosse de Pierre</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ancient_dragon / 1</t>
+          <t>stone_colossus / 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -17399,42 +17399,126 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>tueur_shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>shadow_wraith / 1</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tueur_ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tueur du Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ancient_dragon / 1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>ma_survie_avant_tout</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Ma survie avant tout</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>🛡️</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>dodge_flat → value=1
 speed_flat → value=1
@@ -17442,14 +17526,14 @@
 hp_max_flat → value=200</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>A ignoré une « petite fille » qui s'est révélée être un monstre déguisé — l'instinct de survie récompensé. Esquive +1%, Vitesse +1, Défense +10, PV max +200.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -21,11 +21,11 @@
     <sheet name="⚙️ Calibrage" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$U$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-21 10:16 UTC</t>
+          <t>Généré le 2026-10-23 23:07 UTC</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOUS les équipements en 1 feuille. Filtre par Type (casque…) ou Panoplie via les flèches d'en-tête. Power calculé en direct.</t>
+          <t>Les 23 pièces (stats du COMMUN), le monstre qui la porte et son passif. Power calculé au niveau 30.</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recettes /craft et /forge.</t>
+          <t>Recettes (vide : la fabrication a été remplacée par la fusion).</t>
         </is>
       </c>
     </row>
@@ -890,13 +890,13 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>8</v>
@@ -912,8 +912,8 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 7
-auto_heal_per_turn = 14</t>
+          <t>damage_immunity_threshold = 6
+auto_heal_per_turn = 11</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -938,13 +938,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>12</v>
@@ -962,7 +962,7 @@
         <is>
           <t>enrage_below_pct = 30
 enrage_attack_multiplier = 1.5
-adds = {'attack': 80, 'summon_turn_interval': 4, 'max_active': 3}</t>
+adds = {'attack': 79, 'summon_turn_interval': 4, 'max_active': 3}</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -987,13 +987,13 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 30
+          <t>damage_immunity_threshold = 28
 reflect_pct = 15</t>
         </is>
       </c>
@@ -1038,10 +1038,10 @@
         <v>13000</v>
       </c>
       <c r="E5" t="n">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
         <v>18</v>
@@ -1086,10 +1086,10 @@
         <v>15000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>15</v>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 46
+          <t>damage_immunity_threshold = 44
 enrage_below_pct = 25
 enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 20
+auto_heal_per_turn = 19
 reflect_pct = 20
-adds = {'attack': 158, 'summon_turn_interval': 5, 'max_active': 2}
+adds = {'attack': 182, 'summon_turn_interval': 5, 'max_active': 2}
 phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
         </is>
       </c>
@@ -1533,17 +1533,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -1555,8 +1555,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1582,24 +1581,24 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>Porté par</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Passif (dès épique)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Panoplie</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Rareté</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>2-mains</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Niv. requis</t>
-        </is>
-      </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Atk %</t>
@@ -1656,11 +1655,6 @@
         </is>
       </c>
       <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Prix achat</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1669,12 +1663,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>baton_de_sorcier</t>
+          <t>baton_du_crane_totem</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Baton de sorcier</t>
+          <t>Bâton du crâne-totem</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -1687,19 +1681,21 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Chaman</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+          <t>Mains guérisseuses — Tes soins donnés sont augmentés de 10 %, et 10 % des soins que tu donnes à un allié frappent aussi l'ennemi.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>8</v>
@@ -1720,41 +1716,35 @@
         <v>0</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>(D6)
-craft : boi ,drop du chaman
-niv3-5
-+50mana</t>
+        <v>60</v>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>Le crâne au sommet murmure encore des incantations.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>baton_simple</t>
+          <t>fendoir_d_orage</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baton simple</t>
+          <t>Fendoir d'orage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1767,19 +1757,21 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ogre démoniaque</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Tueur de boss — +15 % de dégâts contre les boss.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>non</t>
         </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
@@ -1788,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1812,26 +1804,23 @@
         <v>0</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>80</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>(D1)</t>
+        <v>69</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>La foudre court le long du tranchant.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>bouclier_simple</t>
+          <t>massue_du_chef_de_guerre</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Bouclier simple</t>
+          <t>Massue du chef de guerre</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1844,34 +1833,36 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Supérieur</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+          <t>Fureur montante — Chaque attaque augmente ton attaque de 1 % pour le combat (max +20 %).</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" s="5" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
@@ -1889,26 +1880,23 @@
         <v>0</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>(D2)</t>
+        <v>64</v>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>Chaque pointe porte le nom d'un ennemi tombé.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>boulet_hante</t>
+          <t>surin_dentele</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boulet hanté</t>
+          <t>Surin dentelé</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1921,31 +1909,33 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gobelin</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Frappe d'ouverture — Ta première attaque est forcément critique ; si elle l'était déjà, c'est un super-critique (les deux critiques se cumulent).</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>25</v>
-      </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1954,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1966,22 +1956,23 @@
         <v>0</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Une lame courbe ébréchée, plus rapide que la pensée d'un gobelin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>baton_a_crane</t>
+          <t>trident_ricaneur</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Bâton à crâne</t>
+          <t>Trident ricaneur</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1994,22 +1985,24 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Diablotin</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+          <t>Coup double — 10 % de chance d'attaquer deux fois d'affilée.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>25</v>
-      </c>
       <c r="I6" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
@@ -2021,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
@@ -2033,28 +2026,29 @@
         <v>0</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>On jurerait l'entendre rire à chaque coup.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dragon_heart</t>
+          <t>tronc_arrache</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cœur du Dragon Ancestral</t>
+          <t>Tronc arraché</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2067,40 +2061,42 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gobelin Géant</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>70</v>
+          <t>Exécuteur — +20 % de dégâts contre un ennemi sous 50 % de ses PV.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -2112,26 +2108,23 @@
         <v>0</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>1856</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Il bat encore. On l'entend quand le combat se tait.</t>
+        <v>141</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Un arbre entier, déraciné à mains nues.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>dague_rouillee</t>
+          <t>epee_de_l_ossuaire</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Dague rouillée</t>
+          <t>Épée de l'ossuaire</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2144,22 +2137,24 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Squelette</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+          <t>Perce-armure — Tes coups ignorent 15 % de la défense ennemie.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="I8" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -2189,27 +2184,28 @@
         <v>0</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>Rouillée, mais elle trouve toujours le défaut de l'armure.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dague_simple</t>
+          <t>pavois_de_granit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dague simple</t>
+          <t>Pavois de granit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2217,34 +2213,36 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Gargouille</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>Peau de pierre — Chaque coup subi augmente ta défense de 1 % pour le combat (max +20 %).</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2262,31 +2260,28 @@
         <v>0</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>80</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>(D3)</t>
+        <v>35</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Plus on le frappe, plus il se durcit.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>dagues_jumelles</t>
+          <t>egide_du_damne</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Dagues jumelles</t>
+          <t>Égide du Damné</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2294,34 +2289,36 @@
           <t>arme</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Archidémon</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>25</v>
+          <t>Épines — Chaque coup subi renvoie 10 % de ta défense en dégâts à l'attaquant.</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>0</v>
@@ -2339,145 +2336,147 @@
         <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>113</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>Une paire de dagues gobelines bien affutées.</t>
+        <v>35</v>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>Le crâne serti mord ceux qui frappent.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>espadon_dentele</t>
+          <t>couronne_de_la_liche</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Espadon denté</t>
+          <t>Couronne de la Liche</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Liche maudite</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>Anti-soin — Les soins de l'ennemi sont divisés par deux.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>45</v>
-      </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>15</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="J11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Là où elle passe, rien ne guérit.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>faux</t>
+          <t>diademe_hurlant</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Faux</t>
+          <t>Diadème hurlant</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Banshee</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+          <t>Cri affaiblissant — L'attaque de l'ennemi est réduite de 5 %.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" s="5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>0</v>
@@ -2489,65 +2488,62 @@
         <v>0</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>(D3)
-craft :fer ,boi ,griffe de goblin 
-niv 5-10</t>
+        <v>34</v>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>Son cri glace le bras qui s'apprête à frapper.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gourdin_de_tronc</t>
+          <t>heaume_aux_cornes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gourdin de tronc</t>
+          <t>Heaume aux cornes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>tete</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Démon cornu</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+          <t>Défi — Tu commences le combat en provocation, et tu subis 15 % de dégâts en moins tant qu'elle dure.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>25</v>
-      </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2556,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -2568,59 +2564,62 @@
         <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Impossible de l'ignorer sur un champ de bataille.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>griffe_noircie</t>
+          <t>bandelettes_embaumees</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Griffe noircie</t>
+          <t>Bandelettes embaumées</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Momie</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+          <t>Bandelettes protectrices — Les dégâts critiques que tu reçois sont réduits de 25 %.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="I14" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0</v>
@@ -2641,62 +2640,65 @@
         <v>0</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>Imprégnées d'huiles qui amortissent les coups.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lame_des_enfers</t>
+          <t>cape_de_nuit_sans_lune</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lame des enfers</t>
+          <t>Cape de nuit sans lune</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gobelin Assassin</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+          <t>Pas de l'ombre — Après une esquive : ta prochaine action fait 10 % de plus, et le prochain coup que tu reçois 10 % de moins.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>70</v>
-      </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2714,59 +2716,62 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>1501</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Elle boit la lumière autour d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>warlord_blade</t>
+          <t>cuirasse_de_l_exil</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Lame du Seigneur de Guerre</t>
+          <t>Cuirasse de l'exil</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Ange déchu</t>
+        </is>
+      </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
+          <t>Garde de l'exil — La première attaque que tu reçois est annulée.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>45</v>
-      </c>
       <c r="I16" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>0</v>
@@ -2775,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>0</v>
@@ -2787,66 +2792,65 @@
         <v>0</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>551</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>L'acier ébréché d'un chef gobelin qui n'a jamais reculé.</t>
+        <v>43</v>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>Forgée au ciel, ternie en enfer.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lame_infernale</t>
+          <t>haillons_du_revenant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lame infernale</t>
+          <t>Haillons du revenant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Zombie</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>Revenant — La première fois que tu meurs, tu reviens à la vie avec 50 % de tes PV.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>25</v>
-      </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2864,68 +2868,71 @@
         <v>0</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Ils ont déjà vu leur porteur mourir. Une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>masse_cloutee</t>
+          <t>peau_de_loup_du_lutteur</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Masse cloutée</t>
+          <t>Peau de loup du lutteur</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Combattant</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+          <t>Riposte — 10 % de chance de contre-attaquer à chaque coup subi.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>45</v>
-      </c>
       <c r="I18" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>0</v>
@@ -2937,123 +2944,129 @@
         <v>0</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>344</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>L'odeur du loup rend téméraire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trident_ebreche</t>
+          <t>baiser_de_la_succube</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trident ébréché</t>
+          <t>Baiser de la Succube</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Succube</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>Volonté de fer — Tu es immunisé au charme.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>10</v>
-      </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Qui l'a reçu ne craint plus aucun charme.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>bracelet_runique</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>arc</t>
+          <t>Bracelet runique</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Runique</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+          <t>Puissance élémentaire — Tes dégâts élémentaires sont augmentés de 10 %.</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
@@ -3068,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
@@ -3077,84 +3090,80 @@
         <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>(D8)
-(snipeur) ta première ataque inflige +5dégat
-craft: bois tissu ,grifes de goblin, dent de goblin
-niv 5-8</t>
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>Les runes s'éveillent au contact des éléments.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>boucli_piquant</t>
+          <t>chaine_de_l_ame_errante</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bouclié piquant</t>
+          <t>Chaîne de l'âme errante</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fantôme</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+          <t>Chasseur d'essences — Chaque monstre tué te donne 1 essence de plus de son élément.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3163,57 +3172,53 @@
         <v>0</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>(D2),(D4)
-quand un énémie l'ataque il perd 2pv
-craft: bois ,fer ,dent de goblin ,griffe de goblin
-niv 5-10</t>
+        <v>18</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Elle attire les âmes des vaincus.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>grife_nergis_e_d6_energis_e_10_du_mana_en_attaque</t>
+          <t>collier_du_gardien</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>grife énergisée (D6) energisée (+10% du mana en attaque)</t>
+          <t>Collier du gardien</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Cerbère</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+          <t>Ténacité — Le premier coup mortel que tu reçois te laisse à 1 PV.</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>25</v>
-      </c>
       <c r="I22" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>0</v>
@@ -3231,62 +3236,65 @@
         <v>0</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>Le gardien des enfers ne lâche jamais prise.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hache</t>
+          <t>grenade_de_suie</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hache</t>
+          <t>Grenade de suie</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gobelin Ballon</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>Pare-souffle — Les dégâts de zone que tu reçois sont réduits de 50 %.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3298,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3307,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -3316,56 +3324,53 @@
         <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>(D4)
-craft: fer ,bois ,gelé de slime ,griff de goblin
-niv 5-8</t>
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>On apprend vite à se protéger des explosions.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>katana</t>
+          <t>perle_de_gelee</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>katana (D7)</t>
+          <t>Perle de gelée</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Arme</t>
+          <t>Accessoire</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+          <t>Trouvaille — Tes chances de butin d'équipement sont augmentées de 10 % (1 % devient 1,1 %).</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>25</v>
-      </c>
       <c r="I24" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>0</v>
@@ -3374,10 +3379,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>0</v>
@@ -3386,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0</v>
@@ -3395,3715 +3400,17 @@
         <v>0</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>155</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>masse</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>masse</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>(D5)
-craft :fer, grif de goblin, dent de goblin
-niv 3-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>sabre</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>sabre</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>(D4)
-craft fer ,gelé de slime ,griffe de goblin
-niv 5-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>p_d_scrime</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>épé d'éscrime</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>10</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>(D1)
-craft bois ,fer, gelé de slime
-niv 5-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>p_simple</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>épé simple</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Arme</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>(D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>grimoire_en_lambeaux</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Grimoire en lambeaux</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Bouclier</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>30</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>orbe_maudit</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Orbe maudit</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Bouclier</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>casque</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Casque</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>80</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>(D2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>casque_piquant</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Casque piquant</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>(D4)(D5)
-craft: grife de goblin ,fer
-Niv 5-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>casque_a_cornes</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Casque à cornes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>25</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>16</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>couronne_d_epines</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Couronne d'épines</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>couronne_dechue</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Couronne déchue</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>70</v>
-      </c>
-      <c r="I35" t="n">
-        <v>18</v>
-      </c>
-      <c r="J35" t="n">
-        <v>18</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>15</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>40</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>1061</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>couronne_ternie</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Couronne ternie</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>211</v>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>home_blind</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Home blindé</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>(D2)
-craft : fer, fourure ,gelé de slime
-niv 5-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>(D1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>80</v>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>(D4) (D6)
-+20 de mana aussi</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>casque_infligeur</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>casque infligeur</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>133</v>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>chapeau</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>chapeau</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-20</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>80</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>(D4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>chapeau_de_sorcier</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>chapeau de sorcier</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="7" t="inlineStr">
-        <is>
-          <t>(D6)
-craft :tissu + drop du chaman goblin
-niv 3-5
-+50man</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>lunette_de_pr_cision_d8_snipeur_20_de_degat_a_la_premi_re_attaque</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>lunette de précision (D8) snipeur+20% de degat a la première attaque</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>25</v>
-      </c>
-      <c r="I43" t="n">
-        <v>18</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M43" t="n">
-        <v>10</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1200</v>
-      </c>
-      <c r="U43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>masque_de_camouflage</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>masque de camouflage</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Tête</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="7" t="inlineStr">
-        <is>
-          <t>(D3)
-craft ,tissu ,gelé de slime ,fourure
-niv 3-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>corset_de_soie_noire</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Corset de soie noire</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>45</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>8</v>
-      </c>
-      <c r="O45" t="n">
-        <v>4</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="6" t="n">
-        <v>263</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>plaque_rouillee</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Plaque rouillée</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="T46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>plaque_a_pointes</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Plaque à pointes</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>25</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>16</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>colossus_plate</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Plastron du Colosse</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="6" t="n">
-        <v>163</v>
-      </c>
-      <c r="T48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>Une plaque de granit vivant, taillée dans le Colosse lui-même.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>tenu_d_aventurier_niv_goblin</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Tenu d'aventurier niv goblin</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>(D4)(D5)  
-craft : tissu ,fourure et dent de goblin
-équipement de niv 3-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>v_tement_vagabon</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Vétement vagabon</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>(D1) (D3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>armure_a_suspention_visceuse</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>armure a suspention visceuse</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>(D2)
-craft: fer beaucoup ,gelé de slime beaucoup
-niv 3-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>armure_de_garde</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>armure de garde</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>-20</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>(D2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>armure_de_m_tal_sup_rieur_d4</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>armure de métal supérieur (D2)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>25</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" t="n">
-        <v>12</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1600</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>exo_squelette_exp_rimental_d5_d4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>exo squelette expérimental (D5)(D4)</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>robe</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>robe</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>8</v>
-      </c>
-      <c r="L55" t="n">
-        <v>5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>10</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T55" t="n">
-        <v>120</v>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>(D3)(D6)
-+30 mana</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>tenu_d_aprentie</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>tenu d'aprentie</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="7" t="inlineStr">
-        <is>
-          <t>(D6)(D5)
-craft :fourure ,tissu et (un drop du goblin chaman 
-Niv 5-8
-+100pt de mana</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>tenu_d_aventurier</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>tenu d'aventurier</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>120</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>(D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>tenu_de_mercen_re</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>tenu de mercenère</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Corps</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="7" t="inlineStr">
-        <is>
-          <t>(D3)(D8)
-craft: tissu ,fourures ,griff de goblin
-niv 5-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>aile_de_cuir</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Aile de cuir</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>25</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4</v>
-      </c>
-      <c r="O59" t="n">
-        <v>5</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>aile_de_pierre</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Aile de pierre</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="5" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>brassard_de_cuir</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Brassard de cuir</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>10</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>12</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>wraith_cloak</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Cape du Spectre</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S62" s="6" t="n">
-        <v>1642</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="5" t="inlineStr">
-        <is>
-          <t>Elle ne projette aucune ombre. Ceux qui la portent non plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cape_silencieuse</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Cape silencieuse</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>45</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>5</v>
-      </c>
-      <c r="M63" t="n">
-        <v>10</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="6" t="n">
-        <v>124</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Annule la première attaque subie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>ceinturon_cloute</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Ceinturon clouté</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="5" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ceinturon_epais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Ceinturon épais</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>10</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>8</v>
-      </c>
-      <c r="K65" t="n">
-        <v>4</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>chaine_de_l_abime</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Chaîne de l'abîme</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="T66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>chaine_spectrale</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Chaîne spectrale</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>25</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>15</v>
-      </c>
-      <c r="K67" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>collier_de_perles</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Collier de perles</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="R68" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>collier_a_pointes</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Collier à pointes</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>25</v>
-      </c>
-      <c r="I69" t="n">
-        <v>10</v>
-      </c>
-      <c r="J69" t="n">
-        <v>8</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>titan_gel_core</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Cœur de Gel du Titan</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q70" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="R70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="T70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5" t="inlineStr">
-        <is>
-          <t>Un noyau de gelée qui bat encore, arraché au Titan Visqueux.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fetiche_d_os</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Fétiche d'os</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>10</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>10</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>sceau_de_corruption</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Sceau de corruption</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="6" t="n">
-        <v>1175</v>
-      </c>
-      <c r="T72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>voile_ectoplasmique</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Voile ectoplasmique</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>25</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>6</v>
-      </c>
-      <c r="O73" t="n">
-        <v>3</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>Tout ce qui tombe y reste collé.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U73"/>
-  <conditionalFormatting sqref="S2:S73">
+  <autoFilter ref="A1:T24"/>
+  <conditionalFormatting sqref="S2:S24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7338,13 +3645,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E3" t="n">
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -7413,13 +3720,13 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -7456,7 +3763,6 @@
       <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>cuir_brut ×1-2 (22%)
-brassard_de_cuir ×1-1 (5%)
 silex ×1-2 (15%)</t>
         </is>
       </c>
@@ -7488,13 +3794,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -7531,8 +3837,7 @@
       <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>os_poli ×1-2 (22%)
-poussiere_d_ossements ×1-2 (18%)
-dague_rouillee ×1-1 (5%)</t>
+poussiere_d_ossements ×1-2 (18%)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -7563,13 +3868,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>5</v>
@@ -7603,11 +3908,9 @@
         <f>IFERROR(VLOOKUP(O6,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>gourde_de_chaman ×1-1 (20%)
-fetiche_d_os ×1-1 (5%)
-baton_a_crane ×1-1 (2%)</t>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>gourde_de_chaman ×1-1 (20%)</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
@@ -7638,13 +3941,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>317</v>
+        <v>248</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -7713,13 +4016,13 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>363</v>
+        <v>286</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>5</v>
@@ -7788,13 +4091,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -7828,11 +4131,9 @@
         <f>IFERROR(VLOOKUP(O9,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>os_massif ×1-2 (22%)
-ceinturon_epais ×1-1 (5%)
-gourdin_de_tronc ×1-1 (2%)</t>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>os_massif ×1-2 (22%)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -7863,13 +4164,13 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>5</v>
@@ -7906,8 +4207,7 @@
       <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>bandelette_maudite ×1-2 (22%)
-resine_d_embaumement ×1-1 (10%)
-griffe_noircie ×1-1 (5%)</t>
+resine_d_embaumement ×1-1 (10%)</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
@@ -7938,13 +4238,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
@@ -7981,8 +4281,7 @@
       <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>encre_rituelle ×1-2 (20%)
-pierre_runique ×1-1 (10%)
-collier_de_perles ×1-1 (4%)</t>
+pierre_runique ×1-1 (10%)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -8013,13 +4312,13 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>9</v>
@@ -8053,13 +4352,7 @@
         <f>IFERROR(VLOOKUP(O12,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>voile_ectoplasmique ×1-1 (4%)
-chaine_spectrale ×1-1 (4%)
-boulet_hante ×1-1 (2%)</t>
-        </is>
-      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr">
         <is>
           <t>fantome.png</t>
@@ -8088,13 +4381,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>9</v>
@@ -8128,11 +4421,9 @@
         <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×1-2 (20%)
-dagues_jumelles ×1-1 (5%)
-cape_silencieuse ×1-1 (1%)</t>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>morceau_de_tissu ×1-2 (20%)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -8163,13 +4454,13 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>539</v>
+        <v>462</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>5</v>
@@ -8203,13 +4494,7 @@
         <f>IFERROR(VLOOKUP(O14,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>plaque_a_pointes ×1-1 (5%)
-casque_a_cornes ×1-1 (4%)
-masse_cloutee ×1-1 (1%)</t>
-        </is>
-      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr">
         <is>
           <t>gobelin_superieur.png</t>
@@ -8238,13 +4523,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>515</v>
+        <v>446</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
         <v>5</v>
@@ -8281,7 +4566,6 @@
       <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>eclat_de_pierre ×1-2 (22%)
-aile_de_pierre ×1-1 (4%)
 coeur_de_granit ×1-1 (3%)</t>
         </is>
       </c>
@@ -8313,13 +4597,13 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>9</v>
@@ -8356,8 +4640,7 @@
       <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>corne_naissante ×1-2 (22%)
-braise_infernale ×1-1 (10%)
-trident_ebreche ×1-1 (5%)</t>
+braise_infernale ×1-1 (10%)</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
@@ -8388,13 +4671,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>510</v>
+        <v>466</v>
       </c>
       <c r="E17" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>5</v>
@@ -8431,8 +4714,7 @@
       <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>echo_de_cri ×1-1 (18%)
-larme_spectrale ×1-1 (5%)
-couronne_d_epines ×1-1 (2%)</t>
+larme_spectrale ×1-1 (5%)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -8463,13 +4745,13 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>726</v>
+        <v>671</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>5</v>
@@ -8503,11 +4785,9 @@
         <f>IFERROR(VLOOKUP(O18,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>corne_de_demon ×1-2 (20%)
-ceinturon_cloute ×1-1 (5%)
-lame_infernale ×1-1 (2%)</t>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>corne_de_demon ×1-2 (20%)</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
@@ -8538,13 +4818,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>598</v>
+        <v>554</v>
       </c>
       <c r="E19" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
         <v>5</v>
@@ -8578,13 +4858,7 @@
         <f>IFERROR(VLOOKUP(O19,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>grimoire_en_lambeaux ×1-1 (5%)
-orbe_maudit ×1-1 (2%)
-couronne_ternie ×1-1 (1%)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>liche_maudite.png</t>
@@ -8613,13 +4887,13 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>5</v>
@@ -8653,11 +4927,9 @@
         <f>IFERROR(VLOOKUP(O20,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>croc_d_ogre ×1-2 (20%)
-plaque_rouillee ×1-1 (5%)
-espadon_dentele ×1-1 (1%)</t>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>croc_d_ogre ×1-2 (20%)</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
@@ -8688,13 +4960,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>924</v>
+        <v>902</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
         <v>5</v>
@@ -8728,11 +5000,9 @@
         <f>IFERROR(VLOOKUP(O21,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>croc_triple ×1-2 (12%)
-collier_a_pointes ×1-1 (5%)
-chaine_de_l_abime ×1-1 (3%)</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>croc_triple ×1-2 (12%)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8763,13 +5033,13 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>5</v>
@@ -8803,11 +5073,9 @@
         <f>IFERROR(VLOOKUP(O22,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>philtre_de_charme ×1-1 (10%)
-aile_de_cuir ×1-1 (5%)
-corset_de_soie_noire ×1-1 (2%)</t>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>philtre_de_charme ×1-1 (10%)</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
@@ -8838,13 +5106,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1111</v>
+        <v>1078</v>
       </c>
       <c r="E23" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
         <v>5</v>
@@ -8881,8 +5149,7 @@
       <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>plume_noircie ×1-2 (15%)
-flamme_sacree ×1-1 (5%)
-couronne_dechue ×1-1 (1%)</t>
+flamme_sacree ×1-1 (5%)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8913,13 +5180,13 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1099</v>
+        <v>1069</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>5</v>
@@ -8953,11 +5220,9 @@
         <f>IFERROR(VLOOKUP(O24,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>corne_d_archidemon ×1-1 (12%)
-sceau_de_corruption ×1-1 (2%)
-lame_des_enfers ×1-1 (1%)</t>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>corne_d_archidemon ×1-1 (12%)</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
@@ -10457,16 +6722,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10506,1140 +6771,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>baton_simple_recipe</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Baton simple</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>baton_simple</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>bois ×3
-silex ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>p_simple_recipe</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>épé simple</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>p_simple</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>silex ×2
-bois ×2
-cuir_brut ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>dague_rouillee_recipe</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Dague rouillée</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>dague_rouillee</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>silex ×3
-os_poli ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bandana_recipe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bandana</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>capuche_recipe</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>capuche</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>casque_recipe</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Casque</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>casque</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre ×3
-cuir_brut ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>armure_de_garde_recipe</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>armure de garde</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>armure_de_garde</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>cuir_brut ×4
-morceau_de_tissu ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tenu_d_aventurier_recipe</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>tenu d'aventurier</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>tenu_d_aventurier</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>cuir_brut ×5
-morceau_de_tissu ×3
-os_poli ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>arc_recipe</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>arc</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>arc</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>bois ×4
-corne_naissante ×2
-morceau_de_tissu ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>hache_recipe</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>hache</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hache</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre ×4
-bois ×3
-dent_de_gobelin ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>baton_a_crane_recipe</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Bâton à crâne</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>baton_a_crane</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>os_massif ×2
-poussiere_d_ossements ×3
-bois ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sabre_recipe</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>sabre</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>sabre</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>coeur_de_granit ×2
-silex ×4
-cuir_brut ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>casque_a_cornes_recipe</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Casque à cornes</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>casque_a_cornes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>corne_naissante ×3
-eclat_de_pierre ×3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>faux_recipe</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Faux</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>faux</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>os_massif ×3
-larme_spectrale ×2
-coeur_de_granit ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>plaque_rouillee_recipe</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Plaque rouillée</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>plaque_rouillee</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>corps</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>coeur_de_granit ×3
-eclat_de_pierre ×5
-resine_d_embaumement ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lame_infernale_recipe</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Lame infernale</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>lame_infernale</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>braise_infernale ×3
-corne_de_demon ×2
-coeur_de_granit ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>masse_cloutee_recipe</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Masse cloutée</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>masse_cloutee</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>coeur_de_granit ×4
-croc_d_ogre ×3
-os_massif ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lame_des_enfers_recipe</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Lame des enfers</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>lame_des_enfers</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>braise_infernale ×5
-corne_de_demon ×3
-c_ur_corrompu ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>couronne_dechue_recipe</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Couronne déchue</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>couronne_dechue</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>tete</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>diamant ×1
-pierre_runique ×3
-larme_spectrale ×4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>katana_recipe</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>katana (D7)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>katana</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>arme</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>diamant ×2
-coeur_de_granit ×5
-flamme_sacree ×1
-croc_triple ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>collier_de_perles_recipe</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Collier de perles</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>collier_de_perles</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>gel_e ×3
-morceau_de_tissu ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fetiche_d_os_recipe</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fétiche d'os</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>fetiche_d_os</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>os_poli ×3
-lambeau_de_vetement ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>cape_silencieuse_recipe</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Cape silencieuse</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>cape_silencieuse</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×4
-plume_noircie ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>aile_de_cuir_recipe</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Aile de cuir</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>aile_de_cuir</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>cuir_brut ×3
-dent_de_gobelin ×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>ceinturon_epais_recipe</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Ceinturon épais</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>ceinturon_epais</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>cuir_brut ×4
-os_poli ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>brassard_de_cuir_recipe</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Brassard de cuir</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>brassard_de_cuir</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>cuir_brut ×3
-morceau_de_tissu ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>chaine_spectrale_recipe</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Chaîne spectrale</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>chaine_spectrale</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>larme_spectrale ×3
-echo_de_cri ×2
-os_poli ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ceinturon_cloute_recipe</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ceinturon clouté</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ceinturon_cloute</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>cuir_brut ×5
-eclat_de_pierre ×3
-dent_gatee ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>aile_de_pierre_recipe</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Aile de pierre</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>aile_de_pierre</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre ×5
-coeur_de_granit ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>collier_a_pointes_recipe</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Collier à pointes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>collier_a_pointes</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>croc_d_ogre ×3
-corne_naissante ×2
-cuir_brut ×2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>sceau_de_corruption_recipe</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Sceau de corruption</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>sceau_de_corruption</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>accessoire</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>c_ur_corrompu ×2
-encre_rituelle ×2
-pierre_runique ×2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -16,9 +16,8 @@
     <sheet name="🏪 Shop" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="🌳 Skill Tree" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="🏷️ Titres" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="🌸 Panoplies" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="🐉 World Bosses" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="⚙️ Calibrage" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="🐉 World Bosses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="⚙️ Calibrage" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$24</definedName>
@@ -29,8 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🌸 Panoplies'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-23 23:07 UTC</t>
+          <t>Généré le 2026-10-24 12:41 UTC</t>
         </is>
       </c>
     </row>
@@ -616,93 +614,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>🌸 Panoplies</t>
+          <t>🐉 World Bosses</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Familles de set + paliers de bonus.</t>
+          <t>Bosses + modifiers.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>🐉 World Bosses</t>
+          <t>⚙️ Calibrage</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bosses + modifiers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>⚙️ Calibrage</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
           <t>Constantes du score de puissance. NE PAS supprimer.</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>🛠️ Comment équilibrer (round-trip)</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>🛠️ Comment équilibrer (round-trip)</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
+          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
+          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
+          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
+          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
-        <is>
-          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
         <is>
           <t>Power d'un équipement = puissance MARGINALE qu'il ajoute à un perso de base (power(base+item) − power(base)).</t>
         </is>
@@ -714,79 +700,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Code famille</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Icône</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Items existants</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Palier 2</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Palier 4</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Palier 8</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Palier 12</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1129,7 +1042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3360,7 +3273,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Trouvaille — Tes chances de butin d'équipement sont augmentées de 10 % (1 % devient 1,1 %).</t>
+          <t>Trouvaille — Tes chances de butin d'équipement sont augmentées de 10 % (1 % devient 1,1 %), pour les raretés INFÉRIEURES à celle de cette pièce — jamais pour le mythique.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -20,10 +20,10 @@
     <sheet name="⚙️ Calibrage" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-24 12:41 UTC</t>
+          <t>Généré le 2026-10-24 12:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1446,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -1728,12 +1728,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>massue_du_chef_de_guerre</t>
+          <t>griffes_de_goule</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Massue du chef de guerre</t>
+          <t>Griffes de goule</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Supérieur</t>
+          <t>Goule</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Fureur montante — Chaque attaque augmente ton attaque de 1 % pour le combat (max +20 %).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1772,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
@@ -1793,23 +1793,23 @@
         <v>0</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>Chaque pointe porte le nom d'un ennemi tombé.</t>
+          <t>Des griffes jaunies montées sur un gantelet.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>surin_dentele</t>
+          <t>lance_des_kobolds</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Surin dentelé</t>
+          <t>Lance des kobolds</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gobelin</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Frappe d'ouverture — Ta première attaque est forcément critique ; si elle l'était déjà, c'est un super-critique (les deux critiques se cumulent).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1869,23 +1869,23 @@
         <v>0</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Une lame courbe ébréchée, plus rapide que la pensée d'un gobelin.</t>
+          <t>Une longue lance à crochets, faite pour tenir les dragons à distance.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>trident_ricaneur</t>
+          <t>massue_du_chef_de_guerre</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Trident ricaneur</t>
+          <t>Massue du chef de guerre</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Diablotin</t>
+          <t>Gobelin Supérieur</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Coup double — 10 % de chance d'attaquer deux fois d'affilée.</t>
+          <t>Fureur montante — Chaque attaque augmente ton attaque de 1 % pour le combat (max +20 %).</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
@@ -1945,23 +1945,23 @@
         <v>0</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>On jurerait l'entendre rire à chaque coup.</t>
+          <t>Chaque pointe porte le nom d'un ennemi tombé.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tronc_arrache</t>
+          <t>rapiere_ecarlate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tronc arraché</t>
+          <t>Rapière écarlate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1976,22 +1976,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gobelin Géant</t>
+          <t>Vampire noble</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Exécuteur — +20 % de dégâts contre un ennemi sous 50 % de ses PV.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2003,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -2021,23 +2021,23 @@
         <v>0</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Un arbre entier, déraciné à mains nues.</t>
+          <t>Fine, rapide, et toujours rouge.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>epee_de_l_ossuaire</t>
+          <t>surin_dentele</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Épée de l'ossuaire</t>
+          <t>Surin dentelé</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Squelette</t>
+          <t>Gobelin</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Perce-armure — Tes coups ignorent 15 % de la défense ennemie.</t>
+          <t>Frappe d'ouverture — Ta première attaque est forcément critique ; si elle l'était déjà, c'est un super-critique (les deux critiques se cumulent).</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0</v>
@@ -2097,28 +2097,28 @@
         <v>0</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>Rouillée, mais elle trouve toujours le défaut de l'armure.</t>
+          <t>Une lame courbe ébréchée, plus rapide que la pensée d'un gobelin.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pavois_de_granit</t>
+          <t>trident_ricaneur</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pavois de granit</t>
+          <t>Trident ricaneur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bouclier</t>
+          <t>Arme</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gargouille</t>
+          <t>Diablotin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peau de pierre — Chaque coup subi augmente ta défense de 1 % pour le combat (max +20 %).</t>
+          <t>Coup double — 10 % de chance d'attaquer deux fois d'affilée.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -2143,20 +2143,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -2173,28 +2173,28 @@
         <v>0</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Plus on le frappe, plus il se durcit.</t>
+          <t>On jurerait l'entendre rire à chaque coup.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>egide_du_damne</t>
+          <t>tronc_arrache</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Égide du Damné</t>
+          <t>Tronc arraché</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Bouclier</t>
+          <t>Arme</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2204,28 +2204,28 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Archidémon</t>
+          <t>Gobelin Géant</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Épines — Chaque coup subi renvoie 10 % de ta défense en dégâts à l'attaquant.</t>
+          <t>Exécuteur — +20 % de dégâts contre un ennemi sous 50 % de ses PV.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P10" s="5" t="n">
         <v>0</v>
@@ -2249,43 +2249,43 @@
         <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>Le crâne serti mord ceux qui frappent.</t>
+          <t>Un arbre entier, déraciné à mains nues.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>couronne_de_la_liche</t>
+          <t>epee_de_l_ossuaire</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Couronne de la Liche</t>
+          <t>Épée de l'ossuaire</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tête</t>
+          <t>Arme</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tete</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liche maudite</t>
+          <t>Squelette</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anti-soin — Les soins de l'ennemi sont divisés par deux.</t>
+          <t>Perce-armure — Tes coups ignorent 15 % de la défense ennemie.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -2295,16 +2295,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -2319,49 +2319,49 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Là où elle passe, rien ne guérit.</t>
+          <t>Rouillée, mais elle trouve toujours le défaut de l'armure.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>diademe_hurlant</t>
+          <t>pavois_de_granit</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Diadème hurlant</t>
+          <t>Pavois de granit</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Tête</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>tete</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Banshee</t>
+          <t>Gargouille</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Cri affaiblissant — L'attaque de l'ennemi est réduite de 5 %.</t>
+          <t>Peau de pierre — Chaque coup subi augmente ta défense de 1 % pour le combat (max +20 %).</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>0</v>
@@ -2401,43 +2401,43 @@
         <v>0</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>Son cri glace le bras qui s'apprête à frapper.</t>
+          <t>Plus on le frappe, plus il se durcit.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>heaume_aux_cornes</t>
+          <t>ecu_de_l_eclipse</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heaume aux cornes</t>
+          <t>Écu de l'éclipse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tête</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tete</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Démon cornu</t>
+          <t>Chevalier de l'éclipse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Défi — Tu commences le combat en provocation, et tu subis 15 % de dégâts en moins tant qu'elle dure.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2477,43 +2477,43 @@
         <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Impossible de l'ignorer sur un champ de bataille.</t>
+          <t>Un bouclier où le soleil ne se reflète plus.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>bandelettes_embaumees</t>
+          <t>egide_de_givre</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bandelettes embaumées</t>
+          <t>Égide de givre</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Momie</t>
+          <t>Dragon de givre</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Bandelettes protectrices — Les dégâts critiques que tu reçois sont réduits de 25 %.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0</v>
@@ -2553,43 +2553,43 @@
         <v>0</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>Imprégnées d'huiles qui amortissent les coups.</t>
+          <t>Un bouclier taillé dans une écaille gelée.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cape_de_nuit_sans_lune</t>
+          <t>egide_du_damne</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cape de nuit sans lune</t>
+          <t>Égide du Damné</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>Bouclier</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>arme</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gobelin Assassin</t>
+          <t>Archidémon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pas de l'ombre — Après une esquive : ta prochaine action fait 10 % de plus, et le prochain coup que tu reçois 10 % de moins.</t>
+          <t>Épines — Chaque coup subi renvoie 10 % de ta défense en dégâts à l'attaquant.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
         <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2629,43 +2629,43 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Elle boit la lumière autour d'elle.</t>
+          <t>Le crâne serti mord ceux qui frappent.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>cuirasse_de_l_exil</t>
+          <t>capuche_de_sang</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Cuirasse de l'exil</t>
+          <t>Capuche de sang</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Ange déchu</t>
+          <t>Sorcière de sang</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Garde de l'exil — La première attaque que tu reçois est annulée.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>6</v>
@@ -2699,49 +2699,49 @@
         <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>Forgée au ciel, ternie en enfer.</t>
+          <t>Le tissu ne sèche jamais tout à fait.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>haillons_du_revenant</t>
+          <t>couronne_de_la_liche</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Haillons du revenant</t>
+          <t>Couronne de la Liche</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Liche maudite</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revenant — La première fois que tu meurs, tu reviens à la vie avec 50 % de tes PV.</t>
+          <t>Anti-soin — Les soins de l'ennemi sont divisés par deux.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -2775,49 +2775,49 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Ils ont déjà vu leur porteur mourir. Une fois.</t>
+          <t>Là où elle passe, rien ne guérit.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>peau_de_loup_du_lutteur</t>
+          <t>couronne_du_heraut</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Peau de loup du lutteur</t>
+          <t>Couronne du héraut</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>corps</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Combattant</t>
+          <t>Héraut du vide</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Riposte — 10 % de chance de contre-attaquer à chaque coup subi.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>6</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="5" t="n">
         <v>0</v>
@@ -2857,43 +2857,43 @@
         <v>0</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>L'odeur du loup rend téméraire.</t>
+          <t>Une couronne d'obsidienne qui murmure.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>baiser_de_la_succube</t>
+          <t>diademe_hurlant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Baiser de la Succube</t>
+          <t>Diadème hurlant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Succube</t>
+          <t>Banshee</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Volonté de fer — Tu es immunisé au charme.</t>
+          <t>Cri affaiblissant — L'attaque de l'ennemi est réduite de 5 %.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2909,16 +2909,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2933,43 +2933,43 @@
         <v>0</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Qui l'a reçu ne craint plus aucun charme.</t>
+          <t>Son cri glace le bras qui s'apprête à frapper.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>bracelet_runique</t>
+          <t>heaume_aux_cornes</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bracelet runique</t>
+          <t>Heaume aux cornes</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Runique</t>
+          <t>Démon cornu</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Puissance élémentaire — Tes dégâts élémentaires sont augmentés de 10 %.</t>
+          <t>Défi — Tu commences le combat en provocation, et tu subis 15 % de dégâts en moins tant qu'elle dure.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>Les runes s'éveillent au contact des éléments.</t>
+          <t>Impossible de l'ignorer sur un champ de bataille.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chaine_de_l_ame_errante</t>
+          <t>heaume_crete_de_wyverne</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaîne de l'âme errante</t>
+          <t>Heaume-crête de wyverne</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fantôme</t>
+          <t>Wyverne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chasseur d'essences — Chaque monstre tué te donne 1 essence de plus de son élément.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -3070,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -3085,43 +3085,43 @@
         <v>0</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Elle attire les âmes des vaincus.</t>
+          <t>Un heaume léger orné d'une crête d'écailles.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>collier_du_gardien</t>
+          <t>ramure_d_esprit</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Collier du gardien</t>
+          <t>Ramure d'esprit</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Tête</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>tete</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Cerbère</t>
+          <t>Cerf-esprit</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Ténacité — Le premier coup mortel que tu reçois te laisse à 1 PV.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -3161,43 +3161,43 @@
         <v>0</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>Le gardien des enfers ne lâche jamais prise.</t>
+          <t>Des bois de cerf qui bourgeonnent encore.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>grenade_de_suie</t>
+          <t>bandelettes_embaumees</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grenade de suie</t>
+          <t>Bandelettes embaumées</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>corps</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gobelin Ballon</t>
+          <t>Momie</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pare-souffle — Les dégâts de zone que tu reçois sont réduits de 50 %.</t>
+          <t>Bandelettes protectrices — Les dégâts critiques que tu reçois sont réduits de 25 %.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3210,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3237,43 +3237,43 @@
         <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>On apprend vite à se protéger des explosions.</t>
+          <t>Imprégnées d'huiles qui amortissent les coups.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>perle_de_gelee</t>
+          <t>cape_de_nuit_sans_lune</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Perle de gelée</t>
+          <t>Cape de nuit sans lune</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Accessoire</t>
+          <t>Corps</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>accessoire</t>
+          <t>corps</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Slime</t>
+          <t>Gobelin Assassin</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Trouvaille — Tes chances de butin d'équipement sont augmentées de 10 % (1 % devient 1,1 %), pour les raretés INFÉRIEURES à celle de cette pièce — jamais pour le mythique.</t>
+          <t>Pas de l'ombre — Après une esquive : ta prochaine action fait 10 % de plus, et le prochain coup que tu reçois 10 % de moins.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0</v>
@@ -3304,26 +3304,2078 @@
         <v>0</v>
       </c>
       <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>Elle boit la lumière autour d'elle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cuirasse_de_l_exil</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cuirasse de l'exil</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ange déchu</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garde de l'exil — La première attaque que tu reçois est annulée.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Forgée au ciel, ternie en enfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>fourrure_de_pleine_lune</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Fourrure de pleine lune</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Loup-garou</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>Elle se hérisse quand la lune se cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>haillons_du_revenant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Haillons du revenant</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zombie</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revenant — La première fois que tu meurs, tu reviens à la vie avec 50 % de tes PV.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Ils ont déjà vu leur porteur mourir. Une fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>peau_de_loup_du_lutteur</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Peau de loup du lutteur</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Combattant</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Riposte — 10 % de chance de contre-attaquer à chaque coup subi.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>L'odeur du loup rend téméraire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pelisse_du_colosse</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pelisse du colosse</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>corps</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ours colosse</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Une fourrure si épaisse qu'aucune lame ne la traverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>aile_de_nuit</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Aile de nuit</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Chauve-souris géante</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>Une membrane noire, légère comme l'ombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aureole_brisee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Auréole brisée</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Séraphin brisé</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Un halo fendu, qui brille encore par moments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>bague_de_la_comtesse</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Bague de la comtesse</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Comtesse écarlate</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>Un rubis taillé en goutte de sang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>baiser_de_la_succube</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Baiser de la Succube</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Succube</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Volonté de fer — Tu es immunisé au charme.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Qui l'a reçu ne craint plus aucun charme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>bracelet_runique</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Bracelet runique</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Runique</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Puissance élémentaire — Tes dégâts élémentaires sont augmentés de 10 %.</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>Les runes s'éveillent au contact des éléments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>chaine_de_l_ame_errante</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chaîne de l'âme errante</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Fantôme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Chasseur d'essences — Chaque monstre tué te donne 1 essence de plus de son élément.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Elle attire les âmes des vaincus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>collier_du_gardien</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Collier du gardien</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Cerbère</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Ténacité — Le premier coup mortel que tu reçois te laisse à 1 PV.</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>Le gardien des enfers ne lâche jamais prise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>croc_du_loup_sacre</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Croc du loup sacré</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Loup sacré</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Porté en pendentif, il aiguise l'instinct du chasseur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>coeur_de_braise</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Cœur de braise</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Drake de braise</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>Une pierre rougeoyante, chaude au creux de la main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>coeur_de_mousse</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cœur de mousse</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Golem de mousse</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Une pierre verte qui palpite doucement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>coeur_du_neant</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Cœur du Néant</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Avatar du Néant</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>Il ne bat pas. Il attire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>coeur_du_dragon_ancien</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cœur du dragon ancien</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dragon ancien</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>9</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Il bat encore, lentement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>flammeche_captive</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Flammèche captive</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Dragonnet</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>Une petite flamme enfermée dans du verre, qui ne s'éteint jamais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fragment_de_neant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fragment de néant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Rejeton du néant</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>20</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Un morceau de rien, étrangement lourd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>grenade_de_suie</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Grenade de suie</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Gobelin Ballon</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Pare-souffle — Les dégâts de zone que tu reçois sont réduits de 50 %.</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>On apprend vite à se protéger des explosions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>machoire_du_devoreur</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mâchoire du dévoreur</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dévoreur</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>9</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Une mâchoire de dents noires, en collier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>perle_de_gelee</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Perle de gelée</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Trouvaille — Tes chances de butin d'équipement sont augmentées de 10 % (1 % devient 1,1 %), pour les raretés INFÉRIEURES à celle de cette pièce — jamais pour le mythique.</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="inlineStr">
         <is>
           <t>Tout ce qui tombe y reste collé.</t>
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>plume_d_orage</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Plume d'orage</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aigle-tempête</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Elle crépite entre les doigts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>sceau_du_gardien_draconique</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du gardien draconique</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Gardien draconique</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>Le sceau des gardiens du nid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tentacule_astral</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tentacule astral</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kraken astral</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Il ondule encore, entre les étoiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>ecaille_racine</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Écaille-racine</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Serpent des racines</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>Souple comme l'écorce, insaisissable comme le serpent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>oeil_de_verre_noir</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Œil de verre noir</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Accessoire</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>accessoire</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Œil errant</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>On y voit les points faibles de ses ennemis.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T24"/>
-  <conditionalFormatting sqref="S2:S24">
+  <autoFilter ref="A1:T51"/>
+  <conditionalFormatting sqref="S2:S51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3345,11 +5397,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -5149,9 +7201,1764 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>loup_sacre</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Loup sacré</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>356</v>
+      </c>
+      <c r="E25" t="n">
+        <v>76</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="n">
+        <v>150</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>288</v>
+      </c>
+      <c r="M25" t="n">
+        <v>138</v>
+      </c>
+      <c r="N25" t="n">
+        <v>40</v>
+      </c>
+      <c r="O25" s="6">
+        <f>ROUND((E25*(1+(H25/100)*MAX(0,I25-100)/100)*(1+G25/100))*((D25+F25*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J25/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="6">
+        <f>IFERROR(VLOOKUP(O25,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Gardien à la fourrure d'argent ; il chasse en meute depuis l'aube des temps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cerf_esprit</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Cerf-esprit</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>627</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O26" s="6">
+        <f>ROUND((E26*(1+(H26/100)*MAX(0,I26-100)/100)*(1+G26/100))*((D26+F26*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J26/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="6">
+        <f>IFERROR(VLOOKUP(O26,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>Un cerf translucide ; la forêt se tait sur son passage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>serpent_des_racines</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Serpent des racines</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>389</v>
+      </c>
+      <c r="E27" t="n">
+        <v>84</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
+        <v>150</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>312</v>
+      </c>
+      <c r="M27" t="n">
+        <v>150</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" s="6">
+        <f>ROUND((E27*(1+(H27/100)*MAX(0,I27-100)/100)*(1+G27/100))*((D27+F27*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J27/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="6">
+        <f>IFERROR(VLOOKUP(O27,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Il dort sous les racines et frappe d'un venin sylvestre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ours_colosse</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Ours colosse</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>537</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O28" s="6">
+        <f>ROUND((E28*(1+(H28/100)*MAX(0,I28-100)/100)*(1+G28/100))*((D28+F28*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J28/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="6">
+        <f>IFERROR(VLOOKUP(O28,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>Ses griffes fendent la pierre comme l'armure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>golem_de_mousse</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Golem de mousse</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>624</v>
+      </c>
+      <c r="E29" t="n">
+        <v>72</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>338</v>
+      </c>
+      <c r="M29" t="n">
+        <v>162</v>
+      </c>
+      <c r="N29" t="n">
+        <v>15</v>
+      </c>
+      <c r="O29" s="6">
+        <f>ROUND((E29*(1+(H29/100)*MAX(0,I29-100)/100)*(1+G29/100))*((D29+F29*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J29/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="6">
+        <f>IFERROR(VLOOKUP(O29,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Un rocher couvert de mousse qui repousse plus vite qu'on ne l'arrache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>aigle_tempete</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Aigle-tempête</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>primordial</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>436</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="6">
+        <f>ROUND((E30*(1+(H30/100)*MAX(0,I30-100)/100)*(1+G30/100))*((D30+F30*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J30/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="6">
+        <f>IFERROR(VLOOKUP(O30,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>Chacun de ses battements d'ailes soulève une bourrasque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>chauve_souris_geante</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chauve-souris géante</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>442</v>
+      </c>
+      <c r="E31" t="n">
+        <v>99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>150</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>356</v>
+      </c>
+      <c r="M31" t="n">
+        <v>171</v>
+      </c>
+      <c r="N31" t="n">
+        <v>40</v>
+      </c>
+      <c r="O31" s="6">
+        <f>ROUND((E31*(1+(H31/100)*MAX(0,I31-100)/100)*(1+G31/100))*((D31+F31*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J31/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="6">
+        <f>IFERROR(VLOOKUP(O31,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Elle surgit de l'éclipse par nuées entières.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>goule</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Goule</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>748</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>362</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" s="6">
+        <f>ROUND((E32*(1+(H32/100)*MAX(0,I32-100)/100)*(1+G32/100))*((D32+F32*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J32/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="6">
+        <f>IFERROR(VLOOKUP(O32,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>Elle rôde entre les tombes, affamée de chair fraîche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>loup_garou</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Loup-garou</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>625</v>
+      </c>
+      <c r="E33" t="n">
+        <v>176</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>100</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>375</v>
+      </c>
+      <c r="M33" t="n">
+        <v>180</v>
+      </c>
+      <c r="N33" t="n">
+        <v>25</v>
+      </c>
+      <c r="O33" s="6">
+        <f>ROUND((E33*(1+(H33/100)*MAX(0,I33-100)/100)*(1+G33/100))*((D33+F33*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J33/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P33" s="6">
+        <f>IFERROR(VLOOKUP(O33,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Sous l'éclipse, la bête l'emporte sur l'homme — et sa rage grandit avec ses blessures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>sorciere_de_sang</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Sorcière de sang</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>642</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O34" s="6">
+        <f>ROUND((E34*(1+(H34/100)*MAX(0,I34-100)/100)*(1+G34/100))*((D34+F34*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J34/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P34" s="6">
+        <f>IFERROR(VLOOKUP(O34,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Elle appelle ses familiers d'un murmure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>chevalier_de_l_eclipse</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chevalier de l'éclipse</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>752</v>
+      </c>
+      <c r="E35" t="n">
+        <v>89</v>
+      </c>
+      <c r="F35" t="n">
+        <v>46</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>100</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>400</v>
+      </c>
+      <c r="M35" t="n">
+        <v>192</v>
+      </c>
+      <c r="N35" t="n">
+        <v>15</v>
+      </c>
+      <c r="O35" s="6">
+        <f>ROUND((E35*(1+(H35/100)*MAX(0,I35-100)/100)*(1+G35/100))*((D35+F35*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J35/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P35" s="6">
+        <f>IFERROR(VLOOKUP(O35,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Son armure noire rend chaque coup à celui qui l'a porté.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>vampire_noble</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Vampire noble</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>412</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" s="6">
+        <f>ROUND((E36*(1+(H36/100)*MAX(0,I36-100)/100)*(1+G36/100))*((D36+F36*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J36/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P36" s="6">
+        <f>IFERROR(VLOOKUP(O36,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>Il boit la vie de ses adversaires avec élégance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>comtesse_ecarlate</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Comtesse écarlate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nocturne</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>521</v>
+      </c>
+      <c r="E37" t="n">
+        <v>119</v>
+      </c>
+      <c r="F37" t="n">
+        <v>28</v>
+      </c>
+      <c r="G37" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" t="n">
+        <v>150</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>419</v>
+      </c>
+      <c r="M37" t="n">
+        <v>201</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="6">
+        <f>ROUND((E37*(1+(H37/100)*MAX(0,I37-100)/100)*(1+G37/100))*((D37+F37*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J37/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P37" s="6">
+        <f>IFERROR(VLOOKUP(O37,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Un regard, et ses ennemis se battent pour elle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>kobold</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Kobold</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>880</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="O38" s="6">
+        <f>ROUND((E38*(1+(H38/100)*MAX(0,I38-100)/100)*(1+G38/100))*((D38+F38*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J38/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P38" s="6">
+        <f>IFERROR(VLOOKUP(O38,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>Petit, rusé, armé d'une lance trop grande pour lui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dragonnet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dragonnet</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>541</v>
+      </c>
+      <c r="E39" t="n">
+        <v>125</v>
+      </c>
+      <c r="F39" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" t="n">
+        <v>150</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>438</v>
+      </c>
+      <c r="M39" t="n">
+        <v>210</v>
+      </c>
+      <c r="N39" t="n">
+        <v>30</v>
+      </c>
+      <c r="O39" s="6">
+        <f>ROUND((E39*(1+(H39/100)*MAX(0,I39-100)/100)*(1+G39/100))*((D39+F39*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J39/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P39" s="6">
+        <f>IFERROR(VLOOKUP(O39,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Un jeune dragon, vif et capricieux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>drake_de_braise</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Drake de braise</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>739</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O40" s="6">
+        <f>ROUND((E40*(1+(H40/100)*MAX(0,I40-100)/100)*(1+G40/100))*((D40+F40*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J40/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P40" s="6">
+        <f>IFERROR(VLOOKUP(O40,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>Ses morsures laissent des brûlures qui couvent longtemps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>wyverne</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wyverne</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>568</v>
+      </c>
+      <c r="E41" t="n">
+        <v>131</v>
+      </c>
+      <c r="F41" t="n">
+        <v>31</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I41" t="n">
+        <v>150</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>462</v>
+      </c>
+      <c r="M41" t="n">
+        <v>222</v>
+      </c>
+      <c r="N41" t="n">
+        <v>20</v>
+      </c>
+      <c r="O41" s="6">
+        <f>ROUND((E41*(1+(H41/100)*MAX(0,I41-100)/100)*(1+G41/100))*((D41+F41*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J41/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P41" s="6">
+        <f>IFERROR(VLOOKUP(O41,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Elle fond sur sa proie et frappe deux fois avant qu'on la voie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>dragon_de_givre</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Dragon de givre</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>871</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>475</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" s="6">
+        <f>ROUND((E42*(1+(H42/100)*MAX(0,I42-100)/100)*(1+G42/100))*((D42+F42*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J42/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P42" s="6">
+        <f>IFERROR(VLOOKUP(O42,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>Son souffle fige le sang dans les veines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gardien_draconique</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gardien draconique</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>990</v>
+      </c>
+      <c r="E43" t="n">
+        <v>153</v>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>488</v>
+      </c>
+      <c r="M43" t="n">
+        <v>234</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10</v>
+      </c>
+      <c r="O43" s="6">
+        <f>ROUND((E43*(1+(H43/100)*MAX(0,I43-100)/100)*(1+G43/100))*((D43+F43*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J43/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P43" s="6">
+        <f>IFERROR(VLOOKUP(O43,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Une écaille-bouclier le protège avant qu'on puisse l'atteindre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>dragon_ancien</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Dragon ancien</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>draconique</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>810</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O44" s="6">
+        <f>ROUND((E44*(1+(H44/100)*MAX(0,I44-100)/100)*(1+G44/100))*((D44+F44*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J44/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P44" s="6">
+        <f>IFERROR(VLOOKUP(O44,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>Le maître des cimes. Blessé, il devient un brasier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>rejeton_du_neant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rejeton du néant</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E45" t="n">
+        <v>159</v>
+      </c>
+      <c r="F45" t="n">
+        <v>42</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>506</v>
+      </c>
+      <c r="M45" t="n">
+        <v>243</v>
+      </c>
+      <c r="N45" t="n">
+        <v>40</v>
+      </c>
+      <c r="O45" s="6">
+        <f>ROUND((E45*(1+(H45/100)*MAX(0,I45-100)/100)*(1+G45/100))*((D45+F45*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J45/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P45" s="6">
+        <f>IFERROR(VLOOKUP(O45,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Une ombre qui a appris à marcher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>oeil_errant</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Œil errant</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>634</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O46" s="6">
+        <f>ROUND((E46*(1+(H46/100)*MAX(0,I46-100)/100)*(1+G46/100))*((D46+F46*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J46/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P46" s="6">
+        <f>IFERROR(VLOOKUP(O46,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>Il flotte, il observe, il ne cligne jamais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>devoreur</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dévoreur</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>862</v>
+      </c>
+      <c r="E47" t="n">
+        <v>254</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>544</v>
+      </c>
+      <c r="M47" t="n">
+        <v>261</v>
+      </c>
+      <c r="N47" t="n">
+        <v>25</v>
+      </c>
+      <c r="O47" s="6">
+        <f>ROUND((E47*(1+(H47/100)*MAX(0,I47-100)/100)*(1+G47/100))*((D47+F47*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J47/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="6">
+        <f>IFERROR(VLOOKUP(O47,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Il se nourrit de tout ce qu'il touche — et se referme sur ses plaies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>heraut_du_vide</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Héraut du vide</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>562</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O48" s="6">
+        <f>ROUND((E48*(1+(H48/100)*MAX(0,I48-100)/100)*(1+G48/100))*((D48+F48*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J48/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P48" s="6">
+        <f>IFERROR(VLOOKUP(O48,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>Il ouvre des failles d'où rampent d'autres créatures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>kraken_astral</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kraken astral</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E49" t="n">
+        <v>127</v>
+      </c>
+      <c r="F49" t="n">
+        <v>62</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>581</v>
+      </c>
+      <c r="M49" t="n">
+        <v>279</v>
+      </c>
+      <c r="N49" t="n">
+        <v>15</v>
+      </c>
+      <c r="O49" s="6">
+        <f>ROUND((E49*(1+(H49/100)*MAX(0,I49-100)/100)*(1+G49/100))*((D49+F49*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J49/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P49" s="6">
+        <f>IFERROR(VLOOKUP(O49,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Ses tentacules frappent de toutes parts et engourdissent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>seraphin_brise</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Séraphin brisé</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>942</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O50" s="6">
+        <f>ROUND((E50*(1+(H50/100)*MAX(0,I50-100)/100)*(1+G50/100))*((D50+F50*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J50/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P50" s="6">
+        <f>IFERROR(VLOOKUP(O50,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>Un ange tombé dans la faille ; il refuse de mourir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>avatar_du_neant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Avatar du Néant</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>abyssal</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E51" t="n">
+        <v>193</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>625</v>
+      </c>
+      <c r="M51" t="n">
+        <v>300</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" s="6">
+        <f>ROUND((E51*(1+(H51/100)*MAX(0,I51-100)/100)*(1+G51/100))*((D51+F51*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J51/100))/'⚙️ Calibrage'!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="P51" s="6">
+        <f>IFERROR(VLOOKUP(O51,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
+        <v/>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Le vide fait chair. Ses sorts dissolvent toute protection.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S24"/>
-  <conditionalFormatting sqref="O2:O24">
+  <autoFilter ref="A1:S51"/>
+  <conditionalFormatting sqref="O2:O51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5276,7 +9083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5286,7 +9093,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6623,8 +10430,160 @@
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>croc_primordial</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Croc primordial</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Un croc ancien, encore tiède de la magie du sanctuaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sang_lunaire</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sang lunaire</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Une goutte de sang qui luit d'un éclat d'argent sous l'éclipse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ecaille_de_dragon</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Écaille de dragon</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Plus dure que l'acier, encore chaude du souffle qui l'a forgée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>eclat_du_neant</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Éclat du néant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Un fragment de vide solidifié. Il semble aspirer la lumière.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H39"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -12,23 +12,21 @@
     <sheet name="👹 Mobs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="🧪 Consommables" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="📦 Ressources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="🛠️ Recettes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="🏪 Shop" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="🌳 Skill Tree" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="🏷️ Titres" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="🐉 World Bosses" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="⚙️ Calibrage" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="🏪 Shop" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="🌳 Skill Tree" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="🏷️ Titres" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="🐉 World Bosses" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="⚙️ Calibrage" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🛠️ Recettes'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -511,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-24 12:50 UTC</t>
+          <t>Généré le 2026-10-25 10:49 UTC</t>
         </is>
       </c>
     </row>
@@ -566,129 +564,117 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>🛠️ Recettes</t>
+          <t>🏪 Shop</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recettes (vide : la fabrication a été remplacée par la fusion).</t>
+          <t>Prix d'achat / vente du shop.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>🏪 Shop</t>
+          <t>🌳 Skill Tree</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prix d'achat / vente du shop.</t>
+          <t>Tous les nœuds de l'arbre.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>🌳 Skill Tree</t>
+          <t>🏷️ Titres</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tous les nœuds de l'arbre.</t>
+          <t>Titres, conditions et effets.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>🏷️ Titres</t>
+          <t>🐉 World Bosses</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Titres, conditions et effets.</t>
+          <t>Bosses + modifiers.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>🐉 World Bosses</t>
+          <t>⚙️ Calibrage</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bosses + modifiers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>⚙️ Calibrage</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>Constantes du score de puissance. NE PAS supprimer.</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>🛠️ Comment équilibrer (round-trip)</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>🛠️ Comment équilibrer (round-trip)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
+          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
+          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
+          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
+          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
-        <is>
-          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
         <is>
           <t>Power d'un équipement = puissance MARGINALE qu'il ajoute à un perso de base (power(base+item) − power(base)).</t>
         </is>
@@ -700,349 +686,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Famille</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>PV max</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Def</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Vit</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Crit %</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Crit dmg</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Esquive</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Modifiers</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Poids spawn</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Lore</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>slime_titan</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Titan Visqueux</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 6
-auto_heal_per_turn = 11</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles et se régénère lentement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gobelin_warlord</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Seigneur de Guerre Gobelin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>113</v>
-      </c>
-      <c r="F3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>130</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>enrage_below_pct = 30
-enrage_attack_multiplier = 1.5
-adds = {'attack': 79, 'summon_turn_interval': 4, 'max_active': 3}</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie, et il appelle des renforts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>stone_colossus</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Colosse de Pierre</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 28
-reflect_pct = 15</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles, sa carapace renvoie une part des coups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>shadow_wraith</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Spectre des Ténèbres</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>245</v>
-      </c>
-      <c r="F5" t="n">
-        <v>32</v>
-      </c>
-      <c r="G5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>crit_immunity = True
-phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée, et il mute en s'affaiblissant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ancient_dragon</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Dragon Ancestral</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>303</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 44
-enrage_below_pct = 25
-enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 19
-reflect_pct = 20
-adds = {'attack': 182, 'summon_turn_interval': 5, 'max_active': 2}
-phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Le sommet de l'évolution. Inflige des coups dévastateurs, renvoie les frappes, invoque des drakelings, se régénère et entre en rage à la fin.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2589,7 +2232,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Épines — Chaque coup subi renvoie 10 % de ta défense en dégâts à l'attaquant.</t>
+          <t>Épines — Ton contrecoup est augmenté de 10 % (la défense qui dépasse 75 % de l'attaque adverse revient à l'attaquant en dégâts).</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -5768,7 +5411,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5842,7 +5485,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -5915,7 +5558,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5990,7 +5633,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -6065,7 +5708,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6138,7 +5781,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -6212,7 +5855,7 @@
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -6286,7 +5929,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>20</v>
@@ -6355,7 +5998,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
         <v>20</v>
@@ -6419,16 +6062,16 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>462</v>
+        <v>1848</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>19</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -6443,10 +6086,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>219</v>
+        <v>656</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>105</v>
+        <v>315</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>10</v>
@@ -6497,7 +6140,7 @@
         <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -6571,7 +6214,7 @@
         <v>19</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>20</v>
@@ -6645,7 +6288,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6696,36 +6339,36 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>demon_cornu</t>
+          <t>loup_sacre</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Démon cornu</t>
+          <t>Loup sacré</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>671</v>
+        <v>356</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -6734,13 +6377,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>325</v>
+        <v>288</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O18" s="6">
         <f>ROUND((E18*(1+(H18/100)*MAX(0,I18-100)/100)*(1+G18/100))*((D18+F18*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J18/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6750,49 +6393,41 @@
         <f>IFERROR(VLOOKUP(O18,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>corne_de_demon ×1-2 (20%)</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>demon_cornu.png</t>
-        </is>
-      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Fantassin cornu des légions infernales, brutal et sans pitié.</t>
+          <t>Gardien à la fourrure d'argent ; il chasse en meute depuis l'aube des temps.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>liche_maudite</t>
+          <t>cerf_esprit</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liche maudite</t>
+          <t>Cerf-esprit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mort-vivant</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>554</v>
+        <v>627</v>
       </c>
       <c r="E19" t="n">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -6807,13 +6442,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="M19" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O19" s="6">
         <f>ROUND((E19*(1+(H19/100)*MAX(0,I19-100)/100)*(1+G19/100))*((D19+F19*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J19/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6824,50 +6459,46 @@
         <v/>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>liche_maudite.png</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
+          <t>Un cerf translucide ; la forêt se tait sur son passage.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ogre_demoniaque</t>
+          <t>serpent_des_racines</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ogre démoniaque</t>
+          <t>Serpent des racines</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>642</v>
+        <v>389</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
@@ -6876,13 +6507,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>388</v>
+        <v>312</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O20" s="6">
         <f>ROUND((E20*(1+(H20/100)*MAX(0,I20-100)/100)*(1+G20/100))*((D20+F20*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J20/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6892,31 +6523,23 @@
         <f>IFERROR(VLOOKUP(O20,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>croc_d_ogre ×1-2 (20%)</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>ogre_demoniaque.png</t>
-        </is>
-      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Masse de muscles corrompue qui écrase tout sur son passage.</t>
+          <t>Il dort sous les racines et frappe d'un venin sylvestre.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cerbere</t>
+          <t>demon_cornu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cerbère</t>
+          <t>Démon cornu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6925,16 +6548,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>902</v>
+        <v>671</v>
       </c>
       <c r="E21" t="n">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -6949,13 +6572,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>438</v>
+        <v>325</v>
       </c>
       <c r="M21" t="n">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O21" s="6">
         <f>ROUND((E21*(1+(H21/100)*MAX(0,I21-100)/100)*(1+G21/100))*((D21+F21*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J21/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6967,47 +6590,47 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>croc_triple ×1-2 (12%)</t>
+          <t>corne_de_demon ×1-2 (20%)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>cerbere.png</t>
+          <t>demon_cornu.png</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Molosse à trois têtes gardant les portes de l'abîme.</t>
+          <t>Fantassin cornu des légions infernales, brutal et sans pitié.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>succube</t>
+          <t>ours_colosse</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Succube</t>
+          <t>Ours colosse</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>792</v>
+        <v>537</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
@@ -7022,13 +6645,13 @@
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>488</v>
+        <v>325</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O22" s="6">
         <f>ROUND((E22*(1+(H22/100)*MAX(0,I22-100)/100)*(1+G22/100))*((D22+F22*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J22/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7038,49 +6661,41 @@
         <f>IFERROR(VLOOKUP(O22,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>philtre_de_charme ×1-1 (10%)</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>succube.png</t>
-        </is>
-      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Démone envoûtante qui draine la vie de ses proies.</t>
+          <t>Ses griffes fendent la pierre comme l'armure.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ange_dechu</t>
+          <t>liche_maudite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ange déchu</t>
+          <t>Liche maudite</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1078</v>
+        <v>9979</v>
       </c>
       <c r="E23" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -7095,13 +6710,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>544</v>
+        <v>1012</v>
       </c>
       <c r="M23" t="n">
-        <v>261</v>
+        <v>486</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O23" s="6">
         <f>ROUND((E23*(1+(H23/100)*MAX(0,I23-100)/100)*(1+G23/100))*((D23+F23*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J23/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7111,50 +6726,45 @@
         <f>IFERROR(VLOOKUP(O23,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>plume_noircie ×1-2 (15%)
-flamme_sacree ×1-1 (5%)</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ange_dechu.png</t>
+          <t>liche_maudite.png</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Ancien séraphin banni ; sa lumière s'est muée en fureur.</t>
+          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>archidemon</t>
+          <t>golem_de_mousse</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Archidémon</t>
+          <t>Golem de mousse</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1069</v>
+        <v>624</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -7169,13 +6779,13 @@
         <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>606</v>
+        <v>338</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>291</v>
+        <v>162</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O24" s="6">
         <f>ROUND((E24*(1+(H24/100)*MAX(0,I24-100)/100)*(1+G24/100))*((D24+F24*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J24/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7185,31 +6795,23 @@
         <f>IFERROR(VLOOKUP(O24,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>corne_d_archidemon ×1-1 (12%)</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>archidemon.png</t>
-        </is>
-      </c>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Seigneur des enfers, apogée de la corruption du Berceau.</t>
+          <t>Un rocher couvert de mousse qui repousse plus vite qu'on ne l'arrache.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>loup_sacre</t>
+          <t>aigle_tempete</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loup sacré</t>
+          <t>Aigle-tempête</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7218,16 +6820,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>356</v>
+        <v>5227</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
         <v>20</v>
@@ -7242,13 +6844,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>288</v>
+        <v>1050</v>
       </c>
       <c r="M25" t="n">
-        <v>138</v>
+        <v>504</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="O25" s="6">
         <f>ROUND((E25*(1+(H25/100)*MAX(0,I25-100)/100)*(1+G25/100))*((D25+F25*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J25/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7262,43 +6864,43 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Gardien à la fourrure d'argent ; il chasse en meute depuis l'aube des temps.</t>
+          <t>Chacun de ses battements d'ailes soulève une bourrasque.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>cerf_esprit</t>
+          <t>chauve_souris_geante</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Cerf-esprit</t>
+          <t>Chauve-souris géante</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>627</v>
+        <v>442</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
@@ -7307,13 +6909,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O26" s="6">
         <f>ROUND((E26*(1+(H26/100)*MAX(0,I26-100)/100)*(1+G26/100))*((D26+F26*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J26/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7327,43 +6929,43 @@
       <c r="R26" s="5" t="inlineStr"/>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Un cerf translucide ; la forêt se tait sur son passage.</t>
+          <t>Elle surgit de l'éclipse par nuées entières.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>serpent_des_racines</t>
+          <t>goule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Serpent des racines</t>
+          <t>Goule</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>389</v>
+        <v>748</v>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7372,13 +6974,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="M27" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="N27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O27" s="6">
         <f>ROUND((E27*(1+(H27/100)*MAX(0,I27-100)/100)*(1+G27/100))*((D27+F27*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J27/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7392,37 +6994,37 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Il dort sous les racines et frappe d'un venin sylvestre.</t>
+          <t>Elle rôde entre les tombes, affamée de chair fraîche.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ours_colosse</t>
+          <t>loup_garou</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Ours colosse</t>
+          <t>Loup-garou</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>537</v>
+        <v>625</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
@@ -7437,13 +7039,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O28" s="6">
         <f>ROUND((E28*(1+(H28/100)*MAX(0,I28-100)/100)*(1+G28/100))*((D28+F28*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J28/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7457,37 +7059,37 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Ses griffes fendent la pierre comme l'armure.</t>
+          <t>Sous l'éclipse, la bête l'emporte sur l'homme — et sa rage grandit avec ses blessures.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>golem_de_mousse</t>
+          <t>ogre_demoniaque</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Golem de mousse</t>
+          <t>Ogre démoniaque</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="E29" t="n">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -7502,13 +7104,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="M29" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O29" s="6">
         <f>ROUND((E29*(1+(H29/100)*MAX(0,I29-100)/100)*(1+G29/100))*((D29+F29*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J29/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7518,62 +7120,70 @@
         <f>IFERROR(VLOOKUP(O29,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>croc_d_ogre ×1-2 (20%)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>ogre_demoniaque.png</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Un rocher couvert de mousse qui repousse plus vite qu'on ne l'arrache.</t>
+          <t>Masse de muscles corrompue qui écrase tout sur son passage.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>aigle_tempete</t>
+          <t>sorciere_de_sang</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Aigle-tempête</t>
+          <t>Sorcière de sang</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>436</v>
+        <v>642</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="N30" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>168</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>10</v>
       </c>
       <c r="O30" s="6">
         <f>ROUND((E30*(1+(H30/100)*MAX(0,I30-100)/100)*(1+G30/100))*((D30+F30*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J30/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7587,19 +7197,19 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Chacun de ses battements d'ailes soulève une bourrasque.</t>
+          <t>Elle appelle ses familiers d'un murmure.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chauve_souris_geante</t>
+          <t>chevalier_de_l_eclipse</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chauve-souris géante</t>
+          <t>Chevalier de l'éclipse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7608,22 +7218,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>442</v>
+        <v>752</v>
       </c>
       <c r="E31" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -7632,13 +7242,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="M31" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="O31" s="6">
         <f>ROUND((E31*(1+(H31/100)*MAX(0,I31-100)/100)*(1+G31/100))*((D31+F31*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J31/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7652,19 +7262,19 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Elle surgit de l'éclipse par nuées entières.</t>
+          <t>Son armure noire rend chaque coup à celui qui l'a porté.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>goule</t>
+          <t>vampire_noble</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Goule</t>
+          <t>Vampire noble</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -7673,16 +7283,16 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>748</v>
+        <v>858</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
@@ -7697,13 +7307,13 @@
         <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O32" s="6">
         <f>ROUND((E32*(1+(H32/100)*MAX(0,I32-100)/100)*(1+G32/100))*((D32+F32*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J32/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7717,19 +7327,19 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Elle rôde entre les tombes, affamée de chair fraîche.</t>
+          <t>Il boit la vie de ses adversaires avec élégance.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>loup_garou</t>
+          <t>comtesse_ecarlate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Loup-garou</t>
+          <t>Comtesse écarlate</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7738,37 +7348,37 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>625</v>
+        <v>9385</v>
       </c>
       <c r="E33" t="n">
-        <v>176</v>
+        <v>478</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1256</v>
+      </c>
+      <c r="M33" t="n">
+        <v>603</v>
+      </c>
+      <c r="N33" t="n">
         <v>5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>100</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>375</v>
-      </c>
-      <c r="M33" t="n">
-        <v>180</v>
-      </c>
-      <c r="N33" t="n">
-        <v>25</v>
       </c>
       <c r="O33" s="6">
         <f>ROUND((E33*(1+(H33/100)*MAX(0,I33-100)/100)*(1+G33/100))*((D33+F33*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J33/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7782,37 +7392,37 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Sous l'éclipse, la bête l'emporte sur l'homme — et sa rage grandit avec ses blessures.</t>
+          <t>Un regard, et ses ennemis se battent pour elle.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>sorciere_de_sang</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Sorcière de sang</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>642</v>
+        <v>880</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0</v>
@@ -7827,13 +7437,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O34" s="6">
         <f>ROUND((E34*(1+(H34/100)*MAX(0,I34-100)/100)*(1+G34/100))*((D34+F34*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J34/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7847,37 +7457,37 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>Elle appelle ses familiers d'un murmure.</t>
+          <t>Petit, rusé, armé d'une lance trop grande pour lui.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chevalier_de_l_eclipse</t>
+          <t>cerbere</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chevalier de l'éclipse</t>
+          <t>Cerbère</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>752</v>
+        <v>902</v>
       </c>
       <c r="E35" t="n">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -7892,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="M35" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="N35" t="n">
         <v>15</v>
@@ -7908,47 +7518,55 @@
         <f>IFERROR(VLOOKUP(O35,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>croc_triple ×1-2 (12%)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>cerbere.png</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Son armure noire rend chaque coup à celui qui l'a porté.</t>
+          <t>Molosse à trois têtes gardant les portes de l'abîme.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>vampire_noble</t>
+          <t>dragonnet</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Vampire noble</t>
+          <t>Dragonnet</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>858</v>
+        <v>541</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
@@ -7957,13 +7575,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O36" s="6">
         <f>ROUND((E36*(1+(H36/100)*MAX(0,I36-100)/100)*(1+G36/100))*((D36+F36*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J36/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7977,43 +7595,43 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>Il boit la vie de ses adversaires avec élégance.</t>
+          <t>Un jeune dragon, vif et capricieux.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>comtesse_ecarlate</t>
+          <t>drake_de_braise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comtesse écarlate</t>
+          <t>Drake de braise</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>521</v>
+        <v>739</v>
       </c>
       <c r="E37" t="n">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8022,13 +7640,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="M37" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O37" s="6">
         <f>ROUND((E37*(1+(H37/100)*MAX(0,I37-100)/100)*(1+G37/100))*((D37+F37*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J37/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8042,19 +7660,19 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Un regard, et ses ennemis se battent pour elle.</t>
+          <t>Ses morsures laissent des brûlures qui couvent longtemps.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>kobold</t>
+          <t>wyverne</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Kobold</t>
+          <t>Wyverne</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -8063,22 +7681,22 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>880</v>
+        <v>568</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -8087,13 +7705,13 @@
         <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="O38" s="6">
         <f>ROUND((E38*(1+(H38/100)*MAX(0,I38-100)/100)*(1+G38/100))*((D38+F38*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J38/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8107,19 +7725,19 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>Petit, rusé, armé d'une lance trop grande pour lui.</t>
+          <t>Elle fond sur sa proie et frappe deux fois avant qu'on la voie.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dragonnet</t>
+          <t>dragon_de_givre</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dragonnet</t>
+          <t>Dragon de givre</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8128,22 +7746,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>541</v>
+        <v>871</v>
       </c>
       <c r="E39" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8152,13 +7770,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="M39" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="N39" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O39" s="6">
         <f>ROUND((E39*(1+(H39/100)*MAX(0,I39-100)/100)*(1+G39/100))*((D39+F39*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J39/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8172,37 +7790,37 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Un jeune dragon, vif et capricieux.</t>
+          <t>Son souffle fige le sang dans les veines.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>drake_de_braise</t>
+          <t>succube</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Drake de braise</t>
+          <t>Succube</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>739</v>
+        <v>792</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
@@ -8217,13 +7835,13 @@
         <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O40" s="6">
         <f>ROUND((E40*(1+(H40/100)*MAX(0,I40-100)/100)*(1+G40/100))*((D40+F40*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J40/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8233,23 +7851,31 @@
         <f>IFERROR(VLOOKUP(O40,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>philtre_de_charme ×1-1 (10%)</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>succube.png</t>
+        </is>
+      </c>
       <c r="S40" s="5" t="inlineStr">
         <is>
-          <t>Ses morsures laissent des brûlures qui couvent longtemps.</t>
+          <t>Démone envoûtante qui draine la vie de ses proies.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>wyverne</t>
+          <t>gardien_draconique</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wyverne</t>
+          <t>Gardien draconique</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8258,22 +7884,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>568</v>
+        <v>990</v>
       </c>
       <c r="E41" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8282,13 +7908,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="M41" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O41" s="6">
         <f>ROUND((E41*(1+(H41/100)*MAX(0,I41-100)/100)*(1+G41/100))*((D41+F41*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J41/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8302,19 +7928,19 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Elle fond sur sa proie et frappe deux fois avant qu'on la voie.</t>
+          <t>Une écaille-bouclier le protège avant qu'on puisse l'atteindre.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>dragon_de_givre</t>
+          <t>dragon_ancien</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Dragon de givre</t>
+          <t>Dragon ancien</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -8323,16 +7949,16 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>871</v>
+        <v>9715</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>105</v>
+        <v>352</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0</v>
@@ -8347,13 +7973,13 @@
         <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>475</v>
+        <v>1500</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>228</v>
+        <v>720</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O42" s="6">
         <f>ROUND((E42*(1+(H42/100)*MAX(0,I42-100)/100)*(1+G42/100))*((D42+F42*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J42/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8367,37 +7993,37 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="5" t="inlineStr">
         <is>
-          <t>Son souffle fige le sang dans les veines.</t>
+          <t>Le maître des cimes. Blessé, il devient un brasier.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gardien_draconique</t>
+          <t>rejeton_du_neant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gardien draconique</t>
+          <t>Rejeton du néant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>abyssal</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>990</v>
+        <v>1023</v>
       </c>
       <c r="E43" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8412,13 +8038,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="M43" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="O43" s="6">
         <f>ROUND((E43*(1+(H43/100)*MAX(0,I43-100)/100)*(1+G43/100))*((D43+F43*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J43/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8432,43 +8058,43 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Une écaille-bouclier le protège avant qu'on puisse l'atteindre.</t>
+          <t>Une ombre qui a appris à marcher.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>dragon_ancien</t>
+          <t>oeil_errant</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Dragon ancien</t>
+          <t>Œil errant</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>abyssal</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>810</v>
+        <v>634</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
@@ -8477,13 +8103,13 @@
         <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O44" s="6">
         <f>ROUND((E44*(1+(H44/100)*MAX(0,I44-100)/100)*(1+G44/100))*((D44+F44*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J44/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8497,37 +8123,37 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="5" t="inlineStr">
         <is>
-          <t>Le maître des cimes. Blessé, il devient un brasier.</t>
+          <t>Il flotte, il observe, il ne cligne jamais.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rejeton_du_neant</t>
+          <t>ange_dechu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rejeton du néant</t>
+          <t>Ange déchu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abyssal</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1023</v>
+        <v>1078</v>
       </c>
       <c r="E45" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="F45" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -8542,13 +8168,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="M45" t="n">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="N45" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="O45" s="6">
         <f>ROUND((E45*(1+(H45/100)*MAX(0,I45-100)/100)*(1+G45/100))*((D45+F45*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J45/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8558,23 +8184,32 @@
         <f>IFERROR(VLOOKUP(O45,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>plume_noircie ×1-2 (15%)
+flamme_sacree ×1-1 (5%)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>ange_dechu.png</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Une ombre qui a appris à marcher.</t>
+          <t>Ancien séraphin banni ; sa lumière s'est muée en fureur.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>oeil_errant</t>
+          <t>devoreur</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Œil errant</t>
+          <t>Dévoreur</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -8583,22 +8218,22 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>634</v>
+        <v>862</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J46" s="5" t="n">
         <v>0</v>
@@ -8607,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O46" s="6">
         <f>ROUND((E46*(1+(H46/100)*MAX(0,I46-100)/100)*(1+G46/100))*((D46+F46*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J46/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8627,19 +8262,19 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="5" t="inlineStr">
         <is>
-          <t>Il flotte, il observe, il ne cligne jamais.</t>
+          <t>Il se nourrit de tout ce qu'il touche — et se referme sur ses plaies.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>devoreur</t>
+          <t>heraut_du_vide</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dévoreur</t>
+          <t>Héraut du vide</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8648,16 +8283,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>862</v>
+        <v>1111</v>
       </c>
       <c r="E47" t="n">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -8672,13 +8307,13 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="M47" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="N47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O47" s="6">
         <f>ROUND((E47*(1+(H47/100)*MAX(0,I47-100)/100)*(1+G47/100))*((D47+F47*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J47/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8692,19 +8327,19 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Il se nourrit de tout ce qu'il touche — et se referme sur ses plaies.</t>
+          <t>Il ouvre des failles d'où rampent d'autres créatures.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>heraut_du_vide</t>
+          <t>kraken_astral</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Héraut du vide</t>
+          <t>Kraken astral</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -8713,16 +8348,16 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1111</v>
+        <v>1030</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
@@ -8737,13 +8372,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O48" s="6">
         <f>ROUND((E48*(1+(H48/100)*MAX(0,I48-100)/100)*(1+G48/100))*((D48+F48*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J48/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8757,19 +8392,19 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="5" t="inlineStr">
         <is>
-          <t>Il ouvre des failles d'où rampent d'autres créatures.</t>
+          <t>Ses tentacules frappent de toutes parts et engourdissent.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kraken_astral</t>
+          <t>seraphin_brise</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kraken astral</t>
+          <t>Séraphin brisé</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8778,16 +8413,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1030</v>
+        <v>942</v>
       </c>
       <c r="E49" t="n">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c r="F49" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -8802,13 +8437,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="M49" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="N49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O49" s="6">
         <f>ROUND((E49*(1+(H49/100)*MAX(0,I49-100)/100)*(1+G49/100))*((D49+F49*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J49/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8822,37 +8457,37 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Ses tentacules frappent de toutes parts et engourdissent.</t>
+          <t>Un ange tombé dans la faille ; il refuse de mourir.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>seraphin_brise</t>
+          <t>archidemon</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Séraphin brisé</t>
+          <t>Archidémon</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>abyssal</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>942</v>
+        <v>19246</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>279</v>
+        <v>527</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -8867,13 +8502,13 @@
         <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>600</v>
+        <v>1819</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>288</v>
+        <v>873</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O50" s="6">
         <f>ROUND((E50*(1+(H50/100)*MAX(0,I50-100)/100)*(1+G50/100))*((D50+F50*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J50/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8883,11 +8518,19 @@
         <f>IFERROR(VLOOKUP(O50,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>corne_d_archidemon ×1-1 (12%)</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>archidemon.png</t>
+        </is>
+      </c>
       <c r="S50" s="5" t="inlineStr">
         <is>
-          <t>Un ange tombé dans la faille ; il refuse de mourir.</t>
+          <t>Seigneur des enfers, apogée de la corruption du Berceau.</t>
         </is>
       </c>
     </row>
@@ -8908,16 +8551,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1221</v>
+        <v>21978</v>
       </c>
       <c r="E51" t="n">
-        <v>193</v>
+        <v>387</v>
       </c>
       <c r="F51" t="n">
         <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -8932,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>625</v>
+        <v>1875</v>
       </c>
       <c r="M51" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="N51" t="n">
         <v>5</v>
@@ -10594,67 +10237,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Code recette</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Résultat (item)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Catégorie résultat</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Slot résultat</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Quantité produite</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Ingrédients</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10750,7 +10332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11615,7 +11197,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11668,7 +11250,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -12145,7 +11727,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12251,7 +11833,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -12569,7 +12151,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -12675,7 +12257,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>speed_flat → [1]</t>
+          <t>speed_flat → [0.5]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -14108,7 +13690,8 @@
           <t>grant_class → [soigneur]
 healer_spell → [1]
 heal_power_multiplier → [2]
-speed_per_ally → [1]</t>
+speed_per_ally → [1]
+team_damage_percent → [25]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -14133,7 +13716,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Classe Soigneur : remplace son attaque par un sort de soin (cible choisie selon sa tactique, /tactique), soins donnés doublés, +1 de vitesse par allié présent au combat.</t>
+          <t>Classe Soigneur : soigne un allié sous 50 % de ses PV à la place de son attaque (cible choisie selon sa tactique, /tactique) — sinon il attaque ; soins donnés doublés, +1 de vitesse par allié présent au combat. Aura : tant qu'il est debout, toute l'équipe inflige +25 % de dégâts (une seule aura par équipe).</t>
         </is>
       </c>
     </row>
@@ -14382,7 +13965,8 @@
       <c r="H66" s="7" t="inlineStr">
         <is>
           <t>grant_class → [rempart]
-redirect_ally_damage_percent → [50]</t>
+redirect_ally_damage_percent → [50]
+defense_to_attack_percent → [50]</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -14407,7 +13991,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Redirige 50% des dégats que devrait recevoir ses alliés sur lui à la place.</t>
+          <t>Redirige 50% des dégats que devrait recevoir ses alliés sur lui à la place. Garde offensive : la moitié de sa défense s'ajoute à son attaque.</t>
         </is>
       </c>
     </row>
@@ -14656,8 +14240,8 @@
       <c r="H71" s="8" t="inlineStr">
         <is>
           <t>grant_class → [assassin]
-crit_chance_multiplier → [2]
-crit_damage_multiplier → [3]</t>
+crit_chance_multiplier → [1.25]
+crit_damage_multiplier → [1.5]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -14682,7 +14266,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Double ses chances de critique et triple ses dégats critiques.</t>
+          <t>Chances de critique ×1,25 et dégâts critiques ×1,5.</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16541,4 +16125,347 @@
   <autoFilter ref="A1:H26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>PV max</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Vit</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Crit %</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Crit dmg</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Poids spawn</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Lore</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>slime_titan</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Titan Visqueux</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 6
+auto_heal_per_turn = 42</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles et se régénère lentement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gobelin_warlord</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seigneur de Guerre Gobelin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>226</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>enrage_below_pct = 30
+enrage_attack_multiplier = 1.5
+adds = {'attack': 158, 'summon_turn_interval': 4, 'max_active': 3}</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie, et il appelle des renforts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>stone_colossus</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="n">
+        <v>535000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 28
+reflect_pct = 15</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles, sa carapace renvoie une part des coups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>176000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>490</v>
+      </c>
+      <c r="F5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>crit_immunity = True
+phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée, et il mute en s'affaiblissant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>113000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>606</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 44
+enrage_below_pct = 25
+enrage_attack_multiplier = 1.8
+auto_heal_per_turn = 177
+reflect_pct = 20
+adds = {'attack': 364, 'summon_turn_interval': 5, 'max_active': 2}
+phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Le sommet de l'évolution. Inflige des coups dévastateurs, renvoie les frappes, invoque des drakelings, se régénère et entre en rage à la fin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-25 10:49 UTC</t>
+          <t>Généré le 2026-10-25 13:35 UTC</t>
         </is>
       </c>
     </row>
@@ -15011,14 +15011,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
@@ -15155,17 +15155,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>champion_1v1</t>
+          <t>fleau_semaine</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Champion en 1vs1</t>
+          <t>Fléau de la semaine</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>👑</t>
+          <t>⚔️</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -15175,39 +15175,39 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>duel_top1</t>
+          <t>weekly_role_trial</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>champion_all_stats → value=1</t>
+          <t>damage_dealt_pct → value=2</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Détenteur du sommet du ladder 1v1. +1% sur toutes vos stats (multiplicatif sur PV/atk/def, additif sur crit/esquive, +1 flat sur vitesse/régen). Perdu dès qu'un autre joueur prend la première place.</t>
+          <t>Meilleur score DPS de la semaine aux défis (/defi). +2 % de dégâts infligés. Remis en jeu chaque dimanche à 20 h.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>farmer_fou</t>
+          <t>bastion_semaine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le Farmer Fou</t>
+          <t>Bastion de la semaine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🌾</t>
+          <t>🛡️</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15217,138 +15217,138 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kills_record</t>
+          <t>weekly_role_trial</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>gold_xp_bonus_pct → value=1</t>
+          <t>damage_taken_reduction_pct → value=2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
+          <t>Meilleur score Tank de la semaine aux défis (/defi). −2 % de dégâts reçus. Remis en jeu chaque dimanche à 20 h.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>bourreau</t>
+          <t>ange_gardien_semaine</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Le Bourreau</t>
+          <t>Ange gardien de la semaine</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>🩸</t>
+          <t>💚</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>kills_total</t>
+          <t>weekly_role_trial</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>soutien</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=5</t>
+          <t>heal_power_pct → value=2</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Tueur impitoyable de 500 monstres au total. +5% sur les dégâts critiques (additif sur crit_damage).</t>
+          <t>Meilleur score Soutien de la semaine aux défis (/defi). +2 % de soins donnés. Remis en jeu chaque dimanche à 20 h.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>intouchable</t>
+          <t>champion_semaine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L'Intouchable</t>
+          <t>Champion de la semaine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🌪️</t>
+          <t>👑</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dodges_total</t>
+          <t>weekly_role_trial</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>dodge_flat → value=1</t>
+          <t>champion_all_stats → value=1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Esquiveur aguerri (100 esquives encaissées en combat de groupe). +1% d'esquive permanent.</t>
+          <t>Meilleur classement général de la semaine aux défis (/defi). +1 % sur toutes vos stats (multiplicatif sur PV/atk/def, additif sur crit/esquive, +1 flat sur vitesse/régen). Remis en jeu chaque dimanche à 20 h.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>habitue_taverne</t>
+          <t>farmer_fou</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Habitué de la taverne</t>
+          <t>Le Farmer Fou</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>🍻</t>
+          <t>🌾</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>daily_streak</t>
+          <t>kills_record</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -15358,24 +15358,24 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Série /daily de 7 jours. +1 % sur l'or et l'XP gagnés en combat.</t>
+          <t>Détenteur du record absolu de monstres tués. +1% sur l'or et l'XP gagnés à la fin d'un combat (uniquement pour le détenteur). Perdu dès qu'un autre joueur dépasse votre record.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taverne_addict</t>
+          <t>bourreau</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taverne Addict</t>
+          <t>Le Bourreau</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🍺</t>
+          <t>🩸</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15385,39 +15385,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>daily_streak</t>
+          <t>kills_total</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>crit_damage_flat → value=5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Série /daily de 30 jours. +3 % de dégâts critiques.</t>
+          <t>Tueur impitoyable de 500 monstres au total. +5% sur les dégâts critiques (additif sur crit_damage).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>pilier_taverne</t>
+          <t>intouchable</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Pilier de la taverne</t>
+          <t>L'Intouchable</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>🏛️</t>
+          <t>🌪️</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>daily_streak</t>
+          <t>dodges_total</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -15437,29 +15437,29 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>gold_xp_bonus_pct → value=2</t>
+          <t>dodge_flat → value=1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Série /daily de 100 jours. +2 % sur l'or et l'XP gagnés en combat.</t>
+          <t>Esquiveur aguerri (100 esquives encaissées en combat de groupe). +1% d'esquive permanent.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>slime_chasseur_legendaire</t>
+          <t>habitue_taverne</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Slime</t>
+          <t>Habitué de la taverne</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>🍻</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15469,39 +15469,39 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>kills_mob</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>slime / 50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
+          <t>gold_xp_bonus_pct → value=1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
+          <t>Série /daily de 7 jours. +1 % sur l'or et l'XP gagnés en combat.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chasseur_legendaire</t>
+          <t>taverne_addict</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin</t>
+          <t>Taverne Addict</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>🍺</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -15511,39 +15511,39 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>kills_mob</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>gobelin / 50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
+          <t>crit_damage_flat → value=3</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
+          <t>Série /daily de 30 jours. +3 % de dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gobelin_combattant_chasseur_legendaire</t>
+          <t>pilier_taverne</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Combattant</t>
+          <t>Pilier de la taverne</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>🏛️</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15553,34 +15553,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>kills_mob</t>
+          <t>daily_streak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>gobelin_combattant / 50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
+          <t>gold_xp_bonus_pct → value=2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
+          <t>Série /daily de 100 jours. +2 % sur l'or et l'XP gagnés en combat.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman_chasseur_legendaire</t>
+          <t>slime_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Chaman</t>
+          <t>Chasseur Légendaire — Slime</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -15600,29 +15600,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman / 50</t>
+          <t>slime / 50</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=slime, value=5</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
+          <t>50 slimes tués. +5% drop rate sur les slimes (multiplicatif, préserve la rareté).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gobelin_geant_chasseur_legendaire</t>
+          <t>gobelin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Géant</t>
+          <t>Chasseur Légendaire — Gobelin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15642,29 +15642,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>gobelin_geant / 50</t>
+          <t>gobelin / 50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin, value=5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins tués. +5% drop rate sur les gobelins.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>gobelin_runique_chasseur_legendaire</t>
+          <t>gobelin_combattant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Runique</t>
+          <t>Chasseur Légendaire — Gobelin Combattant</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -15684,29 +15684,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>gobelin_runique / 50</t>
+          <t>gobelin_combattant / 50</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_combattant, value=5</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins combattants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gobelin_ballon_chasseur_legendaire</t>
+          <t>gobelin_chaman_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Ballon</t>
+          <t>Chasseur Légendaire — Gobelin Chaman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -15726,29 +15726,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>gobelin_ballon / 50</t>
+          <t>gobelin_chaman / 50</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_chaman, value=5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins chamans tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>gobelin_assassin_chasseur_legendaire</t>
+          <t>gobelin_geant_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Assassin</t>
+          <t>Chasseur Légendaire — Gobelin Géant</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -15768,29 +15768,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>gobelin_assassin / 50</t>
+          <t>gobelin_geant / 50</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_geant, value=5</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins géants tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gobelin_superieur_chasseur_legendaire</t>
+          <t>gobelin_runique_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chasseur Légendaire — Gobelin Supérieur</t>
+          <t>Chasseur Légendaire — Gobelin Runique</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -15810,76 +15810,76 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>gobelin_superieur / 50</t>
+          <t>gobelin_runique / 50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_runique, value=5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
+          <t>50 gobelins runiques tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>mvp_world_boss</t>
+          <t>gobelin_ballon_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>MVP des World Boss</t>
+          <t>Chasseur Légendaire — Gobelin Ballon</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>🏆</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>world_boss_mvp</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>gobelin_ballon / 50</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>champion_all_stats → value=2</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_ballon, value=5</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
+          <t>50 gobelins ballons tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tueur_slime_titan</t>
+          <t>gobelin_assassin_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tueur du Titan Visqueux</t>
+          <t>Chasseur Légendaire — Gobelin Assassin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15889,39 +15889,39 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>slime_titan / 1</t>
+          <t>gobelin_assassin / 50</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_assassin, value=5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
+          <t>50 gobelins assassins tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>tueur_gobelin_warlord</t>
+          <t>gobelin_superieur_chasseur_legendaire</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Seigneur de Guerre Gobelin</t>
+          <t>Chasseur Légendaire — Gobelin Supérieur</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -15931,76 +15931,76 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_mob</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>gobelin_warlord / 1</t>
+          <t>gobelin_superieur / 50</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>drop_rate_bonus_vs_mob → target=gobelin_superieur, value=5</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
+          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tueur_stone_colossus</t>
+          <t>mvp_world_boss</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tueur du Colosse de Pierre</t>
+          <t>MVP des World Boss</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🏆</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>world_boss_mvp</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stone_colossus / 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>champion_all_stats → value=2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>tueur_shadow_wraith</t>
+          <t>tueur_slime_titan</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Spectre des Ténèbres</t>
+          <t>Tueur du Titan Visqueux</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>shadow_wraith / 1</t>
+          <t>slime_titan / 1</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -16030,19 +16030,19 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tueur_ancient_dragon</t>
+          <t>tueur_gobelin_warlord</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tueur du Dragon Ancestral</t>
+          <t>Tueur du Seigneur de Guerre Gobelin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ancient_dragon / 1</t>
+          <t>gobelin_warlord / 1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -16072,42 +16072,168 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>tueur_stone_colossus</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>stone_colossus / 1</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tueur_shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tueur du Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>shadow_wraith / 1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>tueur_ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>ancient_dragon / 1</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ma_survie_avant_tout</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Ma survie avant tout</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>🛡️</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>dodge_flat → value=1
 speed_flat → value=1
@@ -16115,14 +16241,14 @@
 hp_max_flat → value=200</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>A ignoré une « petite fille » qui s'est révélée être un monstre déguisé — l'instinct de survie récompensé. Esquive +1%, Vitesse +1, Défense +10, PV max +200.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-25 13:35 UTC</t>
+          <t>Généré le 2026-10-25 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>8</v>
@@ -5411,7 +5411,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>14</v>
@@ -5846,16 +5846,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5920,16 +5920,16 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>20</v>
@@ -5989,16 +5989,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
         <v>20</v>
@@ -6062,16 +6062,16 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1848</v>
+        <v>1320</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -6131,16 +6131,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -6205,16 +6205,16 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>20</v>
@@ -6279,16 +6279,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6353,16 +6353,16 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>20</v>
@@ -6418,16 +6418,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>20</v>
@@ -6548,16 +6548,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="E21" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
@@ -6686,16 +6686,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9979</v>
+        <v>9504</v>
       </c>
       <c r="E23" t="n">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="F23" t="n">
         <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -6755,16 +6755,16 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>624</v>
+        <v>594</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -6820,16 +6820,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5227</v>
+        <v>3274</v>
       </c>
       <c r="E25" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
         <v>20</v>
@@ -6885,16 +6885,16 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>20</v>
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>748</v>
+        <v>715</v>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>625</v>
+        <v>590</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>8</v>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>642</v>
+        <v>607</v>
       </c>
       <c r="E29" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F29" t="n">
         <v>16</v>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>642</v>
+        <v>607</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>16</v>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>752</v>
+        <v>713</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
         <v>8</v>
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>858</v>
+        <v>814</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>8</v>
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9385</v>
+        <v>8910</v>
       </c>
       <c r="E33" t="n">
-        <v>478</v>
+        <v>344</v>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
         <v>14</v>
@@ -7413,13 +7413,13 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>880</v>
+        <v>836</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>8</v>
@@ -7478,13 +7478,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>902</v>
+        <v>858</v>
       </c>
       <c r="E35" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F35" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G35" t="n">
         <v>8</v>
@@ -7551,13 +7551,13 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>541</v>
+        <v>515</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>14</v>
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>739</v>
+        <v>704</v>
       </c>
       <c r="E37" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
@@ -7681,13 +7681,13 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>14</v>
@@ -7746,13 +7746,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>871</v>
+        <v>822</v>
       </c>
       <c r="E39" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
         <v>8</v>
@@ -7811,13 +7811,13 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>792</v>
+        <v>748</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>8</v>
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>990</v>
+        <v>935</v>
       </c>
       <c r="E41" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G41" t="n">
         <v>8</v>
@@ -7949,13 +7949,13 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>9715</v>
+        <v>19906</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>352</v>
+        <v>170</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>8</v>
@@ -8014,13 +8014,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1023</v>
+        <v>968</v>
       </c>
       <c r="E43" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G43" t="n">
         <v>8</v>
@@ -8079,13 +8079,13 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>634</v>
+        <v>601</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>14</v>
@@ -8144,13 +8144,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1078</v>
+        <v>1034</v>
       </c>
       <c r="E45" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G45" t="n">
         <v>8</v>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>862</v>
+        <v>827</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>8</v>
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1111</v>
+        <v>1067</v>
       </c>
       <c r="E47" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G47" t="n">
         <v>8</v>
@@ -8348,13 +8348,13 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1030</v>
+        <v>990</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>8</v>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>942</v>
+        <v>906</v>
       </c>
       <c r="E49" t="n">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="F49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G49" t="n">
         <v>8</v>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>19246</v>
+        <v>18533</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>527</v>
+        <v>381</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>8</v>
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>21978</v>
+        <v>21186</v>
       </c>
       <c r="E51" t="n">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G51" t="n">
         <v>8</v>
@@ -10338,7 +10338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Classe Soigneur : soigne un allié sous 50 % de ses PV à la place de son attaque (cible choisie selon sa tactique, /tactique) — sinon il attaque ; soins donnés doublés, +1 de vitesse par allié présent au combat. Aura : tant qu'il est debout, toute l'équipe inflige +25 % de dégâts (une seule aura par équipe).</t>
+          <t>Spécialisation de la Voie du Support : soigne un allié sous 50 % de ses PV à la place de son attaque (cible selon sa tactique, /tactique), soins doublés, +1 de vitesse par allié. Aura : tant qu'il est debout, toute l'équipe inflige +25 % de dégâts (une seule aura par équipe). Demande 27 points dans la voie ; une seule spécialisation possible.</t>
         </is>
       </c>
     </row>
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13959,14 +13959,14 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
           <t>grant_class → [rempart]
 redirect_ally_damage_percent → [50]
-defense_to_attack_percent → [50]</t>
+defense_to_attack_percent → [25]</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Redirige 50% des dégats que devrait recevoir ses alliés sur lui à la place. Garde offensive : la moitié de sa défense s'ajoute à son attaque.</t>
+          <t>Spécialisation de la Voie du Protecteur : encaisse 50 % des coups portés à ses alliés, et 25 % de sa défense s'ajoutent à son attaque (50 % avec le Gardien). Demande 27 points dans la voie ; une seule spécialisation possible.</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Chances de critique ×1,25 et dégâts critiques ×1,5.</t>
+          <t>Spécialisation de la Voie du Guerrier : chances de critique ×1,25 et dégâts critiques ×1,5. Demande 27 points dans la voie ; une seule spécialisation possible.</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -14999,8 +14999,184 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>base_guerrier</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Guerrier</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>grant_class → [guerrier]
+damage_dealt_percent → [5]</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Voie du Guerrier</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>24, 320</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>🗡️</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Classe de base de la Voie du Guerrier : +5 % de dégâts infligés. Cumulable avec les autres classes de base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>base_gardien</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Gardien</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr"/>
+      <c r="F86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>grant_class → [gardien]
+threat_percent → [50]
+damage_taken_reduction_percent → [5]
+defense_to_attack_percent → [25]</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Voie du Protecteur</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>-28, 586</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>🧱</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>Classe de base de la Voie du Protecteur : attire davantage les coups (+50 % d'aggro), −5 % de dégâts reçus, et 25 % de sa défense s'ajoutent à son attaque. Cumulable avec les autres classes de base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>base_clerc</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Clerc</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>grant_class → [clerc]
+ally_heal_on_hit_percent → [20]</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Voie du Support</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-204, 432</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🕊️</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Classe de base de la Voie du Support : 20 % des dégâts infligés soignent l'allié le plus blessé, sans remplacer l'attaque. Cumulable avec les autres classes de base.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M84"/>
+  <autoFilter ref="A1:M87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16357,10 +16533,10 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
-        <v>32000</v>
+        <v>13000</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>9</v>
@@ -16379,8 +16555,8 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 6
-auto_heal_per_turn = 42</t>
+          <t>damage_immunity_threshold = 5
+auto_heal_per_turn = 32</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -16405,13 +16581,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>12</v>
@@ -16429,7 +16605,7 @@
         <is>
           <t>enrage_below_pct = 30
 enrage_attack_multiplier = 1.5
-adds = {'attack': 158, 'summon_turn_interval': 4, 'max_active': 3}</t>
+adds = {'attack': 148, 'summon_turn_interval': 4, 'max_active': 3}</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -16454,13 +16630,13 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>535000</v>
+        <v>209000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -16476,7 +16652,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 28
+          <t>damage_immunity_threshold = 27
 reflect_pct = 15</t>
         </is>
       </c>
@@ -16502,13 +16678,13 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>176000</v>
+        <v>186000</v>
       </c>
       <c r="E5" t="n">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>18</v>
@@ -16550,13 +16726,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>113000</v>
+        <v>111000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>15</v>
@@ -16572,12 +16748,12 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>damage_immunity_threshold = 44
+          <t>damage_immunity_threshold = 43
 enrage_below_pct = 25
 enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 177
+auto_heal_per_turn = 179
 reflect_pct = 20
-adds = {'attack': 364, 'summon_turn_interval': 5, 'max_active': 2}
+adds = {'attack': 351, 'summon_turn_interval': 5, 'max_active': 2}
 phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
         </is>
       </c>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-25 15:17 UTC</t>
+          <t>Généré le 2026-10-25 16:07 UTC</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>525</v>
+        <v>383</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>800</v>
+        <v>686</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>1125</v>
+        <v>966</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1510</v>
+        <v>1352</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1950</v>
+        <v>2259</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>2450</v>
+        <v>2998</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>3000</v>
+        <v>3992</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v/>
       </c>
       <c r="D11" t="n">
-        <v>3600</v>
+        <v>4886</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="12">
       <c r="D12" t="n">
-        <v>4300</v>
+        <v>7610</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="13">
       <c r="D13" t="n">
-        <v>5000</v>
+        <v>8898</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
     </row>
     <row r="14">
       <c r="D14" t="n">
-        <v>5800</v>
+        <v>10460</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     </row>
     <row r="15">
       <c r="D15" t="n">
-        <v>6600</v>
+        <v>14968</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     </row>
     <row r="16">
       <c r="D16" t="n">
-        <v>7500</v>
+        <v>16978</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     </row>
     <row r="17">
       <c r="D17" t="n">
-        <v>8500</v>
+        <v>19589</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
     </row>
     <row r="18">
       <c r="D18" t="n">
-        <v>9500</v>
+        <v>22354</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
     </row>
     <row r="19">
       <c r="D19" t="n">
-        <v>10500</v>
+        <v>24996</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
     </row>
     <row r="20">
       <c r="D20" t="n">
-        <v>11650</v>
+        <v>28086</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="21">
       <c r="D21" t="n">
-        <v>12600</v>
+        <v>30905</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="22">
       <c r="D22" t="n">
-        <v>13600</v>
+        <v>42500</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="23">
       <c r="D23" t="n">
-        <v>21700</v>
+        <v>68100</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="24">
       <c r="D24" t="n">
-        <v>36000</v>
+        <v>113000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="25">
       <c r="D25" t="n">
-        <v>64000</v>
+        <v>201100</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="26">
       <c r="D26" t="n">
-        <v>130000</v>
+        <v>408300</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="27">
       <c r="D27" t="n">
-        <v>292000</v>
+        <v>918700</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="28">
       <c r="D28" t="n">
-        <v>650000</v>
+        <v>2048700</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="29">
       <c r="D29" t="n">
-        <v>1400000</v>
+        <v>4404700</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
     <col width="48" customWidth="1" min="19" max="19"/>
   </cols>
@@ -5218,11 +5218,9 @@
         <f>IFERROR(VLOOKUP(O2,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>potion_soin ×1-1 (10%)
-noyau_de_slime ×1-1 (8%)
-essence_de_vie ×1-1 (4%)</t>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>potion_soin ×1-1 (10%)</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
@@ -5293,13 +5291,7 @@
         <f>IFERROR(VLOOKUP(O3,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>silex ×1-1 (20%)
-morceau_de_tissu ×1-2 (18%)
-diamant ×1-1 (4%)</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>gobelin.png</t>
@@ -5368,12 +5360,7 @@
         <f>IFERROR(VLOOKUP(O4,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>cuir_brut ×1-2 (22%)
-silex ×1-2 (15%)</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
           <t>gobelin_combattant.png</t>
@@ -5442,12 +5429,7 @@
         <f>IFERROR(VLOOKUP(O5,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>os_poli ×1-2 (22%)
-poussiere_d_ossements ×1-2 (18%)</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>squelette.png</t>
@@ -5516,11 +5498,7 @@
         <f>IFERROR(VLOOKUP(O6,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>gourde_de_chaman ×1-1 (20%)</t>
-        </is>
-      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr">
         <is>
           <t>gobelin_chaman.png</t>
@@ -5589,13 +5567,7 @@
         <f>IFERROR(VLOOKUP(O7,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>chair_putride ×1-2 (22%)
-lambeau_de_vetement ×1-2 (18%)
-dent_gatee ×1-1 (12%)</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>zombie.png</t>
@@ -5664,13 +5636,7 @@
         <f>IFERROR(VLOOKUP(O8,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>toile_de_dirigeable ×1-2 (22%)
-grappin_rouille ×1-1 (10%)
-petite_bombe ×1-2 (6%)</t>
-        </is>
-      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr">
         <is>
           <t>gobelin_ballon.png</t>
@@ -5739,11 +5705,7 @@
         <f>IFERROR(VLOOKUP(O9,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>os_massif ×1-2 (22%)</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>gobelin_geant.png</t>
@@ -5812,12 +5774,7 @@
         <f>IFERROR(VLOOKUP(O10,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>bandelette_maudite ×1-2 (22%)
-resine_d_embaumement ×1-1 (10%)</t>
-        </is>
-      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
           <t>momie.png</t>
@@ -5886,12 +5843,7 @@
         <f>IFERROR(VLOOKUP(O11,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>encre_rituelle ×1-2 (20%)
-pierre_runique ×1-1 (10%)</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>gobelin_runique.png</t>
@@ -6029,11 +5981,7 @@
         <f>IFERROR(VLOOKUP(O13,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>morceau_de_tissu ×1-2 (20%)</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>gobelin_assassin.png</t>
@@ -6171,12 +6119,7 @@
         <f>IFERROR(VLOOKUP(O15,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre ×1-2 (22%)
-coeur_de_granit ×1-1 (3%)</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>gargouille.png</t>
@@ -6245,12 +6188,7 @@
         <f>IFERROR(VLOOKUP(O16,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>corne_naissante ×1-2 (22%)
-braise_infernale ×1-1 (10%)</t>
-        </is>
-      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr">
         <is>
           <t>diablotin.png</t>
@@ -6319,12 +6257,7 @@
         <f>IFERROR(VLOOKUP(O17,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>echo_de_cri ×1-1 (18%)
-larme_spectrale ×1-1 (5%)</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>banshee.png</t>
@@ -6588,11 +6521,7 @@
         <f>IFERROR(VLOOKUP(O21,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>corne_de_demon ×1-2 (20%)</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>demon_cornu.png</t>
@@ -7120,11 +7049,7 @@
         <f>IFERROR(VLOOKUP(O29,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>croc_d_ogre ×1-2 (20%)</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>ogre_demoniaque.png</t>
@@ -7518,11 +7443,7 @@
         <f>IFERROR(VLOOKUP(O35,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>croc_triple ×1-2 (12%)</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>cerbere.png</t>
@@ -7851,11 +7772,7 @@
         <f>IFERROR(VLOOKUP(O40,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>philtre_de_charme ×1-1 (10%)</t>
-        </is>
-      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr">
         <is>
           <t>succube.png</t>
@@ -8184,12 +8101,7 @@
         <f>IFERROR(VLOOKUP(O45,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q45" s="8" t="inlineStr">
-        <is>
-          <t>plume_noircie ×1-2 (15%)
-flamme_sacree ×1-1 (5%)</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>ange_dechu.png</t>
@@ -8518,11 +8430,7 @@
         <f>IFERROR(VLOOKUP(O50,'⚙️ Calibrage'!$D$2:$E$29,2,TRUE),"?")</f>
         <v/>
       </c>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>corne_d_archidemon ×1-1 (12%)</t>
-        </is>
-      </c>
+      <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr">
         <is>
           <t>archidemon.png</t>
@@ -8726,11 +8634,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -8886,12 +8794,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>silex</t>
+          <t>c_ur_corrompu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silex</t>
+          <t>Cœur corrompu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8920,17 +8828,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>diamant</t>
+          <t>croc_primordial</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Croc primordial</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -8949,17 +8857,21 @@
       <c r="G6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Un croc ancien, encore tiède de la magie du sanctuaire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>morceau_de_tissu</t>
+          <t>sang_lunaire</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Morceau de tissu</t>
+          <t>Sang lunaire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8983,17 +8895,21 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Une goutte de sang qui luit d'un éclat d'argent sous l'éclipse.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>bois</t>
+          <t>ecaille_de_dragon</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bois</t>
+          <t>Écaille de dragon</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -9017,22 +8933,26 @@
       <c r="G8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Plus dure que l'acier, encore chaude du souffle qui l'a forgée.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>essence_de_vie</t>
+          <t>eclat_du_neant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Essence de vie</t>
+          <t>Éclat du néant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9051,1182 +8971,14 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>petite_bombe</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Petite bombe</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>c_ur_corrompu</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cœur corrompu</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>cuir_brut</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Cuir brut</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>gourde_de_chaman</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Gourde de chaman</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>os_massif</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Os massif</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pierre_runique</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Pierre runique</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>encre_rituelle</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Encre rituelle</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>toile_de_dirigeable</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Toile de dirigeable</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>grappin_rouille</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Grappin rouillé</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>os_poli</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Os poli</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>poussiere_d_ossements</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Poussière d'ossements</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>chair_putride</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Chair putride</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>lambeau_de_vetement</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Lambeau de vêtement</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dent_gatee</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dent gâtée</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>bandelette_maudite</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Bandelette maudite</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>resine_d_embaumement</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Résine d'embaumement</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>17</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>eclat_de_pierre</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Éclat de pierre</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>coeur_de_granit</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Cœur de granit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>40</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>larme_spectrale</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Larme spectrale</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>echo_de_cri</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Écho de cri</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>20</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>noyau_de_slime</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Noyau de slime</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>corne_naissante</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Corne naissante</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>braise_infernale</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Braise infernale</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>corne_de_demon</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Corne de démon</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>croc_d_ogre</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Croc d'ogre</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>croc_triple</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Croc triple</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>42</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>philtre_de_charme</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Philtre de charme</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>plume_noircie</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Plume noircie</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>44</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>flamme_sacree</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Flamme sacrée</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>corne_d_archidemon</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Corne d'archidémon</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>75</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>croc_primordial</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Croc primordial</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Un croc ancien, encore tiède de la magie du sanctuaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>sang_lunaire</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sang lunaire</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Une goutte de sang qui luit d'un éclat d'argent sous l'éclipse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>ecaille_de_dragon</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Écaille de dragon</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Plus dure que l'acier, encore chaude du souffle qui l'a forgée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>eclat_du_neant</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Éclat du néant</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>∞</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Un fragment de vide solidifié. Il semble aspirer la lumière.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12662,7 +11414,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Classe Mage : dégâts ×1,5 si son affinité dans l'élément de l'attaque atteint 25, ×2 à 50, ×5 à 100.</t>
+          <t>Classe Mage : quand ton coup s'infuse d'un élément (le monstre y est faible), le bonus élémentaire est multiplié par 1,25 si ton affinité dans cet élément atteint 25, par 1,5 à 50, par 2 à 100.</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -11,22 +11,24 @@
     <sheet name="🎽 Équipements" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="👹 Mobs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="🧪 Consommables" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="📦 Ressources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="🏪 Shop" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="🌳 Skill Tree" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="🏷️ Titres" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="🐉 World Bosses" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="⚙️ Calibrage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="⚗️ Alchimie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="📦 Ressources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="🏪 Shop" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="🌳 Skill Tree" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="🏷️ Titres" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="🐉 World Bosses" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="⚙️ Calibrage" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🏪 Shop'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⚗️ Alchimie'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -509,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-25 16:07 UTC</t>
+          <t>Généré le 2026-10-26 07:25 UTC</t>
         </is>
       </c>
     </row>
@@ -557,124 +559,136 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Potions et ressources de craft.</t>
+          <t>Potions et matériaux de famille.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>🏪 Shop</t>
+          <t>⚗️ Alchimie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prix d'achat / vente du shop.</t>
+          <t>Recettes d'Elna : ingrédients, or de confection, maîtrise.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>🌳 Skill Tree</t>
+          <t>🏪 Shop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tous les nœuds de l'arbre.</t>
+          <t>Prix d'achat / vente du shop.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>🏷️ Titres</t>
+          <t>🌳 Skill Tree</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Titres, conditions et effets.</t>
+          <t>Tous les nœuds de l'arbre.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>🐉 World Bosses</t>
+          <t>🏷️ Titres</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bosses + modifiers.</t>
+          <t>Titres, conditions et effets.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>🐉 World Bosses</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bosses + modifiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>⚙️ Calibrage</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Constantes du score de puissance. NE PAS supprimer.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>🛠️ Comment équilibrer (round-trip)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
+          <t>1. Filtre : clique la flèche d'un en-tête (ex : colonne Type = « Casque », ou Panoplie = « gobelin »).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
+          <t>2. Édite les colonnes de stats (Atk, Def, PV, Crit %, Crit dmg, Esquive, Vitesse, Regen), le Prix, la Rareté, le Slot, la Panoplie, le Nom…</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
+          <t>3. La colonne « Power » (fond gris) est AUTO-CALCULÉE — ne l'édite pas, elle se met à jour toute seule quand tu changes une stat.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>4. Tu peux AJOUTER une ligne d'équipement : remplis au moins Code + Type. Tu peux en supprimer aussi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>5. Renvoie-moi le fichier .xlsx modifié → je réapplique via scripts/import_content_spreadsheet.py (puis seed + déploiement).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>Conventions stats : crit_chance &amp; esquive en 0..100 ; crit_damage 100 = neutre, 150 = ×1,5 ; défense soustractive (1 DEF ≈ 25 PV effectifs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Power d'un équipement = puissance MARGINALE qu'il ajoute à un perso de base (power(base+item) − power(base)).</t>
         </is>
@@ -686,6 +700,349 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>PV max</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Vit</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Crit %</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Crit dmg</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Esquive</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Poids spawn</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Lore</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>slime_titan</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Titan Visqueux</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 5
+auto_heal_per_turn = 32</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles et se régénère lentement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gobelin_warlord</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seigneur de Guerre Gobelin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>212</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>enrage_below_pct = 30
+enrage_attack_multiplier = 1.5
+adds = {'attack': 148, 'summon_turn_interval': 4, 'max_active': 3}</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie, et il appelle des renforts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>stone_colossus</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="n">
+        <v>209000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 27
+reflect_pct = 15</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles, sa carapace renvoie une part des coups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>186000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>473</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>crit_immunity = True
+phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée, et il mute en s'affaiblissant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>111000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>585</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>damage_immunity_threshold = 43
+enrage_below_pct = 25
+enrage_attack_multiplier = 1.8
+auto_heal_per_turn = 179
+reflect_pct = 20
+adds = {'attack': 351, 'summon_turn_interval': 5, 'max_active': 2}
+phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Le sommet de l'évolution. Inflige des coups dévastateurs, renvoie les frappes, invoque des drakelings, se régénère et entre en rage à la fin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8531,11 +8888,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -8611,24 +8968,600 @@
         <v>10</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Rend 10% des PV max (sans dépasser le maximum).</t>
+          <t>Rend 10 % des PV max (sans dépasser le maximum). Préparée par Elna, l'alchimiste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>potion_soin_superieure</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Potion de soin supérieure</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>heal_percent</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rend 35 % des PV max (sans dépasser le maximum).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>potion_mana</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Potion de mana</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>mana_percent</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Rend 50 % du mana max (sans dépasser le maximum).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>elixir_recuperation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Élixir de récupération</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pendant 1 h, tes PV et ton mana remontent 3 fois plus vite hors combat. Le reboire renouvelle sa durée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>elixir_force</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Élixir de force</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>+10 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>elixir_garde</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Élixir de garde</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>+10 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>elixir_vitalite</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Élixir de vitalité</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>+10 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Potion</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Effet</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Ingrédients</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Or × niveau</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Or au niveau 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Potion de soin</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>potion_soin</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>rend 10 % de tes PV</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2 × Gelée</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Potion de soin supérieure</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>potion_soin_superieure</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rend 35 % de tes PV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4 × Gelée + 2 × Dent de gobelin</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Potion de mana</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>potion_mana</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>rend 50 % de ton mana</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>3 × Fragment d'âme</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Élixir de récupération</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>elixir_recuperation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>régénération des PV et du mana ×3 hors combat pendant 1 h</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3 × Dent de gobelin + 2 × Fragment d'âme</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Élixir de force</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>elixir_force</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+10 % d'attaque pendant 1 h (combats de zone et world boss)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>3 × Cœur corrompu</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Élixir de garde</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>elixir_garde</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+10 % de défense pendant 1 h (combats de zone et world boss)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2 × Cœur corrompu + 2 × Fragment d'âme</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Élixir de vitalité</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>elixir_vitalite</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+10 % de PV max pendant 1 h (combats de zone et world boss)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2 × Cœur corrompu + 2 × Dent de gobelin</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Maîtrise</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Potions préparées</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Remise</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Potion offerte</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Apprentie</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Compagne</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Maîtresse</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>120</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Légendaire</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>20 %</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8983,17 +9916,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -9044,47 +9977,13 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>potion_soin</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Potion de soin</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>consumable</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13933,7 +14832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15179,347 +16078,4 @@
   <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Famille</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>PV max</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Def</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Vit</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Crit %</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Crit dmg</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Esquive</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Modifiers</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Poids spawn</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Lore</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>slime_titan</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Titan Visqueux</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
-      <c r="D2" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 5
-auto_heal_per_turn = 32</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Un slime ancestral devenu colosse, sa masse étouffante absorbe les coups les plus faibles et se régénère lentement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gobelin_warlord</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Seigneur de Guerre Gobelin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>212</v>
-      </c>
-      <c r="F3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>130</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>enrage_below_pct = 30
-enrage_attack_multiplier = 1.5
-adds = {'attack': 148, 'summon_turn_interval': 4, 'max_active': 3}</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Le chef d'une horde sanguinaire. Plus il est blessé, plus sa rage l'amplifie, et il appelle des renforts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>stone_colossus</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Colosse de Pierre</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>209000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 27
-reflect_pct = 15</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Une statue runique animée par d'antiques magies. Inébranlable face aux frappes faibles, sa carapace renvoie une part des coups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>shadow_wraith</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Spectre des Ténèbres</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>186000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>473</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>crit_immunity = True
-phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Une entité incorporelle qui glisse entre les coups. Les coups critiques traversent sa forme étherée, et il mute en s'affaiblissant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ancient_dragon</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Dragon Ancestral</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="n">
-        <v>111000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>585</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>damage_immunity_threshold = 43
-enrage_below_pct = 25
-enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 179
-reflect_pct = 20
-adds = {'attack': 351, 'summon_turn_interval': 5, 'max_active': 2}
-phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Le sommet de l'évolution. Inflige des coups dévastateurs, renvoie les frappes, invoque des drakelings, se régénère et entre en rage à la fin.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,10 +22,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⚗️ Alchimie'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$I$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-26 07:25 UTC</t>
+          <t>Généré le 2026-10-26 10:11 UTC</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prix d'achat / vente du shop.</t>
+          <t>L'étal de Sorn : outils (cor, sceau, parchemin, jeton, sablier) et cosmétiques.</t>
         </is>
       </c>
     </row>
@@ -8888,11 +8888,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -9195,8 +9195,484 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cor_chasse_f</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cor de chasse de la Clairière</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>summon_elite</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>cor_chasse_e</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Cor de chasse du Cimetière</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>summon_elite</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de le Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cor_chasse_d</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cor de chasse du Berceau</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>summon_elite</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de le Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_e</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang E)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sceau_souffle_d</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang D)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_c</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang C)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sceau_souffle_b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang B)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_a</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang A)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sceau_souffle_s</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang S)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_ss</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SS)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sceau_souffle_sss</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SSS)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>parchemin_oubli</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Parchemin d'oubli</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>respec_stats</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>jeton_arbre</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jeton de réinitialisation d'arbre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>reset_tree</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>sablier_fidelite</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Sablier de fidélité</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>daily_guard</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9922,17 +10398,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9953,22 +10430,22 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Rareté</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Prix achat</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Prix vente max</t>
-        </is>
-      </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Prix vente min</t>
+          <t>Prix × niveau</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Seuil stock</t>
+          <t>Un seul à la fois</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
@@ -9976,9 +10453,1364 @@
           <t>Activé</t>
         </is>
       </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>cor_chasse_f</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Cor de chasse de la Clairière</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cor_chasse_e</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cor de chasse du Cimetière</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de le Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>cor_chasse_d</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Cor de chasse du Berceau</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Fait apparaître l'élite de le Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_e</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang E)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>700</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_d</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang D)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sceau_souffle_c</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang C)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_b</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang B)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sceau_souffle_a</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang A)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_s</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang S)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sceau_souffle_ss</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SS)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_sss</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SSS)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>parchemin_oubli</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Parchemin d'oubli</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>150</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>jeton_arbre</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Jeton de réinitialisation d'arbre</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sablier_fidelite</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sablier de fidélité</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>fond_aube_rosee</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Fond — Aube rosée</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fond_foret_emeraude</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fond — Forêt d'émeraude</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>fond_ocean_profond</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Fond — Océan profond</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fond_braises</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fond — Braises du Berceau</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>fond_crepuscule_dore</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Fond — Crépuscule doré</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fond_aurore_boreale</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fond — Aurore boréale</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>cadre_argent</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Cadre — Argent</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cadre_jade</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cadre — Jade</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>cadre_amethyste</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Cadre — Améthyste</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cadre_or_royal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cadre — Or royal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cadre_sakura_eternel</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Cadre — Sakura éternel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>titre_ivoire</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Titre — Ivoire</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>titre_azur</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Titre — Azur</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>titre_emeraude</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Titre — Émeraude</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>titre_rubis</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Titre — Rubis</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>titre_or_flamboyant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Titre — Or flamboyant</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,12 +22,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⚗️ Alchimie'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⚗️ Alchimie'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'🌳 Skill Tree'!$A$1:$M$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'🏷️ Titres'!$A$1:$H$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'🐉 World Bosses'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-26 10:11 UTC</t>
+          <t>Généré le 2026-10-26 13:23 UTC</t>
         </is>
       </c>
     </row>
@@ -8888,10 +8888,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -9198,12 +9198,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cor_chasse_f</t>
+          <t>grande_potion_soin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cor de chasse de la Clairière</t>
+          <t>Grande potion de soin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9213,10 +9213,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>summon_elite</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>heal_percent</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -9225,19 +9227,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Rend 60 % des PV max (sans dépasser le maximum).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>cor_chasse_e</t>
+          <t>grande_potion_mana</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Cor de chasse du Cimetière</t>
+          <t>Grande potion de mana</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -9247,10 +9249,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>summon_elite</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
+          <t>mana_percent</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
@@ -9259,19 +9263,19 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de le Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Rend tout le mana.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cor_chasse_d</t>
+          <t>elixir_recuperation_sup</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cor de chasse du Berceau</t>
+          <t>Élixir de récupération supérieur</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9281,10 +9285,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>summon_elite</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
@@ -9293,19 +9299,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de le Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Pendant 1 h, tes PV et ton mana remontent 5 fois plus vite hors combat. Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_e</t>
+          <t>elixir_force_sup</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang E)</t>
+          <t>Élixir de force supérieur</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -9315,10 +9321,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>trial_retry</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
@@ -9327,19 +9335,19 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
+          <t>+20 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sceau_souffle_d</t>
+          <t>elixir_garde_sup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang D)</t>
+          <t>Élixir de garde supérieur</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9349,10 +9357,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>trial_retry</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
@@ -9361,19 +9371,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+          <t>+20 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_c</t>
+          <t>elixir_vitalite_sup</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang C)</t>
+          <t>Élixir de vitalité supérieur</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -9383,10 +9393,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>trial_retry</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
@@ -9395,19 +9407,19 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+          <t>+20 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sceau_souffle_b</t>
+          <t>cor_chasse_f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang B)</t>
+          <t>Cor de chasse de la Clairière</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9417,7 +9429,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -9429,19 +9441,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_a</t>
+          <t>cor_chasse_e</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang A)</t>
+          <t>Cor de chasse du Cimetière</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -9451,7 +9463,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
@@ -9463,19 +9475,19 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite du Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sceau_souffle_s</t>
+          <t>cor_chasse_d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang S)</t>
+          <t>Cor de chasse du Berceau</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9485,7 +9497,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -9497,19 +9509,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite du Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_ss</t>
+          <t>cor_chasse_c</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SS)</t>
+          <t>Cor de chasse du Sanctuaire</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -9519,7 +9531,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
@@ -9531,19 +9543,19 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite du Sanctuaire primordial (rang C) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sceau_souffle_sss</t>
+          <t>cor_chasse_b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SSS)</t>
+          <t>Cor de chasse de l'Éclipse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9553,7 +9565,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -9565,19 +9577,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite de l'Éclipse éternelle (rang B) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>parchemin_oubli</t>
+          <t>cor_chasse_a</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Parchemin d'oubli</t>
+          <t>Cor de chasse des Cimes</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -9587,7 +9599,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>respec_stats</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
@@ -9599,19 +9611,19 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+          <t>Fait apparaître l'élite des Cimes des Wyrms (rang A) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jeton_arbre</t>
+          <t>sceau_souffle_e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jeton de réinitialisation d'arbre</t>
+          <t>Sceau du second souffle (rang E)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9621,7 +9633,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>reset_tree</t>
+          <t>trial_retry</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -9633,19 +9645,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>sablier_fidelite</t>
+          <t>sceau_souffle_d</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Sablier de fidélité</t>
+          <t>Sceau du second souffle (rang D)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -9655,7 +9667,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>daily_guard</t>
+          <t>trial_retry</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -9667,12 +9679,318 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sceau_souffle_c</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang C)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_b</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang B)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sceau_souffle_a</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang A)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_s</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang S)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sceau_souffle_ss</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SS)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>sceau_souffle_sss</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Sceau du second souffle (rang SSS)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>trial_retry</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>parchemin_oubli</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Parchemin d'oubli</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>respec_stats</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>jeton_arbre</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Jeton de réinitialisation d'arbre</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>reset_tree</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sablier_fidelite</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sablier de fidélité</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>daily_guard</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9683,13 +10001,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
@@ -9922,117 +10240,285 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Grande potion de soin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>grande_potion_soin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rend 60 % de tes PV</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3 × Croc primordial</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>300</v>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Maîtrise</t>
+          <t>Grande potion de mana</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Potions préparées</t>
+          <t>grande_potion_mana</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Remise</t>
+          <t>rend 100 % de ton mana</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Potion offerte</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+          <t>3 × Sang lunaire</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apprentie</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
+          <t>Élixir de récupération supérieur</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>elixir_recuperation_sup</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>régénération des PV et du mana ×5 hors combat pendant 1 h</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0 %</t>
-        </is>
+          <t>3 × Sang lunaire + 2 × Croc primordial</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Compagne</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>30</v>
+          <t>Élixir de force supérieur</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>elixir_force_sup</t>
+        </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5 %</t>
+          <t>+20 % d'attaque pendant 1 h (combats de zone et world boss)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0 %</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+          <t>3 × Écaille de dragon</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maîtresse</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>120</v>
+          <t>Élixir de garde supérieur</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>elixir_garde_sup</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>+20 % de défense pendant 1 h (combats de zone et world boss)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10 %</t>
-        </is>
+          <t>2 × Écaille de dragon + 2 × Sang lunaire</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>Élixir de vitalité supérieur</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>elixir_vitalite_sup</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+20 % de PV max pendant 1 h (combats de zone et world boss)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2 × Écaille de dragon + 2 × Croc primordial</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Maîtrise</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Potions préparées</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Remise</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Potion offerte</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Apprentie</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Compagne</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Maîtresse</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>Légendaire</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B20" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>15 %</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>20 %</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10398,7 +10884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10545,7 +11031,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de le Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite du Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
@@ -10590,19 +11076,19 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de le Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite du Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sceau_souffle_e</t>
+          <t>cor_chasse_c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang E)</t>
+          <t>Cor de chasse du Sanctuaire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10616,7 +11102,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -10630,24 +11116,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite du Sanctuaire primordial (rang C) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_d</t>
+          <t>cor_chasse_b</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang D)</t>
+          <t>Cor de chasse de l'Éclipse</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -10661,7 +11147,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -10675,24 +11161,24 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite de l'Éclipse éternelle (rang B) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sceau_souffle_c</t>
+          <t>cor_chasse_a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang C)</t>
+          <t>Cor de chasse des Cimes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10706,7 +11192,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -10720,24 +11206,24 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite des Cimes des Wyrms (rang A) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_b</t>
+          <t>sceau_souffle_e</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang B)</t>
+          <t>Sceau du second souffle (rang E)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -10751,7 +11237,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -10770,19 +11256,19 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sceau_souffle_a</t>
+          <t>sceau_souffle_d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang A)</t>
+          <t>Sceau du second souffle (rang D)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10796,7 +11282,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3800</v>
+        <v>1500</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -10815,19 +11301,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_s</t>
+          <t>sceau_souffle_c</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang S)</t>
+          <t>Sceau du second souffle (rang C)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -10841,7 +11327,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -10860,19 +11346,19 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sceau_souffle_ss</t>
+          <t>sceau_souffle_b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SS)</t>
+          <t>Sceau du second souffle (rang B)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10886,7 +11372,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5300</v>
+        <v>3000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -10905,19 +11391,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_sss</t>
+          <t>sceau_souffle_a</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SSS)</t>
+          <t>Sceau du second souffle (rang A)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10931,7 +11417,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6000</v>
+        <v>3800</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -10950,19 +11436,19 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>parchemin_oubli</t>
+          <t>sceau_souffle_s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Parchemin d'oubli</t>
+          <t>Sceau du second souffle (rang S)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10975,39 +11461,39 @@
           <t>common</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>150</v>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>jeton_arbre</t>
+          <t>sceau_souffle_ss</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Jeton de réinitialisation d'arbre</t>
+          <t>Sceau du second souffle (rang SS)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -11020,39 +11506,39 @@
           <t>common</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>60</v>
-      </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sablier_fidelite</t>
+          <t>sceau_souffle_sss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sablier de fidélité</t>
+          <t>Sceau du second souffle (rang SSS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11066,7 +11552,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -11075,34 +11561,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>fond_aube_rosee</t>
+          <t>parchemin_oubli</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Fond — Aube rosée</t>
+          <t>Parchemin d'oubli</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>cosmetic</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -11110,14 +11596,14 @@
           <t>common</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="F16" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>oui</t>
@@ -11130,24 +11616,24 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fond_foret_emeraude</t>
+          <t>jeton_arbre</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fond — Forêt d'émeraude</t>
+          <t>Jeton de réinitialisation d'arbre</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cosmetic</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11155,14 +11641,14 @@
           <t>common</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>oui</t>
@@ -11175,33 +11661,33 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>fond_ocean_profond</t>
+          <t>sablier_fidelite</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Fond — Océan profond</t>
+          <t>Sablier de fidélité</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>cosmetic</t>
+          <t>consumable</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -11220,19 +11706,19 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fond_braises</t>
+          <t>fond_aube_rosee</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fond — Braises du Berceau</t>
+          <t>Fond — Aube rosée</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11242,11 +11728,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11272,12 +11758,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>fond_crepuscule_dore</t>
+          <t>fond_foret_emeraude</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Fond — Crépuscule doré</t>
+          <t>Fond — Forêt d'émeraude</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -11287,11 +11773,11 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -11317,12 +11803,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fond_aurore_boreale</t>
+          <t>fond_ocean_profond</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fond — Aurore boréale</t>
+          <t>Fond — Océan profond</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11332,11 +11818,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11362,12 +11848,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>cadre_argent</t>
+          <t>fond_braises</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Cadre — Argent</t>
+          <t>Fond — Braises du Berceau</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -11377,11 +11863,11 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -11400,19 +11886,19 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cadre_jade</t>
+          <t>fond_crepuscule_dore</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cadre — Jade</t>
+          <t>Fond — Crépuscule doré</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11422,11 +11908,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -11445,19 +11931,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>cadre_amethyste</t>
+          <t>fond_aurore_boreale</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Cadre — Améthyste</t>
+          <t>Fond — Aurore boréale</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -11467,11 +11953,11 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>10000</v>
+        <v>150000</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -11490,19 +11976,19 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change le fond de ta bannière /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cadre_or_royal</t>
+          <t>cadre_argent</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cadre — Or royal</t>
+          <t>Cadre — Argent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11512,11 +11998,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -11542,12 +12028,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>cadre_sakura_eternel</t>
+          <t>cadre_jade</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Cadre — Sakura éternel</t>
+          <t>Cadre — Jade</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -11557,11 +12043,11 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>150000</v>
+        <v>2000</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -11587,12 +12073,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>titre_ivoire</t>
+          <t>cadre_amethyste</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Titre — Ivoire</t>
+          <t>Cadre — Améthyste</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11602,11 +12088,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -11625,19 +12111,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>titre_azur</t>
+          <t>cadre_or_royal</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Titre — Azur</t>
+          <t>Cadre — Or royal</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -11647,11 +12133,11 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -11670,19 +12156,19 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>titre_emeraude</t>
+          <t>cadre_sakura_eternel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Titre — Émeraude</t>
+          <t>Cadre — Sakura éternel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11692,11 +12178,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10000</v>
+        <v>150000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -11715,19 +12201,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+          <t>Cosmétique : change l'anneau autour de ton avatar sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>titre_rubis</t>
+          <t>titre_ivoire</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Titre — Rubis</t>
+          <t>Titre — Ivoire</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -11737,11 +12223,11 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -11767,50 +12253,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>titre_azur</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Titre — Azur</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>titre_emeraude</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Titre — Émeraude</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>titre_rubis</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Titre — Rubis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>cosmetic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>titre_or_flamboyant</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Titre — Or flamboyant</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>cosmetic</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>legendary</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E34" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Cosmétique : change la couleur de ton titre sur /profil. Aucun effet en combat. À choisir avec /apparence.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I31"/>
+  <autoFilter ref="A1:I34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16670,15 +17291,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
@@ -17595,7 +18216,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>gobelin_superieur / 50</t>
+          <t>gobelin_superieur / 25</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -17605,66 +18226,67 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>50 gobelins supérieurs tués. +5% drop rate sur cette espèce.</t>
+          <t>25 gobelins supérieurs vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mvp_world_boss</t>
+          <t>mort_vivant_slayer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MVP des World Boss</t>
+          <t>Pourfendeur de morts-vivants</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>🏆</t>
+          <t>💀</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>world_boss_mvp</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>champion_all_stats → value=2</t>
+          <t>mort-vivant / 100</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=mort-vivant, value=10
+damage_reduction_from_family → target=mort-vivant, value=10</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
+          <t>100 morts-vivants vaincus. +10% dégâts infligés et -10% dégâts subis face aux morts-vivants.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>tueur_slime_titan</t>
+          <t>demoniaque_slayer</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Titan Visqueux</t>
+          <t>Pourfendeur de démons</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>😈</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -17674,39 +18296,40 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>slime_titan / 1</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>demoniaque / 100</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=demoniaque, value=10
+damage_reduction_from_family → target=demoniaque, value=10</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
+          <t>100 démons vaincus. +10% dégâts infligés et -10% dégâts subis face aux démons.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tueur_gobelin_warlord</t>
+          <t>primordial_slayer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tueur du Seigneur de Guerre Gobelin</t>
+          <t>Pourfendeur de bêtes primordiales</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🐺</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,39 +18339,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>gobelin_warlord / 1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>primordial / 100</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=primordial, value=10
+damage_reduction_from_family → target=primordial, value=10</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
+          <t>100 bêtes primordiales vaincus. +10% dégâts infligés et -10% dégâts subis face aux bêtes primordiales.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>tueur_stone_colossus</t>
+          <t>nocturne_slayer</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Colosse de Pierre</t>
+          <t>Pourfendeur des ténèbres</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🦇</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -17758,39 +18382,40 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>stone_colossus / 1</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>nocturne / 100</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=nocturne, value=10
+damage_reduction_from_family → target=nocturne, value=10</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+          <t>100 créatures nocturnes vaincus. +10% dégâts infligés et -10% dégâts subis face aux créatures nocturnes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tueur_shadow_wraith</t>
+          <t>draconique_slayer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tueur du Spectre des Ténèbres</t>
+          <t>Pourfendeur de dragons</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🐉</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17800,39 +18425,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>shadow_wraith / 1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>draconique / 100</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=draconique, value=10
+damage_reduction_from_family → target=draconique, value=10</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+          <t>100 dragons vaincus. +10% dégâts infligés et -10% dégâts subis face aux dragons.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>tueur_ancient_dragon</t>
+          <t>abyssal_slayer</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Tueur du Dragon Ancestral</t>
+          <t>Pourfendeur du Néant</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>⚔️</t>
+          <t>🌌</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -17842,57 +18468,2032 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>world_boss_kill</t>
+          <t>kills_family</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>ancient_dragon / 1</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>crit_damage_flat → value=3</t>
+          <t>abyssal / 100</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>damage_bonus_vs_family → target=abyssal, value=10
+damage_reduction_from_family → target=abyssal, value=10</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+          <t>100 créatures du Néant vaincus. +10% dégâts infligés et -10% dégâts subis face aux créatures du Néant.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>squelette_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Squelette</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>squelette / 50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=squelette, value=5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>50 × Squelette vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>zombie_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Zombie</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>zombie / 50</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=zombie, value=5</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>50 × Zombie vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>momie_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Momie</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>momie / 50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=momie, value=5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>50 × Momie vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>fantome_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Fantôme</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>fantome / 50</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=fantome, value=5</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>50 × Fantôme vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gargouille_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gargouille</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>gargouille / 50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gargouille, value=5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>50 × Gargouille vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>diablotin_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Diablotin</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>diablotin / 50</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=diablotin, value=5</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>50 × Diablotin vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>banshee_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Banshee</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>banshee / 50</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=banshee, value=5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>50 × Banshee vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>loup_sacre_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Loup sacré</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>loup_sacre / 50</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=loup_sacre, value=5</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>50 × Loup sacré vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cerf_esprit_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Cerf-esprit</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>cerf_esprit / 50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=cerf_esprit, value=5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>50 × Cerf-esprit vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>serpent_des_racines_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Serpent des racines</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>serpent_des_racines / 50</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=serpent_des_racines, value=5</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>50 × Serpent des racines vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>demon_cornu_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Démon cornu</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>demon_cornu / 50</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=demon_cornu, value=5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>50 × Démon cornu vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ours_colosse_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Ours colosse</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>ours_colosse / 50</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=ours_colosse, value=5</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>50 × Ours colosse vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>liche_maudite_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Liche maudite</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>liche_maudite / 25</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=liche_maudite, value=5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>25 × Liche maudite vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>golem_de_mousse_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Golem de mousse</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>golem_de_mousse / 50</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=golem_de_mousse, value=5</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>50 × Golem de mousse vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>aigle_tempete_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Aigle-tempête</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>aigle_tempete / 25</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=aigle_tempete, value=5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>25 × Aigle-tempête vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>chauve_souris_geante_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Chauve-souris géante</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>chauve_souris_geante / 50</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=chauve_souris_geante, value=5</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>50 × Chauve-souris géante vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>goule_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Goule</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>goule / 50</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=goule, value=5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>50 × Goule vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>loup_garou_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Loup-garou</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>loup_garou / 50</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=loup_garou, value=5</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>50 × Loup-garou vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ogre_demoniaque_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Ogre démoniaque</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ogre_demoniaque / 50</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=ogre_demoniaque, value=5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>50 × Ogre démoniaque vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>sorciere_de_sang_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Sorcière de sang</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>sorciere_de_sang / 50</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=sorciere_de_sang, value=5</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>50 × Sorcière de sang vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>chevalier_de_l_eclipse_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Chevalier de l'éclipse</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>chevalier_de_l_eclipse / 50</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=chevalier_de_l_eclipse, value=5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>50 × Chevalier de l'éclipse vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>vampire_noble_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Vampire noble</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>vampire_noble / 50</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=vampire_noble, value=5</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>50 × Vampire noble vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>comtesse_ecarlate_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Comtesse écarlate</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>comtesse_ecarlate / 25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=comtesse_ecarlate, value=5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>25 × Comtesse écarlate vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>kobold_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Kobold</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>kobold / 50</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=kobold, value=5</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>50 × Kobold vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cerbere_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Cerbère</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>cerbere / 50</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=cerbere, value=5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>50 × Cerbère vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>dragonnet_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Dragonnet</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>dragonnet / 50</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=dragonnet, value=5</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>50 × Dragonnet vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>drake_de_braise_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Drake de braise</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>drake_de_braise / 50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=drake_de_braise, value=5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>50 × Drake de braise vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>wyverne_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Wyverne</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>wyverne / 50</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=wyverne, value=5</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>50 × Wyverne vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>dragon_de_givre_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Dragon de givre</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>dragon_de_givre / 50</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=dragon_de_givre, value=5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>50 × Dragon de givre vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>succube_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Succube</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>succube / 50</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=succube, value=5</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>50 × Succube vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gardien_draconique_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Gardien draconique</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>gardien_draconique / 50</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=gardien_draconique, value=5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>50 × Gardien draconique vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>dragon_ancien_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Dragon ancien</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>dragon_ancien / 25</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=dragon_ancien, value=5</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>25 × Dragon ancien vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>rejeton_du_neant_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Rejeton du néant</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>rejeton_du_neant / 50</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=rejeton_du_neant, value=5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>50 × Rejeton du néant vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>oeil_errant_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Œil errant</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>oeil_errant / 50</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=oeil_errant, value=5</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>50 × Œil errant vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ange_dechu_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Ange déchu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ange_dechu / 50</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=ange_dechu, value=5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>50 × Ange déchu vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>devoreur_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Dévoreur</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>devoreur / 50</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=devoreur, value=5</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>50 × Dévoreur vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>heraut_du_vide_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Héraut du vide</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>heraut_du_vide / 50</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=heraut_du_vide, value=5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>50 × Héraut du vide vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>kraken_astral_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Kraken astral</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>kraken_astral / 50</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=kraken_astral, value=5</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>50 × Kraken astral vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>seraphin_brise_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Séraphin brisé</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>seraphin_brise / 50</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=seraphin_brise, value=5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>50 × Séraphin brisé vaincus. +5% drop rate sur cette espèce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>archidemon_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Archidémon</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>archidemon / 25</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=archidemon, value=5</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>25 × Archidémon vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>avatar_du_neant_chasseur_legendaire</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chasseur Légendaire — Avatar du Néant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>🏹</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>kills_mob</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>avatar_du_neant / 25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>drop_rate_bonus_vs_mob → target=avatar_du_neant, value=5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>25 × Avatar du Néant vaincus. +5% drop rate sur cette espèce. (élite de groupe : 25 suffisent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>mvp_world_boss</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>MVP des World Boss</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_mvp</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>champion_all_stats → value=2</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Meilleur contributeur du dernier world boss vaincu. +2% sur toutes vos stats. Transmis au MVP du prochain boss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tueur_slime_titan</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tueur du Titan Visqueux</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>slime_titan / 1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Titan Visqueux. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>tueur_gobelin_warlord</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Seigneur de Guerre Gobelin</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>gobelin_warlord / 1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Seigneur de Guerre Gobelin. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>tueur_stone_colossus</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tueur du Colosse de Pierre</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>stone_colossus / 1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Colosse de Pierre. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>tueur_shadow_wraith</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Tueur du Spectre des Ténèbres</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>shadow_wraith / 1</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Spectre des Ténèbres. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>tueur_ancient_dragon</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tueur du Dragon Ancestral</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>⚔️</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>world_boss_kill</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ancient_dragon / 1</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>crit_damage_flat → value=3</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>A participé à la victoire contre Dragon Ancestral. +3 dégâts critiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
           <t>ma_survie_avant_tout</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Ma survie avant tout</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>🛡️</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>dodge_flat → value=1
 speed_flat → value=1
@@ -17900,14 +20501,14 @@
 hp_max_flat → value=200</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>A ignoré une « petite fille » qui s'est révélée être un monstre déguisé — l'instinct de survie récompensé. Esquive +1%, Vitesse +1, Défense +10, PV max +200.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-26 13:23 UTC</t>
+          <t>Généré le 2026-10-27 07:50 UTC</t>
         </is>
       </c>
     </row>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -5632,10 +5632,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>5</v>
@@ -5701,10 +5701,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>30</v>
@@ -5732,27 +5732,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>squelette</t>
+          <t>gobelin_chaman</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Squelette</t>
+          <t>Gobelin Chaman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mort-vivant</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="E5" t="n">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -5770,13 +5770,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O5" s="6">
         <f>ROUND((E5*(1+(H5/100)*MAX(0,I5-100)/100)*(1+G5/100))*((D5+F5*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J5/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -5789,24 +5789,24 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>squelette.png</t>
+          <t>gobelin_chaman.png</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Un pantin d'os réanimé. Le premier pas dans le royaume des morts.</t>
+          <t>Une créature intelligente.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman</t>
+          <t>gobelin_ballon</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Chaman</t>
+          <t>Gobelin Ballon</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>5</v>
@@ -5839,13 +5839,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O6" s="6">
         <f>ROUND((E6*(1+(H6/100)*MAX(0,I6-100)/100)*(1+G6/100))*((D6+F6*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J6/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -5858,39 +5858,39 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>gobelin_chaman.png</t>
+          <t>gobelin_ballon.png</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>Une créature intelligente.</t>
+          <t>Un groupe de créatures inventives.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>gobelin_geant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Gobelin Géant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mort-vivant</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -5908,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="N7" t="n">
         <v>20</v>
@@ -5927,24 +5927,24 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>zombie.png</t>
+          <t>gobelin_geant.png</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Une carcasse putride et lente, mais coriace.</t>
+          <t>Une créature imposante.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>gobelin_ballon</t>
+          <t>gobelin_runique</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Ballon</t>
+          <t>Gobelin Runique</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>5</v>
@@ -5977,10 +5977,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>20</v>
@@ -5996,24 +5996,24 @@
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>gobelin_ballon.png</t>
+          <t>gobelin_runique.png</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Un groupe de créatures inventives.</t>
+          <t>Une créature mystérieuse.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gobelin_geant</t>
+          <t>gobelin_assassin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gobelin Géant</t>
+          <t>Gobelin Assassin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6022,22 +6022,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6046,13 +6046,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O9" s="6">
         <f>ROUND((E9*(1+(H9/100)*MAX(0,I9-100)/100)*(1+G9/100))*((D9+F9*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J9/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6065,42 +6065,42 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>gobelin_geant.png</t>
+          <t>gobelin_assassin.png</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Une créature imposante.</t>
+          <t>Une créature discrète.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>momie</t>
+          <t>gobelin_superieur</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Momie</t>
+          <t>Gobelin Supérieur</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>mort-vivant</t>
+          <t>gobelin</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -6115,10 +6115,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>10</v>
@@ -6134,39 +6134,39 @@
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>momie.png</t>
+          <t>gobelin_superieur.png</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>Un corps embaumé aux bandelettes maudites, quasi increvable.</t>
+          <t>Une créature supérieure.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gobelin_runique</t>
+          <t>squelette</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gobelin Runique</t>
+          <t>Squelette</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -6184,13 +6184,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="M11" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="N11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O11" s="6">
         <f>ROUND((E11*(1+(H11/100)*MAX(0,I11-100)/100)*(1+G11/100))*((D11+F11*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J11/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6203,24 +6203,24 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>gobelin_runique.png</t>
+          <t>squelette.png</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Une créature mystérieuse.</t>
+          <t>Un pantin d'os réanimé. Le premier pas dans le royaume des morts.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>fantome</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Fantôme</t>
+          <t>Zombie</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -6229,37 +6229,37 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>188</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>15</v>
       </c>
       <c r="O12" s="6">
         <f>ROUND((E12*(1+(H12/100)*MAX(0,I12-100)/100)*(1+G12/100))*((D12+F12*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J12/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6272,48 +6272,48 @@
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>fantome.png</t>
+          <t>zombie.png</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Une âme errante insaisissable qui glisse entre les coups.</t>
+          <t>Une carcasse putride et lente, mais coriace.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gobelin_assassin</t>
+          <t>momie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gobelin Assassin</t>
+          <t>Momie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>238</v>
+        <v>341</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -6322,10 +6322,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="M13" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="N13" t="n">
         <v>10</v>
@@ -6341,48 +6341,48 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>gobelin_assassin.png</t>
+          <t>momie.png</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Une créature discrète.</t>
+          <t>Un corps embaumé aux bandelettes maudites, quasi increvable.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_superieur</t>
+          <t>fantome</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Gobelin Supérieur</t>
+          <t>Fantôme</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>gobelin</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1320</v>
+        <v>218</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -6391,13 +6391,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>656</v>
+        <v>169</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O14" s="6">
         <f>ROUND((E14*(1+(H14/100)*MAX(0,I14-100)/100)*(1+G14/100))*((D14+F14*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J14/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6410,12 +6410,12 @@
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>gobelin_superieur.png</t>
+          <t>fantome.png</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>Une créature supérieure.</t>
+          <t>Une âme errante insaisissable qui glisse entre les coups.</t>
         </is>
       </c>
     </row>
@@ -6436,13 +6436,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>426</v>
+        <v>337</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="M15" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="N15" t="n">
         <v>7</v>
@@ -6491,36 +6491,36 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>diablotin</t>
+          <t>banshee</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Diablotin</t>
+          <t>Banshee</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>mort-vivant</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -6529,13 +6529,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="O16" s="6">
         <f>ROUND((E16*(1+(H16/100)*MAX(0,I16-100)/100)*(1+G16/100))*((D16+F16*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J16/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6548,24 +6548,24 @@
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>diablotin.png</t>
+          <t>banshee.png</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>Petit démon espiègle et véloce, tout juste éclos du Berceau.</t>
+          <t>Un spectre hurlant dont le cri glaçant transperce l'âme.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>banshee</t>
+          <t>liche_maudite</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Banshee</t>
+          <t>Liche maudite</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6574,16 +6574,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>440</v>
+        <v>4013</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6598,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>281</v>
+        <v>619</v>
       </c>
       <c r="M17" t="n">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O17" s="6">
         <f>ROUND((E17*(1+(H17/100)*MAX(0,I17-100)/100)*(1+G17/100))*((D17+F17*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J17/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6617,42 +6617,42 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>banshee.png</t>
+          <t>liche_maudite.png</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Un spectre hurlant dont le cri glaçant transperce l'âme.</t>
+          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>loup_sacre</t>
+          <t>diablotin</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Loup sacré</t>
+          <t>Diablotin</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>20</v>
@@ -6667,10 +6667,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>40</v>
@@ -6684,40 +6684,44 @@
         <v/>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>diablotin.png</t>
+        </is>
+      </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Gardien à la fourrure d'argent ; il chasse en meute depuis l'aube des temps.</t>
+          <t>Petit démon espiègle et véloce, tout juste éclos du Berceau.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cerf_esprit</t>
+          <t>demon_cornu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cerf-esprit</t>
+          <t>Démon cornu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>583</v>
+        <v>451</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -6732,10 +6736,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="M19" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -6749,61 +6753,65 @@
         <v/>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>demon_cornu.png</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Un cerf translucide ; la forêt se tait sur son passage.</t>
+          <t>Fantassin cornu des légions infernales, brutal et sans pitié.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>serpent_des_racines</t>
+          <t>ogre_demoniaque</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Serpent des racines</t>
+          <t>Ogre démoniaque</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>25</v>
       </c>
       <c r="O20" s="6">
         <f>ROUND((E20*(1+(H20/100)*MAX(0,I20-100)/100)*(1+G20/100))*((D20+F20*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J20/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6814,22 +6822,26 @@
         <v/>
       </c>
       <c r="Q20" s="5" t="inlineStr"/>
-      <c r="R20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>ogre_demoniaque.png</t>
+        </is>
+      </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Il dort sous les racines et frappe d'un venin sylvestre.</t>
+          <t>Masse de muscles corrompue qui écrase tout sur son passage.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>demon_cornu</t>
+          <t>cerbere</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Démon cornu</t>
+          <t>Cerbère</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6838,16 +6850,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>638</v>
+        <v>495</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -6862,13 +6874,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="M21" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="N21" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O21" s="6">
         <f>ROUND((E21*(1+(H21/100)*MAX(0,I21-100)/100)*(1+G21/100))*((D21+F21*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J21/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6881,39 +6893,39 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>demon_cornu.png</t>
+          <t>cerbere.png</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Fantassin cornu des légions infernales, brutal et sans pitié.</t>
+          <t>Molosse à trois têtes gardant les portes de l'abîme.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ours_colosse</t>
+          <t>succube</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Ours colosse</t>
+          <t>Succube</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>510</v>
+        <v>414</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>7</v>
@@ -6931,13 +6943,13 @@
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>325</v>
+        <v>262</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O22" s="6">
         <f>ROUND((E22*(1+(H22/100)*MAX(0,I22-100)/100)*(1+G22/100))*((D22+F22*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J22/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -6948,37 +6960,41 @@
         <v/>
       </c>
       <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>succube.png</t>
+        </is>
+      </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Ses griffes fendent la pierre comme l'armure.</t>
+          <t>Démone envoûtante qui draine la vie de ses proies.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>liche_maudite</t>
+          <t>ange_dechu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liche maudite</t>
+          <t>Ange déchu</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mort-vivant</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9504</v>
+        <v>539</v>
       </c>
       <c r="E23" t="n">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
         <v>7</v>
@@ -6996,13 +7012,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1012</v>
+        <v>275</v>
       </c>
       <c r="M23" t="n">
-        <v>486</v>
+        <v>132</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O23" s="6">
         <f>ROUND((E23*(1+(H23/100)*MAX(0,I23-100)/100)*(1+G23/100))*((D23+F23*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J23/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7015,39 +7031,39 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>liche_maudite.png</t>
+          <t>ange_dechu.png</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Un sorcier mort-vivant dont la magie noire dévaste.</t>
+          <t>Ancien séraphin banni ; sa lumière s'est muée en fureur.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>golem_de_mousse</t>
+          <t>archidemon</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Golem de mousse</t>
+          <t>Archidémon</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>primordial</t>
+          <t>demoniaque</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>594</v>
+        <v>2970</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>7</v>
@@ -7065,13 +7081,13 @@
         <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>338</v>
+        <v>844</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O24" s="6">
         <f>ROUND((E24*(1+(H24/100)*MAX(0,I24-100)/100)*(1+G24/100))*((D24+F24*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J24/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7082,22 +7098,26 @@
         <v/>
       </c>
       <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>archidemon.png</t>
+        </is>
+      </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Un rocher couvert de mousse qui repousse plus vite qu'on ne l'arrache.</t>
+          <t>Seigneur des enfers, apogée de la corruption du Berceau.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aigle_tempete</t>
+          <t>loup_sacre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aigle-tempête</t>
+          <t>Loup sacré</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7106,13 +7126,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3274</v>
+        <v>337</v>
       </c>
       <c r="E25" t="n">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
         <v>13</v>
@@ -7130,13 +7150,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1050</v>
+        <v>288</v>
       </c>
       <c r="M25" t="n">
-        <v>504</v>
+        <v>138</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="O25" s="6">
         <f>ROUND((E25*(1+(H25/100)*MAX(0,I25-100)/100)*(1+G25/100))*((D25+F25*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J25/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7150,43 +7170,43 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Chacun de ses battements d'ailes soulève une bourrasque.</t>
+          <t>Gardien à la fourrure d'argent ; il chasse en meute depuis l'aube des temps.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>chauve_souris_geante</t>
+          <t>cerf_esprit</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Chauve-souris géante</t>
+          <t>Cerf-esprit</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>416</v>
+        <v>583</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
@@ -7195,13 +7215,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O26" s="6">
         <f>ROUND((E26*(1+(H26/100)*MAX(0,I26-100)/100)*(1+G26/100))*((D26+F26*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J26/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7215,43 +7235,43 @@
       <c r="R26" s="5" t="inlineStr"/>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Elle surgit de l'éclipse par nuées entières.</t>
+          <t>Un cerf translucide ; la forêt se tait sur son passage.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>goule</t>
+          <t>serpent_des_racines</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Goule</t>
+          <t>Serpent des racines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>715</v>
+        <v>363</v>
       </c>
       <c r="E27" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7260,13 +7280,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>362</v>
+        <v>312</v>
       </c>
       <c r="M27" t="n">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="N27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O27" s="6">
         <f>ROUND((E27*(1+(H27/100)*MAX(0,I27-100)/100)*(1+G27/100))*((D27+F27*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J27/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7280,37 +7300,37 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Elle rôde entre les tombes, affamée de chair fraîche.</t>
+          <t>Il dort sous les racines et frappe d'un venin sylvestre.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>loup_garou</t>
+          <t>ours_colosse</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Loup-garou</t>
+          <t>Ours colosse</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>590</v>
+        <v>510</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
@@ -7325,13 +7345,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O28" s="6">
         <f>ROUND((E28*(1+(H28/100)*MAX(0,I28-100)/100)*(1+G28/100))*((D28+F28*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J28/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7345,37 +7365,37 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Sous l'éclipse, la bête l'emporte sur l'homme — et sa rage grandit avec ses blessures.</t>
+          <t>Ses griffes fendent la pierre comme l'armure.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ogre_demoniaque</t>
+          <t>golem_de_mousse</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ogre démoniaque</t>
+          <t>Golem de mousse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="E29" t="n">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -7390,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="M29" t="n">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O29" s="6">
         <f>ROUND((E29*(1+(H29/100)*MAX(0,I29-100)/100)*(1+G29/100))*((D29+F29*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J29/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7407,50 +7427,46 @@
         <v/>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>ogre_demoniaque.png</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Masse de muscles corrompue qui écrase tout sur son passage.</t>
+          <t>Un rocher couvert de mousse qui repousse plus vite qu'on ne l'arrache.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>sorciere_de_sang</t>
+          <t>aigle_tempete</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Sorcière de sang</t>
+          <t>Aigle-tempête</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>nocturne</t>
+          <t>primordial</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>607</v>
+        <v>3274</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
@@ -7459,13 +7475,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>388</v>
+        <v>1050</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>186</v>
+        <v>504</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O30" s="6">
         <f>ROUND((E30*(1+(H30/100)*MAX(0,I30-100)/100)*(1+G30/100))*((D30+F30*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J30/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7479,19 +7495,19 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Elle appelle ses familiers d'un murmure.</t>
+          <t>Chacun de ses battements d'ailes soulève une bourrasque.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chevalier_de_l_eclipse</t>
+          <t>chauve_souris_geante</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chevalier de l'éclipse</t>
+          <t>Chauve-souris géante</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7500,22 +7516,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>713</v>
+        <v>416</v>
       </c>
       <c r="E31" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -7524,13 +7540,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="M31" t="n">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="N31" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="O31" s="6">
         <f>ROUND((E31*(1+(H31/100)*MAX(0,I31-100)/100)*(1+G31/100))*((D31+F31*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J31/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7544,19 +7560,19 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Son armure noire rend chaque coup à celui qui l'a porté.</t>
+          <t>Elle surgit de l'éclipse par nuées entières.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>vampire_noble</t>
+          <t>goule</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Vampire noble</t>
+          <t>Goule</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -7565,16 +7581,16 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>814</v>
+        <v>715</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
@@ -7589,13 +7605,13 @@
         <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O32" s="6">
         <f>ROUND((E32*(1+(H32/100)*MAX(0,I32-100)/100)*(1+G32/100))*((D32+F32*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J32/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7609,19 +7625,19 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Il boit la vie de ses adversaires avec élégance.</t>
+          <t>Elle rôde entre les tombes, affamée de chair fraîche.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>comtesse_ecarlate</t>
+          <t>loup_garou</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Comtesse écarlate</t>
+          <t>Loup-garou</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7630,22 +7646,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8910</v>
+        <v>590</v>
       </c>
       <c r="E33" t="n">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -7654,13 +7670,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1256</v>
+        <v>375</v>
       </c>
       <c r="M33" t="n">
-        <v>603</v>
+        <v>180</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O33" s="6">
         <f>ROUND((E33*(1+(H33/100)*MAX(0,I33-100)/100)*(1+G33/100))*((D33+F33*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J33/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7674,34 +7690,34 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Un regard, et ses ennemis se battent pour elle.</t>
+          <t>Sous l'éclipse, la bête l'emporte sur l'homme — et sa rage grandit avec ses blessures.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>kobold</t>
+          <t>sorciere_de_sang</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Kobold</t>
+          <t>Sorcière de sang</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>836</v>
+        <v>607</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>8</v>
@@ -7719,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="O34" s="6">
         <f>ROUND((E34*(1+(H34/100)*MAX(0,I34-100)/100)*(1+G34/100))*((D34+F34*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J34/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7739,34 +7755,34 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>Petit, rusé, armé d'une lance trop grande pour lui.</t>
+          <t>Elle appelle ses familiers d'un murmure.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cerbere</t>
+          <t>chevalier_de_l_eclipse</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cerbère</t>
+          <t>Chevalier de l'éclipse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>858</v>
+        <v>713</v>
       </c>
       <c r="E35" t="n">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G35" t="n">
         <v>8</v>
@@ -7784,10 +7800,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="M35" t="n">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="N35" t="n">
         <v>15</v>
@@ -7801,50 +7817,46 @@
         <v/>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>cerbere.png</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Molosse à trois têtes gardant les portes de l'abîme.</t>
+          <t>Son armure noire rend chaque coup à celui qui l'a porté.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>dragonnet</t>
+          <t>vampire_noble</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Dragonnet</t>
+          <t>Vampire noble</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>515</v>
+        <v>814</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
@@ -7853,13 +7865,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O36" s="6">
         <f>ROUND((E36*(1+(H36/100)*MAX(0,I36-100)/100)*(1+G36/100))*((D36+F36*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J36/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7873,43 +7885,43 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>Un jeune dragon, vif et capricieux.</t>
+          <t>Il boit la vie de ses adversaires avec élégance.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>drake_de_braise</t>
+          <t>comtesse_ecarlate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Drake de braise</t>
+          <t>Comtesse écarlate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>draconique</t>
+          <t>nocturne</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>704</v>
+        <v>8910</v>
       </c>
       <c r="E37" t="n">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I37" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7918,13 +7930,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>450</v>
+        <v>1256</v>
       </c>
       <c r="M37" t="n">
-        <v>216</v>
+        <v>603</v>
       </c>
       <c r="N37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="O37" s="6">
         <f>ROUND((E37*(1+(H37/100)*MAX(0,I37-100)/100)*(1+G37/100))*((D37+F37*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J37/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -7938,19 +7950,19 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Ses morsures laissent des brûlures qui couvent longtemps.</t>
+          <t>Un regard, et ses ennemis se battent pour elle.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>wyverne</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Wyverne</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -7959,22 +7971,22 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>541</v>
+        <v>836</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -7983,13 +7995,13 @@
         <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O38" s="6">
         <f>ROUND((E38*(1+(H38/100)*MAX(0,I38-100)/100)*(1+G38/100))*((D38+F38*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J38/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8003,19 +8015,19 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>Elle fond sur sa proie et frappe deux fois avant qu'on la voie.</t>
+          <t>Petit, rusé, armé d'une lance trop grande pour lui.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dragon_de_givre</t>
+          <t>dragonnet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dragon de givre</t>
+          <t>Dragonnet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8024,22 +8036,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>822</v>
+        <v>515</v>
       </c>
       <c r="E39" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I39" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8048,13 +8060,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="M39" t="n">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O39" s="6">
         <f>ROUND((E39*(1+(H39/100)*MAX(0,I39-100)/100)*(1+G39/100))*((D39+F39*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J39/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8068,34 +8080,34 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Son souffle fige le sang dans les veines.</t>
+          <t>Un jeune dragon, vif et capricieux.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>succube</t>
+          <t>drake_de_braise</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Succube</t>
+          <t>Drake de braise</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>8</v>
@@ -8113,13 +8125,13 @@
         <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O40" s="6">
         <f>ROUND((E40*(1+(H40/100)*MAX(0,I40-100)/100)*(1+G40/100))*((D40+F40*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J40/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8130,26 +8142,22 @@
         <v/>
       </c>
       <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>succube.png</t>
-        </is>
-      </c>
+      <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="5" t="inlineStr">
         <is>
-          <t>Démone envoûtante qui draine la vie de ses proies.</t>
+          <t>Ses morsures laissent des brûlures qui couvent longtemps.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gardien_draconique</t>
+          <t>wyverne</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gardien draconique</t>
+          <t>Wyverne</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8158,22 +8166,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>935</v>
+        <v>541</v>
       </c>
       <c r="E41" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="F41" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8182,13 +8190,13 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="M41" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O41" s="6">
         <f>ROUND((E41*(1+(H41/100)*MAX(0,I41-100)/100)*(1+G41/100))*((D41+F41*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J41/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8202,19 +8210,19 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Une écaille-bouclier le protège avant qu'on puisse l'atteindre.</t>
+          <t>Elle fond sur sa proie et frappe deux fois avant qu'on la voie.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>dragon_ancien</t>
+          <t>dragon_de_givre</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Dragon ancien</t>
+          <t>Dragon de givre</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -8223,13 +8231,13 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>19906</v>
+        <v>822</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>8</v>
@@ -8247,13 +8255,13 @@
         <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>1500</v>
+        <v>475</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>720</v>
+        <v>228</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O42" s="6">
         <f>ROUND((E42*(1+(H42/100)*MAX(0,I42-100)/100)*(1+G42/100))*((D42+F42*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J42/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8267,34 +8275,34 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="5" t="inlineStr">
         <is>
-          <t>Le maître des cimes. Blessé, il devient un brasier.</t>
+          <t>Son souffle fige le sang dans les veines.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rejeton_du_neant</t>
+          <t>gardien_draconique</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rejeton du néant</t>
+          <t>Gardien draconique</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abyssal</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>968</v>
+        <v>935</v>
       </c>
       <c r="E43" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G43" t="n">
         <v>8</v>
@@ -8312,13 +8320,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="M43" t="n">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="O43" s="6">
         <f>ROUND((E43*(1+(H43/100)*MAX(0,I43-100)/100)*(1+G43/100))*((D43+F43*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J43/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8332,43 +8340,43 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Une ombre qui a appris à marcher.</t>
+          <t>Une écaille-bouclier le protège avant qu'on puisse l'atteindre.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>oeil_errant</t>
+          <t>dragon_ancien</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Œil errant</t>
+          <t>Dragon ancien</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>abyssal</t>
+          <t>draconique</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>601</v>
+        <v>19906</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
@@ -8377,13 +8385,13 @@
         <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>525</v>
+        <v>1500</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>252</v>
+        <v>720</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O44" s="6">
         <f>ROUND((E44*(1+(H44/100)*MAX(0,I44-100)/100)*(1+G44/100))*((D44+F44*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J44/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8397,34 +8405,34 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="5" t="inlineStr">
         <is>
-          <t>Il flotte, il observe, il ne cligne jamais.</t>
+          <t>Le maître des cimes. Blessé, il devient un brasier.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ange_dechu</t>
+          <t>rejeton_du_neant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ange déchu</t>
+          <t>Rejeton du néant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>abyssal</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1034</v>
+        <v>968</v>
       </c>
       <c r="E45" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F45" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
         <v>8</v>
@@ -8442,13 +8450,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>544</v>
+        <v>506</v>
       </c>
       <c r="M45" t="n">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="N45" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O45" s="6">
         <f>ROUND((E45*(1+(H45/100)*MAX(0,I45-100)/100)*(1+G45/100))*((D45+F45*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J45/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8459,26 +8467,22 @@
         <v/>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>ange_dechu.png</t>
-        </is>
-      </c>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Ancien séraphin banni ; sa lumière s'est muée en fureur.</t>
+          <t>Une ombre qui a appris à marcher.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>devoreur</t>
+          <t>oeil_errant</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Dévoreur</t>
+          <t>Œil errant</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -8487,22 +8491,22 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>827</v>
+        <v>601</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J46" s="5" t="n">
         <v>0</v>
@@ -8511,13 +8515,13 @@
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O46" s="6">
         <f>ROUND((E46*(1+(H46/100)*MAX(0,I46-100)/100)*(1+G46/100))*((D46+F46*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J46/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8531,19 +8535,19 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="5" t="inlineStr">
         <is>
-          <t>Il se nourrit de tout ce qu'il touche — et se referme sur ses plaies.</t>
+          <t>Il flotte, il observe, il ne cligne jamais.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>heraut_du_vide</t>
+          <t>devoreur</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Héraut du vide</t>
+          <t>Dévoreur</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8552,13 +8556,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1067</v>
+        <v>827</v>
       </c>
       <c r="E47" t="n">
-        <v>168</v>
+        <v>245</v>
       </c>
       <c r="F47" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G47" t="n">
         <v>8</v>
@@ -8576,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="M47" t="n">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="N47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O47" s="6">
         <f>ROUND((E47*(1+(H47/100)*MAX(0,I47-100)/100)*(1+G47/100))*((D47+F47*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J47/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8596,19 +8600,19 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Il ouvre des failles d'où rampent d'autres créatures.</t>
+          <t>Il se nourrit de tout ce qu'il touche — et se referme sur ses plaies.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>kraken_astral</t>
+          <t>heraut_du_vide</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Kraken astral</t>
+          <t>Héraut du vide</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -8617,13 +8621,13 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>990</v>
+        <v>1067</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>8</v>
@@ -8641,13 +8645,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O48" s="6">
         <f>ROUND((E48*(1+(H48/100)*MAX(0,I48-100)/100)*(1+G48/100))*((D48+F48*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J48/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8661,19 +8665,19 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="5" t="inlineStr">
         <is>
-          <t>Ses tentacules frappent de toutes parts et engourdissent.</t>
+          <t>Il ouvre des failles d'où rampent d'autres créatures.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>seraphin_brise</t>
+          <t>kraken_astral</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Séraphin brisé</t>
+          <t>Kraken astral</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8682,13 +8686,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>906</v>
+        <v>990</v>
       </c>
       <c r="E49" t="n">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G49" t="n">
         <v>8</v>
@@ -8706,13 +8710,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="M49" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="N49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O49" s="6">
         <f>ROUND((E49*(1+(H49/100)*MAX(0,I49-100)/100)*(1+G49/100))*((D49+F49*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J49/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8726,34 +8730,34 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Un ange tombé dans la faille ; il refuse de mourir.</t>
+          <t>Ses tentacules frappent de toutes parts et engourdissent.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>archidemon</t>
+          <t>seraphin_brise</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Archidémon</t>
+          <t>Séraphin brisé</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>demoniaque</t>
+          <t>abyssal</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>18533</v>
+        <v>906</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>381</v>
+        <v>270</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>8</v>
@@ -8771,13 +8775,13 @@
         <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1819</v>
+        <v>600</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>873</v>
+        <v>288</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O50" s="6">
         <f>ROUND((E50*(1+(H50/100)*MAX(0,I50-100)/100)*(1+G50/100))*((D50+F50*'⚙️ Calibrage'!$B$9)/MAX(0.01,1-J50/100))/'⚙️ Calibrage'!$B$10,0)</f>
@@ -8788,14 +8792,10 @@
         <v/>
       </c>
       <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>archidemon.png</t>
-        </is>
-      </c>
+      <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="5" t="inlineStr">
         <is>
-          <t>Seigneur des enfers, apogée de la corruption du Berceau.</t>
+          <t>Un ange tombé dans la faille ; il refuse de mourir.</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
         <v>21186</v>
       </c>
       <c r="E51" t="n">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="F51" t="n">
         <v>48</v>
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 07:50 UTC</t>
+          <t>Généré le 2026-10-27 08:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Festin de chair — Chaque ennemi vaincu te rend 25 % de tes PV max.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Embuscade — +25 % de dégâts contre un ennemi qui n'a pas encore agi.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Soif écarlate — Tes coups critiques te soignent de 20 % des dégâts infligés.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Miroir d'éclipse — 15 % des dégâts que tu reçois sont renvoyés à l'attaquant.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Morsure du givre — 15 % de chance de geler l'ennemi qui te frappe : il perd sa prochaine action (pas les boss).</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pacte de sang — À court de mana, tes compétences se paient en PV : 5 % de tes PV max, et l'érosion réduit tes PV max de 5 % pour le reste du combat.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Échos du vide — Toutes les 8 actions, un écho frappe la cible (50 % de ton attaque, sans défense) et absorbe le prochain coup que tu reçois.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Piqué — Ta première attaque frappe 3 fois, à 60 % chacune.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ramure bienveillante — Tout le groupe reçoit 15 % de soins en plus (une seule ramure par groupe).</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rage lunaire — Sous 50 % de PV : +15 % d'attaque et de vitesse.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Coup de patte brisant — Chaque coup réduit la défense de l'ennemi de 3 % pour le combat (max −15 %, non cumulable).</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vol nocturne — +5 % d'esquive tant que tu es au-dessus de 50 % de tes PV.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grâce brisée — Le premier allié qui tombe se relève avec 30 % de ses PV (une fois par combat).</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Valse sanglante — Après chaque esquive, ton coup suivant est un critique qui fait saigner (10 % des dégâts à chaque action de l'ennemi, 3 actions, jusqu'à 3 fois).</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Instinct de meute — +3 % de dégâts par allié encore debout (max +9 %).</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Braise persistante — Tes critiques enflamment l'ennemi : −20 % d'attaque pendant 2 actions (non cumulable) et 10 % des dégâts du coup à chacune de ses 2 actions suivantes (cumulable).</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mousse vivace — La première fois que tu passes sous 30 % de PV, tu récupères 10 % de tes PV max à chacune de tes 7 actions suivantes.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Néant dévorant — Un coup sur deux ignore 50 % de la défense ennemie.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Souffle ancestral — Exécute la cible de ton attaque si elle passe sous 20 % de ses PV (les boss y sont immunisés).</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Souffle juvénile — Toutes les 5 attaques, des flammes frappent tous les ennemis (30 % de ton attaque, sans défense).</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Réserve abyssale — Tes compétences coûtent 20 % de mana en moins.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dévoration — Quand un allié meurt, tu gagnes 10 % de son attaque, de sa défense et de ses PV max pour le reste du combat.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Œil de la tempête — Ta première action frappe TOUS les ennemis, avec 50 % de chance d'étourdir chacun (pas les boss).</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Serment du gardien — Tant que tu provoques : −20 % de dégâts reçus pour toi, −10 % pour tes alliés.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Étreinte astrale — Tes coups ralentissent l'ennemi de 5 % (max −25 %, non cumulable).</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sève vénéneuse — Tes coups empoisonnent l'ennemi : 1 % de ses PV max à chacune de ses actions pendant 3 actions, au plus 25 % de ton attaque (non cumulable).</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Regard du vide — L'ennemi ne peut pas esquiver tes coups.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 08:03 UTC</t>
+          <t>Généré le 2026-10-27 08:16 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 08:16 UTC</t>
+          <t>Généré le 2026-10-27 08:36 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 08:36 UTC</t>
+          <t>Généré le 2026-10-27 09:40 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 09:40 UTC</t>
+          <t>Généré le 2026-10-27 11:35 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 11:35 UTC</t>
+          <t>Généré le 2026-10-27 14:47 UTC</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="n">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>110</v>
@@ -826,7 +826,7 @@
       <c r="K2" s="7" t="inlineStr">
         <is>
           <t>damage_immunity_threshold = 5
-auto_heal_per_turn = 32</t>
+auto_heal_per_turn = 30</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="E3" t="n">
         <v>212</v>
@@ -871,11 +871,9 @@
       <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>enrage_below_pct = 30
-enrage_attack_multiplier = 1.5
-adds = {'attack': 148, 'summon_turn_interval': 4, 'max_active': 3}</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adds = {'attack': 148, 'summon_turn_interval': 4, 'max_active': 3}</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -900,7 +898,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="n">
-        <v>209000</v>
+        <v>148000</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>350</v>
@@ -948,7 +946,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>186000</v>
+        <v>82000</v>
       </c>
       <c r="E5" t="n">
         <v>473</v>
@@ -968,10 +966,9 @@
       <c r="J5" t="n">
         <v>30</v>
       </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>crit_immunity = True
-phases = [{'below_pct': 50, 'attack_multiplier': 1.3}, {'below_pct': 20, 'attack_multiplier': 1.6}]</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>crit_immunity = True</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -996,7 +993,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="n">
-        <v>111000</v>
+        <v>66000</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>585</v>
@@ -1019,12 +1016,9 @@
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>damage_immunity_threshold = 43
-enrage_below_pct = 25
-enrage_attack_multiplier = 1.8
-auto_heal_per_turn = 179
+auto_heal_per_turn = 174
 reflect_pct = 20
-adds = {'attack': 351, 'summon_turn_interval': 5, 'max_active': 2}
-phases = [{'below_pct': 50, 'attack_multiplier': 1.25}]</t>
+adds = {'attack': 351, 'summon_turn_interval': 5, 'max_active': 2}</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">

--- a/docs/sakura_content.xlsx
+++ b/docs/sakura_content.xlsx
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🎽 Équipements'!$A$1:$T$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👹 Mobs'!$A$1:$S$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🧪 Consommables'!$A$1:$H$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⚗️ Alchimie'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'📦 Ressources'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏪 Shop'!$A$1:$I$34</definedName>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Généré le 2026-10-27 14:47 UTC</t>
+          <t>Généré le 2026-10-31 18:41 UTC</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8976,17 +8976,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>potion_soin_superieure</t>
+          <t>potion_soin_totale</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Potion de soin supérieure</t>
+          <t>Potion du Grand Cerisier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -9005,19 +9005,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rend 35 % des PV max (sans dépasser le maximum).</t>
+          <t>Rend 100 % des PV max. Offerte par Hana à la fin du tutoriel (/tuto).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>potion_mana</t>
+          <t>potion_soin_superieure</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Potion de mana</t>
+          <t>Potion de soin supérieure</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>mana_percent</t>
+          <t>heal_percent</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -9041,19 +9041,19 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Rend 50 % du mana max (sans dépasser le maximum).</t>
+          <t>Rend 35 % des PV max (sans dépasser le maximum).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elixir_recuperation</t>
+          <t>potion_mana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élixir de récupération</t>
+          <t>Potion de mana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9063,11 +9063,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>elixir</t>
+          <t>mana_percent</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -9077,19 +9077,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pendant 1 h, tes PV et ton mana remontent 3 fois plus vite hors combat. Le reboire renouvelle sa durée.</t>
+          <t>Rend 50 % du mana max (sans dépasser le maximum).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>elixir_force</t>
+          <t>elixir_recuperation</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Élixir de force</t>
+          <t>Élixir de récupération</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -9113,19 +9113,19 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>+10 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
+          <t>Pendant 1 h, tes PV et ton mana remontent 3 fois plus vite hors combat. Le reboire renouvelle sa durée.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elixir_garde</t>
+          <t>elixir_force</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Élixir de garde</t>
+          <t>Élixir de force</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9149,19 +9149,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>+10 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
+          <t>+10 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>elixir_vitalite</t>
+          <t>elixir_garde</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Élixir de vitalité</t>
+          <t>Élixir de garde</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -9185,19 +9185,19 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>+10 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
+          <t>+10 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>grande_potion_soin</t>
+          <t>elixir_vitalite</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grande potion de soin</t>
+          <t>Élixir de vitalité</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9207,11 +9207,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>heal_percent</t>
+          <t>elixir</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -9221,19 +9221,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rend 60 % des PV max (sans dépasser le maximum).</t>
+          <t>+10 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>grande_potion_mana</t>
+          <t>grande_potion_soin</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Grande potion de mana</t>
+          <t>Grande potion de soin</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -9243,11 +9243,11 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>mana_percent</t>
+          <t>heal_percent</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -9257,19 +9257,19 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Rend tout le mana.</t>
+          <t>Rend 60 % des PV max (sans dépasser le maximum).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>elixir_recuperation_sup</t>
+          <t>grande_potion_mana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Élixir de récupération supérieur</t>
+          <t>Grande potion de mana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9279,11 +9279,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>elixir</t>
+          <t>mana_percent</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -9293,19 +9293,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pendant 1 h, tes PV et ton mana remontent 5 fois plus vite hors combat. Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
+          <t>Rend tout le mana.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>elixir_force_sup</t>
+          <t>elixir_recuperation_sup</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Élixir de force supérieur</t>
+          <t>Élixir de récupération supérieur</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -9329,19 +9329,19 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>+20 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
+          <t>Pendant 1 h, tes PV et ton mana remontent 5 fois plus vite hors combat. Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>elixir_garde_sup</t>
+          <t>elixir_force_sup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Élixir de garde supérieur</t>
+          <t>Élixir de force supérieur</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9365,19 +9365,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>+20 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
+          <t>+20 % d'attaque pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>elixir_vitalite_sup</t>
+          <t>elixir_garde_sup</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Élixir de vitalité supérieur</t>
+          <t>Élixir de garde supérieur</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -9401,19 +9401,19 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>+20 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
+          <t>+20 % de défense pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cor_chasse_f</t>
+          <t>elixir_vitalite_sup</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cor de chasse de la Clairière</t>
+          <t>Élixir de vitalité supérieur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9423,10 +9423,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>summon_elite</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>elixir</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -9435,19 +9437,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>+20 % de PV max pendant 1 h, en combat de zone et au world boss (pas en épreuve ni en défi). Le reboire renouvelle sa durée ; un élixir plus faible du même type ne le remplace pas.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>cor_chasse_e</t>
+          <t>cor_chasse_f</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Cor de chasse du Cimetière</t>
+          <t>Cor de chasse de la Clairière</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -9469,19 +9471,19 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite du Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite de la Clairière sinistre (rang F) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cor_chasse_d</t>
+          <t>cor_chasse_e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cor de chasse du Berceau</t>
+          <t>Cor de chasse du Cimetière</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9503,19 +9505,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite du Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite du Cimetière abandonné (rang E) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>cor_chasse_c</t>
+          <t>cor_chasse_d</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Cor de chasse du Sanctuaire</t>
+          <t>Cor de chasse du Berceau</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -9537,19 +9539,19 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite du Sanctuaire primordial (rang C) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite du Berceau cataclysmique (rang D) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cor_chasse_b</t>
+          <t>cor_chasse_c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cor de chasse de l'Éclipse</t>
+          <t>Cor de chasse du Sanctuaire</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9571,19 +9573,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite de l'Éclipse éternelle (rang B) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite du Sanctuaire primordial (rang C) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>cor_chasse_a</t>
+          <t>cor_chasse_b</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Cor de chasse des Cimes</t>
+          <t>Cor de chasse de l'Éclipse</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -9605,19 +9607,19 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Fait apparaître l'élite des Cimes des Wyrms (rang A) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
+          <t>Fait apparaître l'élite de l'Éclipse éternelle (rang B) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sceau_souffle_e</t>
+          <t>cor_chasse_a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang E)</t>
+          <t>Cor de chasse des Cimes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9627,7 +9629,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>trial_retry</t>
+          <t>summon_elite</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -9639,19 +9641,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
+          <t>Fait apparaître l'élite des Cimes des Wyrms (rang A) dans le salon de la zone, à la suite du combat en cours. Il faut avoir accès à la zone ; 1 h d'attente entre deux cors, une seule élite invoquée par zone à la fois.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_d</t>
+          <t>sceau_souffle_e</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang D)</t>
+          <t>Sceau du second souffle (rang E)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -9673,19 +9675,19 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang E : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sceau_souffle_c</t>
+          <t>sceau_souffle_d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang C)</t>
+          <t>Sceau du second souffle (rang D)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9707,19 +9709,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang D : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_b</t>
+          <t>sceau_souffle_c</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang B)</t>
+          <t>Sceau du second souffle (rang C)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -9741,19 +9743,19 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang C : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sceau_souffle_a</t>
+          <t>sceau_souffle_b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang A)</t>
+          <t>Sceau du second souffle (rang B)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9775,19 +9777,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang B : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_s</t>
+          <t>sceau_souffle_a</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang S)</t>
+          <t>Sceau du second souffle (rang A)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -9809,19 +9811,19 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang A : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sceau_souffle_ss</t>
+          <t>sceau_souffle_s</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SS)</t>
+          <t>Sceau du second souffle (rang S)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9843,19 +9845,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang S : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>sceau_souffle_sss</t>
+          <t>sceau_souffle_ss</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Sceau du second souffle (rang SSS)</t>
+          <t>Sceau du second souffle (rang SS)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -9877,19 +9879,19 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang SS : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>parchemin_oubli</t>
+          <t>sceau_souffle_sss</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Parchemin d'oubli</t>
+          <t>Sceau du second souffle (rang SSS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9899,7 +9901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>respec_stats</t>
+          <t>trial_retry</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -9911,19 +9913,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
+          <t>Efface l'attente après un échec à l'épreuve du rang SSS : tu peux la retenter tout de suite.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>jeton_arbre</t>
+          <t>parchemin_oubli</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Jeton de réinitialisation d'arbre</t>
+          <t>Parchemin d'oubli</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -9933,7 +9935,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>reset_tree</t>
+          <t>respec_stats</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -9945,19 +9947,19 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+          <t>Reprend TOUS tes points de stats (attaque, défense, PV) : replace-les ensuite avec /stats.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sablier_fidelite</t>
+          <t>jeton_arbre</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sablier de fidélité</t>
+          <t>Jeton de réinitialisation d'arbre</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9967,7 +9969,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>daily_guard</t>
+          <t>reset_tree</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -9979,12 +9981,46 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>Réinitialise ton arbre de compétences EN PLUS du reset gratuit de la semaine (à garder pour quand il est déjà pris).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>sablier_fidelite</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Sablier de fidélité</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>daily_guard</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
           <t>Le premier jour de /daily manqué, ta série n'est pas divisée par deux. Il agit tout seul ; un seul à la fois.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H31"/>
+  <autoFilter ref="A1:H32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
